--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28616,6 +28616,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>95103</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>12.4799995422363</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28639,6 +28639,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1230" t="n">
+        <v>65547</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28662,6 +28662,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>186076</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>12.7399997711182</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28685,6 +28685,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1232" t="n">
+        <v>122856</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28526,22 +28526,22 @@
     </row>
     <row r="1225">
       <c r="A1225" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1225" t="n">
-        <v>136416</v>
+        <v>74156</v>
       </c>
       <c r="C1225" t="n">
-        <v>12.7600002288818</v>
+        <v>12.6800003051758</v>
       </c>
       <c r="D1225" t="n">
-        <v>12.6000003814697</v>
+        <v>12.5</v>
       </c>
       <c r="E1225" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1225" t="n">
         <v>12.6400003433228</v>
-      </c>
-      <c r="F1225" t="n">
-        <v>12.6999998092651</v>
       </c>
       <c r="G1225" t="s">
         <v>7</v>
@@ -28549,22 +28549,22 @@
     </row>
     <row r="1226">
       <c r="A1226" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1226" t="n">
-        <v>92993</v>
+        <v>136416</v>
       </c>
       <c r="C1226" t="n">
-        <v>12.8999996185303</v>
+        <v>12.7600002288818</v>
       </c>
       <c r="D1226" t="n">
-        <v>12.4200000762939</v>
+        <v>12.6000003814697</v>
       </c>
       <c r="E1226" t="n">
-        <v>12.8999996185303</v>
+        <v>12.6400003433228</v>
       </c>
       <c r="F1226" t="n">
-        <v>12.4399995803833</v>
+        <v>12.6999998092651</v>
       </c>
       <c r="G1226" t="s">
         <v>7</v>
@@ -28572,22 +28572,22 @@
     </row>
     <row r="1227">
       <c r="A1227" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1227" t="n">
-        <v>80047</v>
+        <v>92993</v>
       </c>
       <c r="C1227" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1227" t="n">
         <v>12.4399995803833</v>
-      </c>
-      <c r="D1227" t="n">
-        <v>12.2799997329712</v>
-      </c>
-      <c r="E1227" t="n">
-        <v>12.3800001144409</v>
-      </c>
-      <c r="F1227" t="n">
-        <v>12.3599996566772</v>
       </c>
       <c r="G1227" t="s">
         <v>7</v>
@@ -28595,22 +28595,22 @@
     </row>
     <row r="1228">
       <c r="A1228" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1228" t="n">
-        <v>72202</v>
+        <v>80047</v>
       </c>
       <c r="C1228" t="n">
-        <v>12.4799995422363</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D1228" t="n">
-        <v>12.1999998092651</v>
+        <v>12.2799997329712</v>
       </c>
       <c r="E1228" t="n">
-        <v>12.1999998092651</v>
+        <v>12.3800001144409</v>
       </c>
       <c r="F1228" t="n">
-        <v>12.3400001525879</v>
+        <v>12.3599996566772</v>
       </c>
       <c r="G1228" t="s">
         <v>7</v>
@@ -28618,22 +28618,22 @@
     </row>
     <row r="1229">
       <c r="A1229" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1229" t="n">
-        <v>95103</v>
+        <v>72202</v>
       </c>
       <c r="C1229" t="n">
-        <v>12.6599998474121</v>
+        <v>12.4799995422363</v>
       </c>
       <c r="D1229" t="n">
-        <v>12.3000001907349</v>
+        <v>12.1999998092651</v>
       </c>
       <c r="E1229" t="n">
-        <v>12.4799995422363</v>
+        <v>12.1999998092651</v>
       </c>
       <c r="F1229" t="n">
-        <v>12.5799999237061</v>
+        <v>12.3400001525879</v>
       </c>
       <c r="G1229" t="s">
         <v>7</v>
@@ -28641,22 +28641,22 @@
     </row>
     <row r="1230">
       <c r="A1230" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1230" t="n">
-        <v>65547</v>
+        <v>95103</v>
       </c>
       <c r="C1230" t="n">
-        <v>12.6800003051758</v>
+        <v>12.6599998474121</v>
       </c>
       <c r="D1230" t="n">
-        <v>12.460000038147</v>
+        <v>12.3000001907349</v>
       </c>
       <c r="E1230" t="n">
-        <v>12.5</v>
+        <v>12.4799995422363</v>
       </c>
       <c r="F1230" t="n">
-        <v>12.460000038147</v>
+        <v>12.5799999237061</v>
       </c>
       <c r="G1230" t="s">
         <v>7</v>
@@ -28664,22 +28664,22 @@
     </row>
     <row r="1231">
       <c r="A1231" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1231" t="n">
-        <v>186076</v>
+        <v>65547</v>
       </c>
       <c r="C1231" t="n">
-        <v>12.7399997711182</v>
+        <v>12.6800003051758</v>
       </c>
       <c r="D1231" t="n">
-        <v>12.3000001907349</v>
+        <v>12.460000038147</v>
       </c>
       <c r="E1231" t="n">
-        <v>12.3000001907349</v>
+        <v>12.5</v>
       </c>
       <c r="F1231" t="n">
-        <v>12.6000003814697</v>
+        <v>12.460000038147</v>
       </c>
       <c r="G1231" t="s">
         <v>7</v>
@@ -28687,24 +28687,47 @@
     </row>
     <row r="1232">
       <c r="A1232" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1232" t="n">
-        <v>122856</v>
+        <v>186076</v>
       </c>
       <c r="C1232" t="n">
-        <v>12.8999996185303</v>
+        <v>12.7399997711182</v>
       </c>
       <c r="D1232" t="n">
-        <v>12.6199998855591</v>
+        <v>12.3000001907349</v>
       </c>
       <c r="E1232" t="n">
-        <v>12.6199998855591</v>
+        <v>12.3000001907349</v>
       </c>
       <c r="F1232" t="n">
-        <v>12.8000001907349</v>
+        <v>12.6000003814697</v>
       </c>
       <c r="G1232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1233" t="n">
+        <v>151631</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>12.8400001525879</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>12.7799997329712</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>12.7799997329712</v>
+      </c>
+      <c r="G1233" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -551,7 +551,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738290786743</v>
+        <v>15.1738300323486</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197484970093</v>
+        <v>14.7197494506836</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007905960083</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710691452026</v>
+        <v>14.1710681915283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115901947021</v>
+        <v>13.8115911483765</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034309387207</v>
+        <v>12.903431892395</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466691970825</v>
+        <v>12.8466701507568</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.616870880127</v>
+        <v>11.6168718338013</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358306884766</v>
+        <v>12.3358316421509</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276714324951</v>
+        <v>11.4276723861694</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.834451675415</v>
+        <v>11.8344526290894</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G124" t="n">
-        <v>11.3425302505493</v>
+        <v>11.3425312042236</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614910125732</v>
+        <v>12.0614919662476</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371698379517</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223110198975</v>
+        <v>12.2223119735718</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.420970916748</v>
+        <v>12.4209699630737</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871114730835</v>
+        <v>11.0871124267578</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587320327759</v>
+        <v>11.0587310791016</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316528320312</v>
+        <v>10.1316518783569</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083282470703</v>
+        <v>9.97083187103271</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.349232673645</v>
+        <v>10.3492317199707</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789522171021</v>
+        <v>10.1789531707764</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729370117188</v>
+        <v>9.50729274749756</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884515762329</v>
+        <v>10.8884525299072</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>11.3425302505493</v>
+        <v>11.3425312042236</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371698379517</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.9006719589233</v>
+        <v>11.900671005249</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818307876587</v>
+        <v>13.2818298339844</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182907104492</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669700622559</v>
+        <v>13.3669710159302</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.4804887771606</v>
+        <v>13.480489730835</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912902832031</v>
+        <v>13.2912912368774</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.139931678772</v>
+        <v>13.1399307250977</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9696493148804</v>
+        <v>12.9696502685547</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088293075562</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723304748535</v>
+        <v>12.5723314285278</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.1777696609497</v>
+        <v>13.177770614624</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426498413086</v>
+        <v>13.4426488876343</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196317672729</v>
+        <v>12.6196308135986</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225093841553</v>
+        <v>15.7225074768066</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990909576416</v>
+        <v>15.1990919113159</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843811035156</v>
+        <v>15.0843820571899</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593688964844</v>
+        <v>14.7593698501587</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211332321167</v>
+        <v>14.7211322784424</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976064682007</v>
+        <v>14.7976055145264</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563999176025</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431257247925</v>
+        <v>12.9431247711182</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034027099609</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533782958984</v>
+        <v>11.8533792495728</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.9872074127197</v>
+        <v>11.987208366394</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.025444984436</v>
+        <v>12.0254440307617</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181125640869</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151426315308</v>
+        <v>11.8151416778564</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299022674561</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416881561279</v>
+        <v>13.8416891098022</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225698471069</v>
+        <v>13.8225708007812</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137548446655</v>
+        <v>14.0137538909912</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093463897705</v>
+        <v>14.1093454360962</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047555923462</v>
+        <v>14.4047546386719</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751253128052</v>
+        <v>15.9751262664795</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108379364014</v>
+        <v>16.1108360290527</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761779785156</v>
+        <v>14.6761770248413</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496124267578</v>
+        <v>16.1496105194092</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843166351318</v>
+        <v>15.6843156814575</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975772857666</v>
+        <v>15.8975763320923</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833101272583</v>
+        <v>15.0833110809326</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506622314453</v>
+        <v>14.8506631851196</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078193664551</v>
+        <v>14.3078184127808</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823036193848</v>
+        <v>14.4823045730591</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965698242188</v>
+        <v>15.2965707778931</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486059188843</v>
+        <v>15.5486068725586</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914958953857</v>
+        <v>14.1914949417114</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.210883140564</v>
+        <v>14.2108821868896</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976224899292</v>
+        <v>13.9976215362549</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.1639680862427</v>
+        <v>13.163969039917</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.920072555542</v>
+        <v>13.9200735092163</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210790634155</v>
+        <v>14.5210781097412</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751724243164</v>
+        <v>14.0751714706421</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098766326904</v>
+        <v>13.6098756790161</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.3497018814087</v>
+        <v>12.349702835083</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.524188041687</v>
+        <v>12.5241889953613</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017379760742</v>
+        <v>12.6017370223999</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037942886353</v>
+        <v>11.9037952423096</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.535436630249</v>
+        <v>11.5354356765747</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262453079224</v>
+        <v>11.8262462615967</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129856109619</v>
+        <v>11.6129846572876</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905345916748</v>
+        <v>11.6905355453491</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201177597046</v>
+        <v>12.0201187133789</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558294296265</v>
+        <v>12.1558303833008</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -32482,6 +32482,32 @@
         <v>12.8400001525879</v>
       </c>
       <c r="H1235" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1236" t="n">
+        <v>139016</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>13.2600002288818</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>12.8400001525879</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>12.9200000762939</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="H1236" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -551,7 +551,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738300323486</v>
+        <v>15.1738290786743</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197494506836</v>
+        <v>14.7197484970093</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.0007905960083</v>
+        <v>14.000789642334</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710681915283</v>
+        <v>14.1710691452026</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115911483765</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.903431892395</v>
+        <v>12.9034309387207</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466701507568</v>
+        <v>12.8466691970825</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.6168718338013</v>
+        <v>11.616870880127</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358316421509</v>
+        <v>12.3358306884766</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276723861694</v>
+        <v>11.4276714324951</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.8344526290894</v>
+        <v>11.834451675415</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G124" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425302505493</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979898452759</v>
+        <v>12.2979907989502</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614919662476</v>
+        <v>12.0614910125732</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371698379517</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223119735718</v>
+        <v>12.2223110198975</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209699630737</v>
+        <v>12.420970916748</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871124267578</v>
+        <v>11.0871114730835</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587310791016</v>
+        <v>11.0587320327759</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275926589966</v>
+        <v>10.0275936126709</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083187103271</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789531707764</v>
+        <v>10.1789522171021</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884525299072</v>
+        <v>10.8884515762329</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425302505493</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371698379517</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.900671005249</v>
+        <v>11.9006719589233</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818298339844</v>
+        <v>13.2818307876587</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182907104492</v>
+        <v>12.8182916641235</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669710159302</v>
+        <v>13.3669700622559</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804887771606</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912912368774</v>
+        <v>13.2912902832031</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399307250977</v>
+        <v>13.139931678772</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9696502685547</v>
+        <v>12.9696493148804</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088293075562</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723314285278</v>
+        <v>12.5723304748535</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.177770614624</v>
+        <v>13.1777696609497</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426488876343</v>
+        <v>13.4426498413086</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196308135986</v>
+        <v>12.6196317672729</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225074768066</v>
+        <v>15.7225093841553</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990919113159</v>
+        <v>15.1990909576416</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843820571899</v>
+        <v>15.0843811035156</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211322784424</v>
+        <v>14.7211332321167</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976055145264</v>
+        <v>14.7976064682007</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563999176025</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431247711182</v>
+        <v>12.9431257247925</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034027099609</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533782958984</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.987208366394</v>
+        <v>11.9872074127197</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.0254440307617</v>
+        <v>12.025444984436</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181125640869</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151416778564</v>
+        <v>11.8151426315308</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299022674561</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416891098022</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225708007812</v>
+        <v>13.8225698471069</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137538909912</v>
+        <v>14.0137548446655</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093454360962</v>
+        <v>14.1093463897705</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047546386719</v>
+        <v>14.4047555923462</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751262664795</v>
+        <v>15.9751253128052</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108360290527</v>
+        <v>16.1108379364014</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761770248413</v>
+        <v>14.6761779785156</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496105194092</v>
+        <v>16.1496124267578</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843156814575</v>
+        <v>15.6843166351318</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975763320923</v>
+        <v>15.8975772857666</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833110809326</v>
+        <v>15.0833101272583</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506631851196</v>
+        <v>14.8506622314453</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078184127808</v>
+        <v>14.3078193664551</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823045730591</v>
+        <v>14.4823036193848</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965707778931</v>
+        <v>15.2965698242188</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486068725586</v>
+        <v>15.5486059188843</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914949417114</v>
+        <v>14.1914958953857</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.2108821868896</v>
+        <v>14.210883140564</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976215362549</v>
+        <v>13.9976224899292</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.163969039917</v>
+        <v>13.1639680862427</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.9200735092163</v>
+        <v>13.920072555542</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210781097412</v>
+        <v>14.5210790634155</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751714706421</v>
+        <v>14.0751724243164</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098756790161</v>
+        <v>13.6098766326904</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.349702835083</v>
+        <v>12.3497018814087</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.5241889953613</v>
+        <v>12.524188041687</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017370223999</v>
+        <v>12.6017379760742</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037952423096</v>
+        <v>11.9037942886353</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.5354356765747</v>
+        <v>11.535436630249</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262462615967</v>
+        <v>11.8262453079224</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129846572876</v>
+        <v>11.6129856109619</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905355453491</v>
+        <v>11.6905345916748</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201187133789</v>
+        <v>12.0201177597046</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558303833008</v>
+        <v>12.1558294296265</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -32508,6 +32508,32 @@
         <v>13.1999998092651</v>
       </c>
       <c r="H1236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1237" t="n">
+        <v>94535</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>13.0799999237061</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="H1237" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387073516846</v>
+        <v>15.4387083053589</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954301834106</v>
+        <v>14.7954292297363</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873497009277</v>
+        <v>15.2873487472534</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738290786743</v>
+        <v>15.1738300323486</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>14.833270072937</v>
+        <v>14.8332691192627</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008285522461</v>
+        <v>14.7008295059204</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711099624634</v>
+        <v>14.8711090087891</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197484970093</v>
+        <v>14.7197504043579</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359493255615</v>
+        <v>14.4359502792358</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007905960083</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278289794922</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710691452026</v>
+        <v>14.171070098877</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547895431519</v>
+        <v>13.0547904968262</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466691970825</v>
+        <v>12.8466701507568</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2790699005127</v>
+        <v>12.279070854187</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357927322388</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952707290649</v>
+        <v>11.9952716827393</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>10.9735927581787</v>
+        <v>10.9735918045044</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736316680908</v>
+        <v>11.6736307144165</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357927322388</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G108" t="n">
-        <v>11.5601119995117</v>
+        <v>11.5601110458374</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884914398193</v>
+        <v>11.5884923934937</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G124" t="n">
-        <v>11.3425302505493</v>
+        <v>11.3425312042236</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195501327515</v>
+        <v>11.2195510864258</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168319702148</v>
+        <v>10.9168329238892</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303895950317</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979917526245</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G146" t="n">
-        <v>12.515570640564</v>
+        <v>12.5155696868896</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899103164673</v>
+        <v>12.7899112701416</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371698379517</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912105560303</v>
+        <v>11.8912115097046</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722906112671</v>
+        <v>11.8722915649414</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966117858887</v>
+        <v>11.7966108322144</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925914764404</v>
+        <v>12.3925905227661</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.6263303756714</v>
+        <v>11.6263313293457</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695714950562</v>
+        <v>11.5695705413818</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749717712402</v>
+        <v>11.4749708175659</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371318817139</v>
+        <v>11.4371309280396</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G215" t="n">
-        <v>11.5601119995117</v>
+        <v>11.5601110458374</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208902359009</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208902359009</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789920806885</v>
+        <v>10.8789930343628</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059915542603</v>
+        <v>10.4059925079346</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93299293518066</v>
+        <v>9.93299198150635</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947326660156</v>
+        <v>9.81947231292725</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.037052154541</v>
+        <v>10.0370512008667</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083282470703</v>
+        <v>9.97083377838135</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.5</v>
       </c>
       <c r="G235" t="n">
-        <v>9.93299293518066</v>
+        <v>9.93299198150635</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055236816406</v>
+        <v>9.80055141448975</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.349232673645</v>
+        <v>10.3492317199707</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0086727142334</v>
+        <v>10.0086736679077</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647369384766</v>
+        <v>9.34647274017334</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701229095459</v>
+        <v>9.33701324462891</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971290588379</v>
+        <v>9.28971385955811</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.96137237548828</v>
+        <v>9.9613733291626</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>11.3425302505493</v>
+        <v>11.3425312042236</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668523788452</v>
+        <v>11.2668514251709</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>11.0681924819946</v>
+        <v>11.0681915283203</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.247932434082</v>
+        <v>11.2479314804077</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G278" t="n">
-        <v>11.7020120620728</v>
+        <v>11.7020111083984</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992919921875</v>
+        <v>11.3992929458618</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966117858887</v>
+        <v>11.7966108322144</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885313034058</v>
+        <v>12.2885303497314</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371698379517</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939315795898</v>
+        <v>12.1939306259155</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>14</v>
       </c>
       <c r="G322" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872301101685</v>
+        <v>13.1872291564941</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075290679932</v>
+        <v>13.7075300216675</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.4804887771606</v>
+        <v>13.480489730835</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>14</v>
       </c>
       <c r="G331" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.139931678772</v>
+        <v>13.1399307250977</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9696493148804</v>
+        <v>12.9696502685547</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088312149048</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142305374146</v>
+        <v>12.7142295837402</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439500808716</v>
+        <v>12.5439519882202</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372106552124</v>
+        <v>12.8372097015381</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.764289855957</v>
+        <v>13.7642908096313</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.1777696609497</v>
+        <v>13.177770614624</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.7264499664307</v>
+        <v>13.726450920105</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196317672729</v>
+        <v>12.6196308135986</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737503051758</v>
+        <v>13.7737512588501</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278289794922</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225093841553</v>
+        <v>15.722508430481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549091339111</v>
+        <v>15.1549100875854</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.950553894043</v>
+        <v>14.9505529403687</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>14.3578844070435</v>
+        <v>14.3578834533691</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593688964844</v>
+        <v>14.7593698501587</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108318328857</v>
+        <v>14.5108308792114</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G409" t="n">
-        <v>14.3578844070435</v>
+        <v>14.3578834533691</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299501419067</v>
+        <v>14.5299491882324</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520383834839</v>
+        <v>15.3520374298096</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976064682007</v>
+        <v>14.7976055145264</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417369842529</v>
+        <v>15.1417360305786</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563980102539</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711097717285</v>
+        <v>14.0711088180542</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G454" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034046173096</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.388692855835</v>
+        <v>12.3886938095093</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533782958984</v>
+        <v>11.8533792495728</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.0636806488037</v>
+        <v>12.063681602478</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.29310131073</v>
+        <v>12.2931022644043</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181144714355</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769060134888</v>
+        <v>11.7769069671631</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239585876465</v>
+        <v>11.6239595413208</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.344612121582</v>
+        <v>13.3446111679077</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299003601074</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.440203666687</v>
+        <v>13.4402027130127</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G534" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.5931510925293</v>
+        <v>13.593150138855</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416881561279</v>
+        <v>13.8416872024536</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G572" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005294799805</v>
+        <v>14.3005285263062</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137548446655</v>
+        <v>14.0137538909912</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093463897705</v>
+        <v>14.1093454360962</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G594" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G596" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G597" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.2548637390137</v>
+        <v>12.254864692688</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>13.1151914596558</v>
+        <v>13.1151905059814</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G618" t="n">
-        <v>13.1151914596558</v>
+        <v>13.1151905059814</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754684448242</v>
+        <v>12.6754693984985</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G626" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -32534,6 +32534,32 @@
         <v>13.3000001907349</v>
       </c>
       <c r="H1237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>149252</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>13.460000038147</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>13.3999996185303</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1238" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387083053589</v>
+        <v>15.4387092590332</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873487472534</v>
+        <v>15.2873497009277</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>14.8332691192627</v>
+        <v>14.833270072937</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711090087891</v>
+        <v>14.8711099624634</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197504043579</v>
+        <v>14.7197494506836</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548683166504</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.246750831604</v>
+        <v>14.2467498779297</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.171070098877</v>
+        <v>14.1710681915283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G29" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250690460205</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250690460205</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.6223888397217</v>
+        <v>13.622389793396</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.6980695724487</v>
+        <v>13.6980686187744</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034309387207</v>
+        <v>12.9034299850464</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G50" t="n">
-        <v>12.7520704269409</v>
+        <v>12.7520694732666</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.279070854187</v>
+        <v>12.2790699005127</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817510604858</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357927322388</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952716827393</v>
+        <v>11.9952707290649</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817510604858</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006311416626</v>
+        <v>11.2006320953369</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763118743896</v>
+        <v>11.276312828064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736307144165</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>11.3519916534424</v>
+        <v>11.3519926071167</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357927322388</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G107" t="n">
-        <v>11.5222721099854</v>
+        <v>11.522271156311</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.834451675415</v>
+        <v>11.8344507217407</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817510604858</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884923934937</v>
+        <v>11.5884914398193</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G124" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425321578979</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952327728271</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074502944946</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195510864258</v>
+        <v>11.2195520401001</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168329238892</v>
+        <v>10.9168319702148</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979518890381</v>
+        <v>11.5979509353638</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195919036865</v>
+        <v>11.9195909500122</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979917526245</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899112701416</v>
+        <v>12.7899103164673</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912115097046</v>
+        <v>11.8912105560303</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722915649414</v>
+        <v>11.8722906112671</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966108322144</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>12.3452911376953</v>
+        <v>12.345290184021</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169116973877</v>
+        <v>12.3169107437134</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G179" t="n">
-        <v>12.3547515869141</v>
+        <v>12.3547506332397</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G191" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817510604858</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209320068359</v>
+        <v>11.7209310531616</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G208" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817510604858</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749708175659</v>
+        <v>11.4749717712402</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3709125518799</v>
+        <v>11.3709115982056</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371309280396</v>
+        <v>11.4371318817139</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871114730835</v>
+        <v>11.0871124267578</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208902359009</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208902359009</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059925079346</v>
+        <v>10.4059934616089</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947231292725</v>
+        <v>9.81947326660156</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>9.88569259643555</v>
+        <v>9.88569355010986</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0370512008667</v>
+        <v>10.037052154541</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083377838135</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.5</v>
       </c>
       <c r="G235" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055141448975</v>
+        <v>9.80055332183838</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621269226074</v>
+        <v>9.52621364593506</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971385955811</v>
+        <v>9.28971290588379</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884515762329</v>
+        <v>10.8884525299072</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425321578979</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668514251709</v>
+        <v>11.2668523788452</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952327728271</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290115356445</v>
+        <v>11.2290124893188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>11.0681915283203</v>
+        <v>11.0681924819946</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>11.1533317565918</v>
+        <v>11.1533327102661</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439121246338</v>
+        <v>11.8439102172852</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2479314804077</v>
+        <v>11.247932434082</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992929458618</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046913146973</v>
+        <v>11.3046922683716</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G283" t="n">
-        <v>12.2696113586426</v>
+        <v>12.2696104049683</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966108322144</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101314544678</v>
+        <v>11.9101305007935</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074502944946</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.9006719589233</v>
+        <v>11.900671005249</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939306259155</v>
+        <v>12.1939315795898</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>12.3547515869141</v>
+        <v>12.3547506332397</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>12.5534114837646</v>
+        <v>12.5534105300903</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818307876587</v>
+        <v>13.2818298339844</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182897567749</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872291564941</v>
+        <v>13.1872301101685</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G324" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250690460205</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804906845093</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385906219482</v>
+        <v>13.3385896682739</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.6980695724487</v>
+        <v>13.6980686187744</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399307250977</v>
+        <v>13.1399297714233</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088312149048</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439519882202</v>
+        <v>12.5439510345459</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.799370765686</v>
+        <v>12.7993698120117</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372097015381</v>
+        <v>12.8372106552124</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>12.7804508209229</v>
+        <v>12.7804498672485</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.7642908096313</v>
+        <v>13.764289855957</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.177770614624</v>
+        <v>13.1777696609497</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629098892212</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629098892212</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.726450920105</v>
+        <v>13.7264499664307</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548303604126</v>
+        <v>13.7548294067383</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764295578003</v>
+        <v>13.3764305114746</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737512588501</v>
+        <v>13.7737503051758</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548683166504</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684278488159</v>
+        <v>15.2684288024902</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765491485596</v>
+        <v>15.4765501022339</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.722508430481</v>
+        <v>15.7225093841553</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549100875854</v>
+        <v>15.1549091339111</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990909576416</v>
+        <v>15.1990919113159</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020149230957</v>
+        <v>14.7020139694214</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.0079078674316</v>
+        <v>15.007908821106</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G409" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064224243164</v>
+        <v>14.6064233779907</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211332321167</v>
+        <v>14.7211322784424</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G430" t="n">
-        <v>15.1799736022949</v>
+        <v>15.1799726486206</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902759552002</v>
+        <v>15.3902750015259</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563980102539</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G454" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034046173096</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.3886938095093</v>
+        <v>12.388692855835</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533802032471</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.273983001709</v>
+        <v>12.2739839553833</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181144714355</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769069671631</v>
+        <v>11.7769060134888</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151426315308</v>
+        <v>11.8151435852051</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960243225098</v>
+        <v>11.7960252761841</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299003601074</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G534" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G572" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G594" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G596" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G597" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137050628662</v>
+        <v>12.7137060165405</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.254864692688</v>
+        <v>12.2548656463623</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G618" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G626" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -32560,6 +32560,32 @@
         <v>13</v>
       </c>
       <c r="H1238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1239" t="n">
+        <v>63037</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>13.2600002288818</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>13.0600004196167</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="H1239" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387083053589</v>
+        <v>15.4387092590332</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1927490234375</v>
+        <v>15.1927480697632</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846277236938</v>
+        <v>14.9846286773682</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738300323486</v>
+        <v>15.1738290786743</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197504043579</v>
+        <v>14.7197494506836</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.0007905960083</v>
+        <v>14.000789642334</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819105148315</v>
+        <v>14.6819086074829</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927082061768</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.246750831604</v>
+        <v>14.2467498779297</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.171070098877</v>
+        <v>14.1710681915283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115892410278</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547914505005</v>
+        <v>13.0547904968262</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>12.9791097640991</v>
+        <v>12.9791107177734</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034299850464</v>
+        <v>12.9034309387207</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358316421509</v>
+        <v>12.3358306884766</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G63" t="n">
-        <v>11.9385108947754</v>
+        <v>11.9385118484497</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1844701766968</v>
+        <v>12.1844711303711</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952716827393</v>
+        <v>11.9952707290649</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G75" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006320953369</v>
+        <v>11.2006311416626</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763109207153</v>
+        <v>11.276312828064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951919555664</v>
+        <v>10.5951929092407</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303127288818</v>
+        <v>10.3303117752075</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>11.1249523162842</v>
+        <v>11.1249513626099</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736307144165</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.654712677002</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G92" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.834451675415</v>
+        <v>11.8344526290894</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5</v>
       </c>
       <c r="G112" t="n">
-        <v>12.7709903717041</v>
+        <v>12.7709913253784</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884923934937</v>
+        <v>11.588490486145</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G126" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.210090637207</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168319702148</v>
+        <v>10.9168329238892</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195909500122</v>
+        <v>11.9195919036865</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G139" t="n">
-        <v>11.9385108947754</v>
+        <v>11.9385118484497</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>12.0898704528809</v>
+        <v>12.0898714065552</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899112701416</v>
+        <v>12.7899103164673</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912115097046</v>
+        <v>11.8912105560303</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722915649414</v>
+        <v>11.8722906112671</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>12.3452920913696</v>
+        <v>12.3452911376953</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169116973877</v>
+        <v>12.3169107437134</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>12.2317724227905</v>
+        <v>12.2317705154419</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223110198975</v>
+        <v>12.2223119735718</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925905227661</v>
+        <v>12.3925914764404</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344896316528</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398519515991</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398519515991</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.62633228302</v>
+        <v>11.6263313293457</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209320068359</v>
+        <v>11.7209310531616</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.654712677002</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033512115479</v>
+        <v>11.5033502578735</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G205" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749708175659</v>
+        <v>11.4749717712402</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371309280396</v>
+        <v>11.4371318817139</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G216" t="n">
-        <v>11.1249523162842</v>
+        <v>11.1249513626099</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871124267578</v>
+        <v>11.0871133804321</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789930343628</v>
+        <v>10.8789920806885</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830123901367</v>
+        <v>10.2830114364624</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>9.88569355010986</v>
+        <v>9.88569259643555</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083377838135</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055141448975</v>
+        <v>9.80055236816406</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032743453979</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032743453979</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G244" t="n">
-        <v>10.1600332260132</v>
+        <v>10.1600322723389</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621269226074</v>
+        <v>9.52621173858643</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647274017334</v>
+        <v>9.34647369384766</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701229095459</v>
+        <v>9.33701324462891</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917335510254</v>
+        <v>9.29917240142822</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.210090637207</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>11.9668912887573</v>
+        <v>11.966890335083</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992929458618</v>
+        <v>11.3992910385132</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046913146973</v>
+        <v>11.3046922683716</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101314544678</v>
+        <v>11.9101305007935</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885313034058</v>
+        <v>12.2885303497314</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939306259155</v>
+        <v>12.1939315795898</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>14</v>
       </c>
       <c r="G322" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872301101685</v>
+        <v>13.1872291564941</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075300216675</v>
+        <v>13.7075290679932</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669700622559</v>
+        <v>13.3669710159302</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804906845093</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>14</v>
       </c>
       <c r="G331" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912902832031</v>
+        <v>13.2912912368774</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088293075562</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439519882202</v>
+        <v>12.5439510345459</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372097015381</v>
+        <v>12.8372106552124</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344896316528</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723314285278</v>
+        <v>12.5723304748535</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.7642908096313</v>
+        <v>13.764289855957</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.1777696609497</v>
+        <v>13.177770614624</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629117965698</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629117965698</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548294067383</v>
+        <v>13.7548303604126</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196308135986</v>
+        <v>12.6196298599243</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764305114746</v>
+        <v>13.3764295578003</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684278488159</v>
+        <v>15.2684288024902</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>15.2305898666382</v>
+        <v>15.2305889129639</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765491485596</v>
+        <v>15.4765481948853</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792284011841</v>
+        <v>15.0792293548584</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927082061768</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549091339111</v>
+        <v>15.1549081802368</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.9505529403687</v>
+        <v>14.950553894043</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108308792114</v>
+        <v>14.5108318328857</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G409" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299491882324</v>
+        <v>14.5299501419067</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520374298096</v>
+        <v>15.3520383834839</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976055145264</v>
+        <v>14.7976064682007</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417360305786</v>
+        <v>15.1417369842529</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563980102539</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711088180542</v>
+        <v>14.0711097717285</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G454" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034046173096</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.3886938095093</v>
+        <v>12.388692855835</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533782958984</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.063681602478</v>
+        <v>12.0636806488037</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.2931022644043</v>
+        <v>12.29310131073</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181144714355</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769069671631</v>
+        <v>11.7769060134888</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239595413208</v>
+        <v>11.6239585876465</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.3446111679077</v>
+        <v>13.344612121582</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299003601074</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.4402027130127</v>
+        <v>13.440203666687</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G534" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.593150138855</v>
+        <v>13.5931510925293</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416872024536</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G572" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005285263062</v>
+        <v>14.3005294799805</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137538909912</v>
+        <v>14.0137548446655</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093454360962</v>
+        <v>14.1093463897705</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G594" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G596" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G597" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.254864692688</v>
+        <v>12.2548637390137</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G618" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754693984985</v>
+        <v>12.6754684448242</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G626" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -32638,6 +32638,32 @@
         <v>13.0600004196167</v>
       </c>
       <c r="H1241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1242" t="n">
+        <v>105969</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>13.3800001144409</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>13.3800001144409</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>13.039999961853</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>13.039999961853</v>
+      </c>
+      <c r="H1242" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -28995,13 +28995,36 @@
         <v>12.8999996185303</v>
       </c>
       <c r="D1245" t="n">
-        <v>12.460000038147</v>
+        <v>12.4200000762939</v>
       </c>
       <c r="E1245" t="n">
         <v>12.8999996185303</v>
       </c>
-      <c r="F1245"/>
+      <c r="F1245" t="n">
+        <v>12.4200000762939</v>
+      </c>
       <c r="G1245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>84330</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1246"/>
+      <c r="G1246" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -29023,8 +29023,31 @@
       <c r="E1246" t="n">
         <v>12.8999996185303</v>
       </c>
-      <c r="F1246"/>
+      <c r="F1246" t="n">
+        <v>12.4799995422363</v>
+      </c>
       <c r="G1246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1247" t="n">
+        <v>139140</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>11.9799995422363</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="F1247"/>
+      <c r="G1247" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -29046,8 +29046,31 @@
       <c r="E1247" t="n">
         <v>12.6999998092651</v>
       </c>
-      <c r="F1247"/>
+      <c r="F1247" t="n">
+        <v>11.9799995422363</v>
+      </c>
       <c r="G1247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>114187</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>11.8199996948242</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1248"/>
+      <c r="G1248" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -29069,8 +29069,31 @@
       <c r="E1248" t="n">
         <v>12.8999996185303</v>
       </c>
-      <c r="F1248"/>
+      <c r="F1248" t="n">
+        <v>11.8599996566772</v>
+      </c>
       <c r="G1248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>53040</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>12.1800003051758</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>11.8800001144409</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>11.9799995422363</v>
+      </c>
+      <c r="F1249"/>
+      <c r="G1249" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -29099,6 +29099,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>38281</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387092590332</v>
+        <v>15.4387073516846</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954292297363</v>
+        <v>14.7954301834106</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873487472534</v>
+        <v>15.2873497009277</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846296310425</v>
+        <v>14.9846286773682</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711090087891</v>
+        <v>14.8711099624634</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007905960083</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819086074829</v>
+        <v>14.6819095611572</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2467489242554</v>
+        <v>14.246750831604</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710691452026</v>
+        <v>14.1710681915283</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115901947021</v>
+        <v>13.8115911483765</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.622389793396</v>
+        <v>13.6223888397217</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007516860962</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007516860962</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547904968262</v>
+        <v>13.0547895431519</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007099151611</v>
+        <v>12.6007108688354</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G45" t="n">
-        <v>12.9412717819214</v>
+        <v>12.9412708282471</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034309387207</v>
+        <v>12.903431892395</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466711044312</v>
+        <v>12.8466701507568</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.616870880127</v>
+        <v>11.6168718338013</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358306884766</v>
+        <v>12.3358316421509</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G63" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952716827393</v>
+        <v>11.9952707290649</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006320953369</v>
+        <v>11.2006311416626</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.276312828064</v>
+        <v>11.2763118743896</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951910018921</v>
+        <v>10.5951919555664</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303117752075</v>
+        <v>10.3303127288818</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>10.9735918045044</v>
+        <v>10.9735927581787</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736326217651</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>11.3519906997681</v>
+        <v>11.3519916534424</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276714324951</v>
+        <v>11.4276723861694</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.834451675415</v>
+        <v>11.8344526290894</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5</v>
       </c>
       <c r="G112" t="n">
-        <v>12.7709913253784</v>
+        <v>12.7709903717041</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195520401001</v>
+        <v>11.2195501327515</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168329238892</v>
+        <v>10.9168319702148</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>11.1627912521362</v>
+        <v>11.1627922058105</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979509353638</v>
+        <v>11.5979518890381</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G136" t="n">
-        <v>11.5317316055298</v>
+        <v>11.5317306518555</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195909500122</v>
+        <v>11.9195919036865</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G139" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331125259399</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614910125732</v>
+        <v>12.0614919662476</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899112701416</v>
+        <v>12.7899103164673</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912115097046</v>
+        <v>11.8912105560303</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169107437134</v>
+        <v>12.3169116973877</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223110198975</v>
+        <v>12.2223119735718</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.420970916748</v>
+        <v>12.4209699630737</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344915390015</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.62633228302</v>
+        <v>11.6263303756714</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695705413818</v>
+        <v>11.5695714950562</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033502578735</v>
+        <v>11.5033512115479</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059925079346</v>
+        <v>10.4059915542603</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830114364624</v>
+        <v>10.2830123901367</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083282470703</v>
+        <v>9.97083187103271</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0086736679077</v>
+        <v>10.0086727142334</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789522171021</v>
+        <v>10.1789531707764</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729370117188</v>
+        <v>9.50729274749756</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647274017334</v>
+        <v>9.34647369384766</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971195220947</v>
+        <v>9.28971290588379</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917240142822</v>
+        <v>9.29917335510254</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.9613733291626</v>
+        <v>9.96137237548828</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290124893188</v>
+        <v>11.2290115356445</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>11.0681915283203</v>
+        <v>11.0681924819946</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992910385132</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087505340576</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101305007935</v>
+        <v>11.9101314544678</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885303497314</v>
+        <v>12.2885313034058</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331125259399</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939306259155</v>
+        <v>12.1939315795898</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966905593872</v>
+        <v>13.1966896057129</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872291564941</v>
+        <v>13.1872301101685</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075309753418</v>
+        <v>13.7075290679932</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669700622559</v>
+        <v>13.3669710159302</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912902832031</v>
+        <v>13.2912912368774</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399297714233</v>
+        <v>13.1399307250977</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.969651222229</v>
+        <v>12.9696502685547</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088293075562</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142295837402</v>
+        <v>12.7142305374146</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439519882202</v>
+        <v>12.5439500808716</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344915390015</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723304748535</v>
+        <v>12.5723314285278</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088691711426</v>
+        <v>13.5088701248169</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.7642908096313</v>
+        <v>13.764289855957</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426498413086</v>
+        <v>13.4426488876343</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548313140869</v>
+        <v>13.7548303604126</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.5817899703979</v>
+        <v>12.5817909240723</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196298599243</v>
+        <v>12.6196308135986</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764305114746</v>
+        <v>13.3764295578003</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684288024902</v>
+        <v>15.2684278488159</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225093841553</v>
+        <v>15.7225074768066</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792284011841</v>
+        <v>15.0792293548584</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549081802368</v>
+        <v>15.1549091339111</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843811035156</v>
+        <v>15.0843820571899</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.9505529403687</v>
+        <v>14.950553894043</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108308792114</v>
+        <v>14.5108318328857</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299491882324</v>
+        <v>14.5299501419067</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4917116165161</v>
+        <v>14.4917125701904</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>15.5</v>
       </c>
       <c r="G423" t="n">
-        <v>14.8167238235474</v>
+        <v>14.8167247772217</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520393371582</v>
+        <v>15.3520383834839</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G434" t="n">
-        <v>14.7784872055054</v>
+        <v>14.7784881591797</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417360305786</v>
+        <v>15.1417369842529</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902750015259</v>
+        <v>15.3902759552002</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G444" t="n">
-        <v>13.9755163192749</v>
+        <v>13.9755172729492</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G445" t="n">
-        <v>13.6313858032227</v>
+        <v>13.631386756897</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563999176025</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>14.0902261734009</v>
+        <v>14.0902271270752</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711088180542</v>
+        <v>14.0711097717285</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049360275269</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G456" t="n">
-        <v>13.3254919052124</v>
+        <v>13.3254928588867</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>13.2872552871704</v>
+        <v>13.2872562408447</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431257247925</v>
+        <v>12.9431247711182</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034027099609</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.3886938095093</v>
+        <v>12.388692855835</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.063681602478</v>
+        <v>12.0636806488037</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1975107192993</v>
+        <v>12.197509765625</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181125640869</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>12.0828008651733</v>
+        <v>12.082799911499</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769069671631</v>
+        <v>11.7769060134888</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960252761841</v>
+        <v>11.7960243225098</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239595413208</v>
+        <v>11.6239585876465</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.5225229263306</v>
+        <v>12.5225219726562</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.3446111679077</v>
+        <v>13.344612121582</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G509" t="n">
-        <v>13.3254919052124</v>
+        <v>13.3254928588867</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>13.3063735961914</v>
+        <v>13.3063745498657</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9813632965088</v>
+        <v>12.9813623428345</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G515" t="n">
-        <v>13.2107820510864</v>
+        <v>13.2107830047607</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299022674561</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>13.2872552871704</v>
+        <v>13.2872562408447</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G523" t="n">
-        <v>13.3254919052124</v>
+        <v>13.3254928588867</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.4402027130127</v>
+        <v>13.440203666687</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G528" t="n">
-        <v>13.3254919052124</v>
+        <v>13.3254928588867</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G531" t="n">
-        <v>13.6313858032227</v>
+        <v>13.631386756897</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G532" t="n">
-        <v>13.6313858032227</v>
+        <v>13.631386756897</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.593150138855</v>
+        <v>13.5931510925293</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>13.7652139663696</v>
+        <v>13.7652149200439</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G548" t="n">
-        <v>13.6313858032227</v>
+        <v>13.631386756897</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>13.7652139663696</v>
+        <v>13.7652149200439</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049360275269</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>15</v>
       </c>
       <c r="G586" t="n">
-        <v>14.3387651443481</v>
+        <v>14.3387660980225</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G591" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G595" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>12.9240083694458</v>
+        <v>12.9240074157715</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G619" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754693984985</v>
+        <v>12.6754684448242</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -32906,7 +32906,7 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B1252" t="n">
-        <v>88997</v>
+        <v>97506</v>
       </c>
       <c r="C1252" t="n">
         <v>12.7200002670288</v>
@@ -32924,6 +32924,32 @@
         <v>12.3999996185303</v>
       </c>
       <c r="H1252" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1253" t="n">
+        <v>271415</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>12.539999961853</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>12.539999961853</v>
+      </c>
+      <c r="H1253" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -551,7 +551,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738300323486</v>
+        <v>15.1738290786743</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197494506836</v>
+        <v>14.7197484970093</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.0007905960083</v>
+        <v>14.000789642334</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710681915283</v>
+        <v>14.1710691452026</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115911483765</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.903431892395</v>
+        <v>12.9034309387207</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466701507568</v>
+        <v>12.8466691970825</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.6168718338013</v>
+        <v>11.616870880127</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358316421509</v>
+        <v>12.3358306884766</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276723861694</v>
+        <v>11.4276714324951</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.8344526290894</v>
+        <v>11.834451675415</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G124" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425302505493</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303895950317</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979898452759</v>
+        <v>12.2979907989502</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614919662476</v>
+        <v>12.0614910125732</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371698379517</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223119735718</v>
+        <v>12.2223110198975</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209699630737</v>
+        <v>12.420970916748</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G190" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871124267578</v>
+        <v>11.0871114730835</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587310791016</v>
+        <v>11.0587320327759</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275926589966</v>
+        <v>10.0275936126709</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083187103271</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789531707764</v>
+        <v>10.1789522171021</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884525299072</v>
+        <v>10.8884515762329</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>11.3425312042236</v>
+        <v>11.3425302505493</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>11.966890335083</v>
+        <v>11.9668912887573</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371698379517</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.900671005249</v>
+        <v>11.9006719589233</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818298339844</v>
+        <v>13.2818307876587</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182907104492</v>
+        <v>12.8182916641235</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669710159302</v>
+        <v>13.3669700622559</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804887771606</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912912368774</v>
+        <v>13.2912902832031</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399307250977</v>
+        <v>13.139931678772</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9696502685547</v>
+        <v>12.9696493148804</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088293075562</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723314285278</v>
+        <v>12.5723304748535</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.177770614624</v>
+        <v>13.1777696609497</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426488876343</v>
+        <v>13.4426498413086</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196308135986</v>
+        <v>12.6196317672729</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225074768066</v>
+        <v>15.7225093841553</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990919113159</v>
+        <v>15.1990909576416</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843820571899</v>
+        <v>15.0843811035156</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211322784424</v>
+        <v>14.7211332321167</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976055145264</v>
+        <v>14.7976064682007</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563999176025</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431247711182</v>
+        <v>12.9431257247925</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034027099609</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533782958984</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.987208366394</v>
+        <v>11.9872074127197</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.0254440307617</v>
+        <v>12.025444984436</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181125640869</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151416778564</v>
+        <v>11.8151426315308</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299022674561</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416891098022</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225708007812</v>
+        <v>13.8225698471069</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137538909912</v>
+        <v>14.0137548446655</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093454360962</v>
+        <v>14.1093463897705</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047546386719</v>
+        <v>14.4047555923462</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751262664795</v>
+        <v>15.9751253128052</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108360290527</v>
+        <v>16.1108379364014</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761770248413</v>
+        <v>14.6761779785156</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496105194092</v>
+        <v>16.1496124267578</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843156814575</v>
+        <v>15.6843166351318</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975763320923</v>
+        <v>15.8975772857666</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833110809326</v>
+        <v>15.0833101272583</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506631851196</v>
+        <v>14.8506622314453</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078184127808</v>
+        <v>14.3078193664551</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823045730591</v>
+        <v>14.4823036193848</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965707778931</v>
+        <v>15.2965698242188</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486068725586</v>
+        <v>15.5486059188843</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914949417114</v>
+        <v>14.1914958953857</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.2108821868896</v>
+        <v>14.210883140564</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976215362549</v>
+        <v>13.9976224899292</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.163969039917</v>
+        <v>13.1639680862427</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.9200735092163</v>
+        <v>13.920072555542</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210781097412</v>
+        <v>14.5210790634155</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751714706421</v>
+        <v>14.0751724243164</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098756790161</v>
+        <v>13.6098766326904</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.349702835083</v>
+        <v>12.3497018814087</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.5241889953613</v>
+        <v>12.524188041687</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017370223999</v>
+        <v>12.6017379760742</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037952423096</v>
+        <v>11.9037942886353</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.5354356765747</v>
+        <v>11.535436630249</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262462615967</v>
+        <v>11.8262453079224</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129846572876</v>
+        <v>11.6129856109619</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905355453491</v>
+        <v>11.6905345916748</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201187133789</v>
+        <v>12.0201177597046</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558303833008</v>
+        <v>12.1558294296265</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -32950,6 +32950,32 @@
         <v>12.539999961853</v>
       </c>
       <c r="H1253" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1254" t="n">
+        <v>36793</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="H1254" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387083053589</v>
+        <v>15.4387092590332</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954301834106</v>
+        <v>14.7954292297363</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -485,7 +485,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873487472534</v>
+        <v>15.2873497009277</v>
       </c>
       <c r="H4" t="n">
         <v>131763</v>
@@ -572,7 +572,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738300323486</v>
+        <v>15.1738290786743</v>
       </c>
       <c r="H7" t="n">
         <v>90407</v>
@@ -746,7 +746,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>14.379189491272</v>
+        <v>14.3791885375977</v>
       </c>
       <c r="H13" t="n">
         <v>27473</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548683166504</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899909973145</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -833,7 +833,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359493255615</v>
+        <v>14.4359502792358</v>
       </c>
       <c r="H16" t="n">
         <v>13170</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899909973145</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -891,7 +891,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007905960083</v>
       </c>
       <c r="H18" t="n">
         <v>7979</v>
@@ -920,7 +920,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>14.379189491272</v>
+        <v>14.3791885375977</v>
       </c>
       <c r="H19" t="n">
         <v>20715</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819095611572</v>
+        <v>14.6819086074829</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927082061768</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2467498779297</v>
+        <v>14.2467489242554</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1152,7 +1152,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115911483765</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="n">
         <v>47594</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926692962646</v>
+        <v>13.7926712036133</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1471,7 +1471,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H38" t="n">
         <v>18250</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1558,7 +1558,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H41" t="n">
         <v>36059</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007108688354</v>
+        <v>12.6007099151611</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1761,7 +1761,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466701507568</v>
+        <v>12.8466711044312</v>
       </c>
       <c r="H48" t="n">
         <v>83814</v>
@@ -1848,7 +1848,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2790699005127</v>
+        <v>12.279070854187</v>
       </c>
       <c r="H51" t="n">
         <v>54490</v>
@@ -1877,7 +1877,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H52" t="n">
         <v>30733</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.616870880127</v>
+        <v>11.6168718338013</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -2022,7 +2022,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H57" t="n">
         <v>59171</v>
@@ -2051,7 +2051,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H58" t="n">
         <v>38827</v>
@@ -2080,7 +2080,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H59" t="n">
         <v>23840</v>
@@ -2196,7 +2196,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G63" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H63" t="n">
         <v>22454</v>
@@ -2254,7 +2254,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1844720840454</v>
+        <v>12.1844711303711</v>
       </c>
       <c r="H65" t="n">
         <v>17790</v>
@@ -2283,7 +2283,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H66" t="n">
         <v>68260</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2370,7 +2370,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H69" t="n">
         <v>21775</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.108790397644</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2457,7 +2457,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H72" t="n">
         <v>14203</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2544,7 +2544,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G75" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H75" t="n">
         <v>23088</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2602,7 +2602,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H77" t="n">
         <v>19525</v>
@@ -2631,7 +2631,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H78" t="n">
         <v>9685</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763118743896</v>
+        <v>11.276312828064</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951919555664</v>
+        <v>10.5951910018921</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2776,7 +2776,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303127288818</v>
+        <v>10.3303117752075</v>
       </c>
       <c r="H83" t="n">
         <v>41339</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2921,7 +2921,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736326217651</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="n">
         <v>118173</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -2979,7 +2979,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H90" t="n">
         <v>13547</v>
@@ -3008,7 +3008,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H91" t="n">
         <v>194662</v>
@@ -3037,7 +3037,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G92" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H92" t="n">
         <v>21761</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141508102417</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276723861694</v>
+        <v>11.4276704788208</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3443,7 +3443,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H106" t="n">
         <v>19298</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3559,7 +3559,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.8344526290894</v>
+        <v>11.834451675415</v>
       </c>
       <c r="H110" t="n">
         <v>21276</v>
@@ -3588,7 +3588,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H111" t="n">
         <v>18000</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3849,7 +3849,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H120" t="n">
         <v>18650</v>
@@ -3907,7 +3907,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>11.6641712188721</v>
+        <v>11.6641721725464</v>
       </c>
       <c r="H122" t="n">
         <v>38398</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.588490486145</v>
+        <v>11.5884914398193</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4023,7 +4023,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G126" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H126" t="n">
         <v>54519</v>
@@ -4052,7 +4052,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H127" t="n">
         <v>53178</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979509353638</v>
+        <v>11.5979518890381</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4313,7 +4313,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G136" t="n">
-        <v>11.5317316055298</v>
+        <v>11.5317306518555</v>
       </c>
       <c r="H136" t="n">
         <v>34461</v>
@@ -4342,7 +4342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H137" t="n">
         <v>33734</v>
@@ -4371,7 +4371,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195909500122</v>
+        <v>11.9195919036865</v>
       </c>
       <c r="H138" t="n">
         <v>19683</v>
@@ -4400,7 +4400,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G139" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H139" t="n">
         <v>13065</v>
@@ -4429,7 +4429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H140" t="n">
         <v>24892</v>
@@ -4545,7 +4545,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H144" t="n">
         <v>9829</v>
@@ -4574,7 +4574,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="n">
         <v>14891</v>
@@ -4748,7 +4748,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614910125732</v>
+        <v>12.0614919662476</v>
       </c>
       <c r="H151" t="n">
         <v>41978</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4922,7 +4922,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H157" t="n">
         <v>25916</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.108790397644</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5038,7 +5038,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H161" t="n">
         <v>34152</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5125,7 +5125,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912115097046</v>
+        <v>11.8912105560303</v>
       </c>
       <c r="H164" t="n">
         <v>18357</v>
@@ -5154,7 +5154,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722906112671</v>
+        <v>11.8722915649414</v>
       </c>
       <c r="H165" t="n">
         <v>6548</v>
@@ -5241,7 +5241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H168" t="n">
         <v>17974</v>
@@ -5299,7 +5299,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169107437134</v>
+        <v>12.3169116973877</v>
       </c>
       <c r="H170" t="n">
         <v>6203</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5415,7 +5415,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H174" t="n">
         <v>9566</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750106811523</v>
+        <v>12.175009727478</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209699630737</v>
+        <v>12.420970916748</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.5912523269653</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5705,7 +5705,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344915390015</v>
       </c>
       <c r="H184" t="n">
         <v>90193</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.108790397644</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5792,7 +5792,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H187" t="n">
         <v>3679</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.108790397644</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5850,7 +5850,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H189" t="n">
         <v>22438</v>
@@ -5908,7 +5908,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G191" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H191" t="n">
         <v>5115</v>
@@ -5937,7 +5937,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H192" t="n">
         <v>9607</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6198,7 +6198,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209310531616</v>
+        <v>11.7209320068359</v>
       </c>
       <c r="H201" t="n">
         <v>4105</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6256,7 +6256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033502578735</v>
+        <v>11.5033512115479</v>
       </c>
       <c r="H203" t="n">
         <v>16925</v>
@@ -6285,7 +6285,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H204" t="n">
         <v>5041</v>
@@ -6314,7 +6314,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G205" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H205" t="n">
         <v>14567</v>
@@ -6401,7 +6401,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G208" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H208" t="n">
         <v>15504</v>
@@ -6459,7 +6459,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749727249146</v>
+        <v>11.4749717712402</v>
       </c>
       <c r="H210" t="n">
         <v>12812</v>
@@ -6488,7 +6488,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3709125518799</v>
+        <v>11.3709115982056</v>
       </c>
       <c r="H211" t="n">
         <v>30604</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141508102417</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6778,7 +6778,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789920806885</v>
+        <v>10.8789930343628</v>
       </c>
       <c r="H221" t="n">
         <v>10402</v>
@@ -6807,7 +6807,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059915542603</v>
+        <v>10.4059925079346</v>
       </c>
       <c r="H222" t="n">
         <v>8716</v>
@@ -6836,7 +6836,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1221933364868</v>
+        <v>10.1221914291382</v>
       </c>
       <c r="H223" t="n">
         <v>18441</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -7068,7 +7068,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>10.1221933364868</v>
+        <v>10.1221914291382</v>
       </c>
       <c r="H231" t="n">
         <v>19711</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275926589966</v>
+        <v>10.0275936126709</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0370512008667</v>
+        <v>10.037052154541</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083282470703</v>
+        <v>9.97083187103271</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055332183838</v>
+        <v>9.80055236816406</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032743453979</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032743453979</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7445,7 +7445,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G244" t="n">
-        <v>10.1600322723389</v>
+        <v>10.1600313186646</v>
       </c>
       <c r="H244" t="n">
         <v>12339</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621173858643</v>
+        <v>9.52621364593506</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7648,7 +7648,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647369384766</v>
+        <v>9.34647274017334</v>
       </c>
       <c r="H251" t="n">
         <v>15863</v>
@@ -7677,7 +7677,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701229095459</v>
+        <v>9.33701324462891</v>
       </c>
       <c r="H252" t="n">
         <v>8169</v>
@@ -7706,7 +7706,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971290588379</v>
+        <v>9.28971195220947</v>
       </c>
       <c r="H253" t="n">
         <v>10943</v>
@@ -7735,7 +7735,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917240142822</v>
+        <v>9.29917335510254</v>
       </c>
       <c r="H254" t="n">
         <v>10680</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141508102417</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141508102417</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439121246338</v>
+        <v>11.8439111709595</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8431,7 +8431,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G278" t="n">
-        <v>11.7020111083984</v>
+        <v>11.7020120620728</v>
       </c>
       <c r="H278" t="n">
         <v>6135</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992910385132</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101305007935</v>
+        <v>11.9101314544678</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8779,7 +8779,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H290" t="n">
         <v>11428</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8866,7 +8866,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885313034058</v>
+        <v>12.2885303497314</v>
       </c>
       <c r="H293" t="n">
         <v>19905</v>
@@ -8895,7 +8895,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H294" t="n">
         <v>39678</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750106811523</v>
+        <v>12.175009727478</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -8953,7 +8953,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H296" t="n">
         <v>113027</v>
@@ -9011,7 +9011,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H298" t="n">
         <v>4631</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.108790397644</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939315795898</v>
+        <v>12.1939306259155</v>
       </c>
       <c r="H304" t="n">
         <v>1793</v>
@@ -9243,7 +9243,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H306" t="n">
         <v>22411</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141916275024</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9533,7 +9533,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818298339844</v>
+        <v>13.2818307876587</v>
       </c>
       <c r="H316" t="n">
         <v>52099</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182907104492</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9649,7 +9649,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966905593872</v>
+        <v>13.1966896057129</v>
       </c>
       <c r="H320" t="n">
         <v>115939</v>
@@ -9707,7 +9707,7 @@
         <v>14</v>
       </c>
       <c r="G322" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H322" t="n">
         <v>121250</v>
@@ -9736,7 +9736,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872291564941</v>
+        <v>13.1872301101685</v>
       </c>
       <c r="H323" t="n">
         <v>10973</v>
@@ -9852,7 +9852,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669700622559</v>
+        <v>13.3669710159302</v>
       </c>
       <c r="H327" t="n">
         <v>36337</v>
@@ -9968,7 +9968,7 @@
         <v>14</v>
       </c>
       <c r="G331" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H331" t="n">
         <v>50115</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467109680176</v>
+        <v>13.5467090606689</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10055,7 +10055,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399297714233</v>
+        <v>13.1399307250977</v>
       </c>
       <c r="H334" t="n">
         <v>35387</v>
@@ -10084,7 +10084,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H335" t="n">
         <v>11048</v>
@@ -10113,7 +10113,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9696502685547</v>
+        <v>12.969651222229</v>
       </c>
       <c r="H336" t="n">
         <v>8861</v>
@@ -10287,7 +10287,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344915390015</v>
       </c>
       <c r="H342" t="n">
         <v>31055</v>
@@ -10316,7 +10316,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723304748535</v>
+        <v>12.5723314285278</v>
       </c>
       <c r="H343" t="n">
         <v>71453</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088701248169</v>
+        <v>13.5088691711426</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10432,7 +10432,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.1777696609497</v>
+        <v>13.177770614624</v>
       </c>
       <c r="H347" t="n">
         <v>1624911</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548313140869</v>
+        <v>13.7548303604126</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10693,7 +10693,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.5817899703979</v>
+        <v>12.5817909240723</v>
       </c>
       <c r="H356" t="n">
         <v>162095</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.5912523269653</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10780,7 +10780,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H359" t="n">
         <v>54126</v>
@@ -10809,7 +10809,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H360" t="n">
         <v>130944</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764295578003</v>
+        <v>13.3764305114746</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10867,7 +10867,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737503051758</v>
+        <v>13.7737512588501</v>
       </c>
       <c r="H362" t="n">
         <v>69104</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926692962646</v>
+        <v>13.7926712036133</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548683166504</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11099,7 +11099,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522298812866</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H370" t="n">
         <v>87340</v>
@@ -11128,7 +11128,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G371" t="n">
-        <v>15.344108581543</v>
+        <v>15.3441076278687</v>
       </c>
       <c r="H371" t="n">
         <v>38672</v>
@@ -11186,7 +11186,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522298812866</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H373" t="n">
         <v>58745</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225093841553</v>
+        <v>15.7225103378296</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11244,7 +11244,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522298812866</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H375" t="n">
         <v>73481</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792293548584</v>
+        <v>15.0792284011841</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927082061768</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11360,7 +11360,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549081802368</v>
+        <v>15.1549091339111</v>
       </c>
       <c r="H379" t="n">
         <v>175080</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11476,7 +11476,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H383" t="n">
         <v>42204</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11679,7 +11679,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843820571899</v>
+        <v>15.0843811035156</v>
       </c>
       <c r="H390" t="n">
         <v>50895</v>
@@ -11708,7 +11708,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H391" t="n">
         <v>32365</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020149230957</v>
+        <v>14.7020139694214</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.0079078674316</v>
+        <v>15.007908821106</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314346313477</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314346313477</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -11911,7 +11911,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.950553894043</v>
+        <v>14.9505529403687</v>
       </c>
       <c r="H398" t="n">
         <v>35897</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12201,7 +12201,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108318328857</v>
+        <v>14.5108308792114</v>
       </c>
       <c r="H408" t="n">
         <v>38004</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064224243164</v>
+        <v>14.6064233779907</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12346,7 +12346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H413" t="n">
         <v>34048</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12404,7 +12404,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H415" t="n">
         <v>18337</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299501419067</v>
+        <v>14.5299482345581</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12491,7 +12491,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4917125701904</v>
+        <v>14.4917116165161</v>
       </c>
       <c r="H418" t="n">
         <v>21147</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12752,7 +12752,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G427" t="n">
-        <v>15.2373285293579</v>
+        <v>15.2373275756836</v>
       </c>
       <c r="H427" t="n">
         <v>44358</v>
@@ -12897,7 +12897,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H432" t="n">
         <v>28274</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314346313477</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13042,7 +13042,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9696712493896</v>
+        <v>14.9696702957153</v>
       </c>
       <c r="H437" t="n">
         <v>13330</v>
@@ -13071,7 +13071,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H438" t="n">
         <v>18515</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902759552002</v>
+        <v>15.3902750015259</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13187,7 +13187,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G442" t="n">
-        <v>15.2373285293579</v>
+        <v>15.2373275756836</v>
       </c>
       <c r="H442" t="n">
         <v>36186</v>
@@ -13216,7 +13216,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H443" t="n">
         <v>45829</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563999176025</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>14.0902271270752</v>
+        <v>14.0902261734009</v>
       </c>
       <c r="H448" t="n">
         <v>21910</v>
@@ -13419,7 +13419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711097717285</v>
+        <v>14.0711088180542</v>
       </c>
       <c r="H450" t="n">
         <v>16818</v>
@@ -13506,7 +13506,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G453" t="n">
-        <v>13.68874168396</v>
+        <v>13.6887407302856</v>
       </c>
       <c r="H453" t="n">
         <v>37597</v>
@@ -13564,7 +13564,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H455" t="n">
         <v>15285</v>
@@ -13709,7 +13709,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431247711182</v>
+        <v>12.9431257247925</v>
       </c>
       <c r="H460" t="n">
         <v>31924</v>
@@ -13796,7 +13796,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H463" t="n">
         <v>22702</v>
@@ -13825,7 +13825,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H464" t="n">
         <v>16431</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034027099609</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14086,7 +14086,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.388692855835</v>
+        <v>12.3886938095093</v>
       </c>
       <c r="H473" t="n">
         <v>30946</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14289,7 +14289,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.987208366394</v>
+        <v>11.9872074127197</v>
       </c>
       <c r="H480" t="n">
         <v>47163</v>
@@ -14318,7 +14318,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.0636806488037</v>
+        <v>12.063681602478</v>
       </c>
       <c r="H481" t="n">
         <v>28977</v>
@@ -14347,7 +14347,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.0254440307617</v>
+        <v>12.025444984436</v>
       </c>
       <c r="H482" t="n">
         <v>53386</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.273983001709</v>
+        <v>12.2739839553833</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181125640869</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14550,7 +14550,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>12.082799911499</v>
+        <v>12.0828008651733</v>
       </c>
       <c r="H489" t="n">
         <v>48158</v>
@@ -14579,7 +14579,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>12.10191822052</v>
+        <v>12.1019172668457</v>
       </c>
       <c r="H490" t="n">
         <v>55351</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151416778564</v>
+        <v>11.8151426315308</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -14724,7 +14724,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>12.044563293457</v>
+        <v>12.0445642471313</v>
       </c>
       <c r="H495" t="n">
         <v>11804</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960243225098</v>
+        <v>11.7960252761841</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14811,7 +14811,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239585876465</v>
+        <v>11.6239595413208</v>
       </c>
       <c r="H498" t="n">
         <v>38500</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.5225219726562</v>
+        <v>12.5225229263306</v>
       </c>
       <c r="H500" t="n">
         <v>76184</v>
@@ -15014,7 +15014,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G505" t="n">
-        <v>12.8857698440552</v>
+        <v>12.8857707977295</v>
       </c>
       <c r="H505" t="n">
         <v>58282</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15101,7 +15101,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.344612121582</v>
+        <v>13.3446111679077</v>
       </c>
       <c r="H508" t="n">
         <v>57867</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H512" t="n">
         <v>20590</v>
@@ -15246,7 +15246,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9813623428345</v>
+        <v>12.9813632965088</v>
       </c>
       <c r="H513" t="n">
         <v>115376</v>
@@ -15304,7 +15304,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G515" t="n">
-        <v>13.2107830047607</v>
+        <v>13.2107820510864</v>
       </c>
       <c r="H515" t="n">
         <v>37142</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299022674561</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15420,7 +15420,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H519" t="n">
         <v>40078</v>
@@ -15449,7 +15449,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H520" t="n">
         <v>21758</v>
@@ -15478,7 +15478,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H521" t="n">
         <v>64754</v>
@@ -15507,7 +15507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H522" t="n">
         <v>13016</v>
@@ -15565,7 +15565,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.440203666687</v>
+        <v>13.4402027130127</v>
       </c>
       <c r="H524" t="n">
         <v>10410</v>
@@ -15594,7 +15594,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G525" t="n">
-        <v>13.612268447876</v>
+        <v>13.6122674942017</v>
       </c>
       <c r="H525" t="n">
         <v>28328</v>
@@ -15826,7 +15826,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H533" t="n">
         <v>18743</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16000,7 +16000,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H539" t="n">
         <v>78221</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16116,7 +16116,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.5931510925293</v>
+        <v>13.593150138855</v>
       </c>
       <c r="H543" t="n">
         <v>40682</v>
@@ -16174,7 +16174,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G545" t="n">
-        <v>13.68874168396</v>
+        <v>13.6887407302856</v>
       </c>
       <c r="H545" t="n">
         <v>37826</v>
@@ -16290,7 +16290,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>13.650505065918</v>
+        <v>13.6505041122437</v>
       </c>
       <c r="H549" t="n">
         <v>19079</v>
@@ -16348,7 +16348,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H551" t="n">
         <v>11098</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416891098022</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16406,7 +16406,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225708007812</v>
+        <v>13.8225698471069</v>
       </c>
       <c r="H553" t="n">
         <v>12102</v>
@@ -16522,7 +16522,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H557" t="n">
         <v>24397</v>
@@ -16580,7 +16580,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H559" t="n">
         <v>22244</v>
@@ -16609,7 +16609,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H560" t="n">
         <v>16756</v>
@@ -16638,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H561" t="n">
         <v>10223</v>
@@ -16754,7 +16754,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H565" t="n">
         <v>66135</v>
@@ -16783,7 +16783,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H566" t="n">
         <v>38521</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16841,7 +16841,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H568" t="n">
         <v>46017</v>
@@ -16899,7 +16899,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H570" t="n">
         <v>219173</v>
@@ -16928,7 +16928,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H571" t="n">
         <v>178522</v>
@@ -17044,7 +17044,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H575" t="n">
         <v>33781</v>
@@ -17073,7 +17073,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H576" t="n">
         <v>20626</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17450,7 +17450,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G589" t="n">
-        <v>13.612268447876</v>
+        <v>13.6122674942017</v>
       </c>
       <c r="H589" t="n">
         <v>1148601</v>
@@ -17479,7 +17479,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H590" t="n">
         <v>109158</v>
@@ -17508,7 +17508,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G591" t="n">
-        <v>13.650505065918</v>
+        <v>13.6505041122437</v>
       </c>
       <c r="H591" t="n">
         <v>64144</v>
@@ -17624,7 +17624,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G595" t="n">
-        <v>13.1343097686768</v>
+        <v>13.1343088150024</v>
       </c>
       <c r="H595" t="n">
         <v>46485</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137050628662</v>
+        <v>12.7137060165405</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17740,7 +17740,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H599" t="n">
         <v>76279</v>
@@ -17769,7 +17769,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>12.9240074157715</v>
+        <v>12.9240083694458</v>
       </c>
       <c r="H600" t="n">
         <v>34751</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17943,7 +17943,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.2548637390137</v>
+        <v>12.254864692688</v>
       </c>
       <c r="H606" t="n">
         <v>57474</v>
@@ -18030,7 +18030,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H609" t="n">
         <v>88111</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H611" t="n">
         <v>86158</v>
@@ -18262,7 +18262,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H617" t="n">
         <v>46574</v>
@@ -18320,7 +18320,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G619" t="n">
-        <v>13.1343097686768</v>
+        <v>13.1343088150024</v>
       </c>
       <c r="H619" t="n">
         <v>185777</v>
@@ -18494,7 +18494,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754684448242</v>
+        <v>12.6754693984985</v>
       </c>
       <c r="H625" t="n">
         <v>51174</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18610,7 +18610,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G629" t="n">
-        <v>12.5416402816772</v>
+        <v>12.5416393280029</v>
       </c>
       <c r="H629" t="n">
         <v>54542</v>
@@ -18668,7 +18668,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H631" t="n">
         <v>69447</v>
@@ -18697,7 +18697,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>12.8857698440552</v>
+        <v>12.8857707977295</v>
       </c>
       <c r="H632" t="n">
         <v>24374</v>
@@ -36741,6 +36741,64 @@
         <v>36793</v>
       </c>
       <c r="I1254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1255" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>35465</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1256" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>12.1800003051758</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>66169</v>
+      </c>
+      <c r="I1256" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387092590332</v>
+        <v>15.4387083053589</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -485,7 +485,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873497009277</v>
+        <v>15.2873487472534</v>
       </c>
       <c r="H4" t="n">
         <v>131763</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846296310425</v>
+        <v>14.9846286773682</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -572,7 +572,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738290786743</v>
+        <v>15.1738300323486</v>
       </c>
       <c r="H7" t="n">
         <v>90407</v>
@@ -630,7 +630,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>14.833270072937</v>
+        <v>14.8332691192627</v>
       </c>
       <c r="H9" t="n">
         <v>13899</v>
@@ -659,7 +659,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008285522461</v>
+        <v>14.7008295059204</v>
       </c>
       <c r="H10" t="n">
         <v>75622</v>
@@ -688,7 +688,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711099624634</v>
+        <v>14.8711090087891</v>
       </c>
       <c r="H11" t="n">
         <v>77954</v>
@@ -717,7 +717,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197494506836</v>
+        <v>14.7197504043579</v>
       </c>
       <c r="H12" t="n">
         <v>31842</v>
@@ -746,7 +746,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>14.3791885375977</v>
+        <v>14.379189491272</v>
       </c>
       <c r="H13" t="n">
         <v>27473</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548692703247</v>
+        <v>14.4548683166504</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899909973145</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899909973145</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -920,7 +920,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>14.3791885375977</v>
+        <v>14.379189491272</v>
       </c>
       <c r="H19" t="n">
         <v>20715</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819086074829</v>
+        <v>14.6819095611572</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2467489242554</v>
+        <v>14.246750831604</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1094,7 +1094,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278289794922</v>
       </c>
       <c r="H25" t="n">
         <v>54159</v>
@@ -1123,7 +1123,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710691452026</v>
+        <v>14.171070098877</v>
       </c>
       <c r="H26" t="n">
         <v>81706</v>
@@ -1297,7 +1297,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.622389793396</v>
+        <v>13.6223888397217</v>
       </c>
       <c r="H32" t="n">
         <v>22783</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926712036133</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007099151611</v>
+        <v>12.6007108688354</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1761,7 +1761,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466711044312</v>
+        <v>12.8466701507568</v>
       </c>
       <c r="H48" t="n">
         <v>83814</v>
@@ -1790,7 +1790,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H49" t="n">
         <v>62308</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.6168718338013</v>
+        <v>11.616870880127</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1935,7 +1935,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H54" t="n">
         <v>41198</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357927322388</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -2022,7 +2022,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H57" t="n">
         <v>59171</v>
@@ -2109,7 +2109,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H60" t="n">
         <v>20661</v>
@@ -2167,7 +2167,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H62" t="n">
         <v>17275</v>
@@ -2283,7 +2283,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H66" t="n">
         <v>68260</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2399,7 +2399,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H70" t="n">
         <v>77040</v>
@@ -2457,7 +2457,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H72" t="n">
         <v>14203</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2544,7 +2544,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G75" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H75" t="n">
         <v>23088</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2631,7 +2631,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H78" t="n">
         <v>9685</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.276312828064</v>
+        <v>11.2763118743896</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951910018921</v>
+        <v>10.5951919555664</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2776,7 +2776,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303117752075</v>
+        <v>10.3303127288818</v>
       </c>
       <c r="H83" t="n">
         <v>41339</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2921,7 +2921,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736316680908</v>
+        <v>11.6736307144165</v>
       </c>
       <c r="H88" t="n">
         <v>118173</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -2979,7 +2979,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H90" t="n">
         <v>13547</v>
@@ -3008,7 +3008,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H91" t="n">
         <v>194662</v>
@@ -3037,7 +3037,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G92" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H92" t="n">
         <v>21761</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276704788208</v>
+        <v>11.4276714324951</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628301620483</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357927322388</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3443,7 +3443,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H106" t="n">
         <v>19298</v>
@@ -3501,7 +3501,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G108" t="n">
-        <v>11.5601119995117</v>
+        <v>11.5601110458374</v>
       </c>
       <c r="H108" t="n">
         <v>51913</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3704,7 +3704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H115" t="n">
         <v>10754</v>
@@ -3733,7 +3733,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H116" t="n">
         <v>29281</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3907,7 +3907,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>11.6641721725464</v>
+        <v>11.6641712188721</v>
       </c>
       <c r="H122" t="n">
         <v>38398</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884914398193</v>
+        <v>11.5884923934937</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4023,7 +4023,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G126" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H126" t="n">
         <v>54519</v>
@@ -4081,7 +4081,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H128" t="n">
         <v>17714</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4342,7 +4342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H137" t="n">
         <v>33734</v>
@@ -4574,7 +4574,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979898452759</v>
+        <v>12.2979917526245</v>
       </c>
       <c r="H145" t="n">
         <v>14891</v>
@@ -4603,7 +4603,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G146" t="n">
-        <v>12.515570640564</v>
+        <v>12.5155696868896</v>
       </c>
       <c r="H146" t="n">
         <v>29207</v>
@@ -4632,7 +4632,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H147" t="n">
         <v>23423</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4748,7 +4748,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614919662476</v>
+        <v>12.0614910125732</v>
       </c>
       <c r="H151" t="n">
         <v>41978</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4864,7 +4864,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H155" t="n">
         <v>41701</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -5067,7 +5067,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="n">
         <v>39212</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628301620483</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5125,7 +5125,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912105560303</v>
+        <v>11.8912115097046</v>
       </c>
       <c r="H164" t="n">
         <v>18357</v>
@@ -5212,7 +5212,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966117858887</v>
+        <v>11.7966108322144</v>
       </c>
       <c r="H167" t="n">
         <v>6760</v>
@@ -5241,7 +5241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H168" t="n">
         <v>17974</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5386,7 +5386,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H173" t="n">
         <v>21249</v>
@@ -5415,7 +5415,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H174" t="n">
         <v>9566</v>
@@ -5444,7 +5444,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="n">
         <v>13252</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.175009727478</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925914764404</v>
+        <v>12.3925905227661</v>
       </c>
       <c r="H181" t="n">
         <v>37878</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5705,7 +5705,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344915390015</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H184" t="n">
         <v>90193</v>
@@ -5734,7 +5734,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H185" t="n">
         <v>18304</v>
@@ -5792,7 +5792,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H187" t="n">
         <v>3679</v>
@@ -5937,7 +5937,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H192" t="n">
         <v>9607</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6024,7 +6024,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H195" t="n">
         <v>9323</v>
@@ -6053,7 +6053,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H196" t="n">
         <v>5717</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6111,7 +6111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H198" t="n">
         <v>9999</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695714950562</v>
+        <v>11.5695705413818</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6285,7 +6285,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H204" t="n">
         <v>5041</v>
@@ -6314,7 +6314,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G205" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H205" t="n">
         <v>14567</v>
@@ -6372,7 +6372,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H207" t="n">
         <v>15879</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6459,7 +6459,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749717712402</v>
+        <v>11.4749708175659</v>
       </c>
       <c r="H210" t="n">
         <v>12812</v>
@@ -6488,7 +6488,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3709115982056</v>
+        <v>11.3709125518799</v>
       </c>
       <c r="H211" t="n">
         <v>30604</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6575,7 +6575,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371318817139</v>
+        <v>11.4371309280396</v>
       </c>
       <c r="H214" t="n">
         <v>46989</v>
@@ -6604,7 +6604,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G215" t="n">
-        <v>11.5601119995117</v>
+        <v>11.5601110458374</v>
       </c>
       <c r="H215" t="n">
         <v>5494</v>
@@ -6662,7 +6662,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871124267578</v>
+        <v>11.0871114730835</v>
       </c>
       <c r="H217" t="n">
         <v>62592</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208902359009</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208902359009</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6836,7 +6836,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1221914291382</v>
+        <v>10.1221923828125</v>
       </c>
       <c r="H223" t="n">
         <v>18441</v>
@@ -6865,7 +6865,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830114364624</v>
+        <v>10.2830123901367</v>
       </c>
       <c r="H224" t="n">
         <v>15661</v>
@@ -6952,7 +6952,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H227" t="n">
         <v>62780</v>
@@ -7010,7 +7010,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947326660156</v>
+        <v>9.81947231292725</v>
       </c>
       <c r="H229" t="n">
         <v>68277</v>
@@ -7068,7 +7068,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>10.1221914291382</v>
+        <v>10.1221923828125</v>
       </c>
       <c r="H231" t="n">
         <v>19711</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.037052154541</v>
+        <v>10.0370512008667</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083187103271</v>
+        <v>9.97083377838135</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055236816406</v>
+        <v>9.80055141448975</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7387,7 +7387,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029327392578</v>
+        <v>9.98029232025146</v>
       </c>
       <c r="H242" t="n">
         <v>3631</v>
@@ -7445,7 +7445,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G244" t="n">
-        <v>10.1600313186646</v>
+        <v>10.1600322723389</v>
       </c>
       <c r="H244" t="n">
         <v>12339</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621364593506</v>
+        <v>9.52621269226074</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7706,7 +7706,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971195220947</v>
+        <v>9.28971385955811</v>
       </c>
       <c r="H253" t="n">
         <v>10943</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7938,7 +7938,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668523788452</v>
+        <v>11.2668514251709</v>
       </c>
       <c r="H261" t="n">
         <v>11841</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -7996,7 +7996,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290124893188</v>
+        <v>11.2290115356445</v>
       </c>
       <c r="H263" t="n">
         <v>3066</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141527175903</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8228,7 +8228,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H271" t="n">
         <v>119668</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439111709595</v>
+        <v>11.8439121246338</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8373,7 +8373,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.247932434082</v>
+        <v>11.2479314804077</v>
       </c>
       <c r="H276" t="n">
         <v>32729</v>
@@ -8431,7 +8431,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G278" t="n">
-        <v>11.7020120620728</v>
+        <v>11.7020111083984</v>
       </c>
       <c r="H278" t="n">
         <v>6135</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992919921875</v>
+        <v>11.3992929458618</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8605,7 +8605,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966117858887</v>
+        <v>11.7966108322144</v>
       </c>
       <c r="H284" t="n">
         <v>13107</v>
@@ -8634,7 +8634,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H285" t="n">
         <v>8932</v>
@@ -8721,7 +8721,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="n">
         <v>5961</v>
@@ -8779,7 +8779,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H290" t="n">
         <v>11428</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.175009727478</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -8982,7 +8982,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H297" t="n">
         <v>1507</v>
@@ -9011,7 +9011,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H298" t="n">
         <v>4631</v>
@@ -9069,7 +9069,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H300" t="n">
         <v>23263</v>
@@ -9098,7 +9098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.900671005249</v>
+        <v>11.9006719589233</v>
       </c>
       <c r="H301" t="n">
         <v>4323</v>
@@ -9127,7 +9127,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249912261963</v>
+        <v>11.8249921798706</v>
       </c>
       <c r="H302" t="n">
         <v>35060</v>
@@ -9243,7 +9243,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858102798462</v>
       </c>
       <c r="H306" t="n">
         <v>22411</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141916275024</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9359,7 +9359,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H310" t="n">
         <v>86708</v>
@@ -9388,7 +9388,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H311" t="n">
         <v>118963</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9591,7 +9591,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H318" t="n">
         <v>114421</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182907104492</v>
+        <v>12.8182916641235</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9736,7 +9736,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872301101685</v>
+        <v>13.1872291564941</v>
       </c>
       <c r="H323" t="n">
         <v>10973</v>
@@ -9852,7 +9852,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669710159302</v>
+        <v>13.3669700622559</v>
       </c>
       <c r="H327" t="n">
         <v>36337</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467090606689</v>
+        <v>13.5467100143433</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10113,7 +10113,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G336" t="n">
-        <v>12.969651222229</v>
+        <v>12.9696502685547</v>
       </c>
       <c r="H336" t="n">
         <v>8861</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088312149048</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10171,7 +10171,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142305374146</v>
+        <v>12.7142295837402</v>
       </c>
       <c r="H338" t="n">
         <v>27898</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439510345459</v>
+        <v>12.5439519882202</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10258,7 +10258,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372106552124</v>
+        <v>12.8372097015381</v>
       </c>
       <c r="H341" t="n">
         <v>71543</v>
@@ -10287,7 +10287,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344915390015</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H342" t="n">
         <v>31055</v>
@@ -10316,7 +10316,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723314285278</v>
+        <v>12.5723304748535</v>
       </c>
       <c r="H343" t="n">
         <v>71453</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088691711426</v>
+        <v>13.5088701248169</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10403,7 +10403,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.764289855957</v>
+        <v>13.7642908096313</v>
       </c>
       <c r="H346" t="n">
         <v>87295</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10577,7 +10577,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.7264499664307</v>
+        <v>13.726450920105</v>
       </c>
       <c r="H352" t="n">
         <v>43550</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764305114746</v>
+        <v>13.3764295578003</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926712036133</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -10983,7 +10983,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278289794922</v>
       </c>
       <c r="H366" t="n">
         <v>130359</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548692703247</v>
+        <v>14.4548683166504</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11041,7 +11041,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684288024902</v>
+        <v>15.2684278488159</v>
       </c>
       <c r="H368" t="n">
         <v>206675</v>
@@ -11128,7 +11128,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G371" t="n">
-        <v>15.3441076278687</v>
+        <v>15.344108581543</v>
       </c>
       <c r="H371" t="n">
         <v>38672</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225103378296</v>
+        <v>15.722508430481</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792284011841</v>
+        <v>15.0792293548584</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11360,7 +11360,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549091339111</v>
+        <v>15.1549100875854</v>
       </c>
       <c r="H379" t="n">
         <v>175080</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11563,7 +11563,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990919113159</v>
+        <v>15.1990909576416</v>
       </c>
       <c r="H386" t="n">
         <v>145295</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020139694214</v>
+        <v>14.7020149230957</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.007908821106</v>
+        <v>15.0079078674316</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314336776733</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314336776733</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12085,7 +12085,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>14.3578844070435</v>
+        <v>14.3578834533691</v>
       </c>
       <c r="H404" t="n">
         <v>39114</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593688964844</v>
+        <v>14.7593698501587</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12230,7 +12230,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G409" t="n">
-        <v>14.3578844070435</v>
+        <v>14.3578834533691</v>
       </c>
       <c r="H409" t="n">
         <v>107726</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064233779907</v>
+        <v>14.6064224243164</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299482345581</v>
+        <v>14.5299491882324</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12491,7 +12491,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4917116165161</v>
+        <v>14.4917125701904</v>
       </c>
       <c r="H418" t="n">
         <v>21147</v>
@@ -12520,7 +12520,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211322784424</v>
+        <v>14.7211332321167</v>
       </c>
       <c r="H419" t="n">
         <v>25706</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12694,7 +12694,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H425" t="n">
         <v>125301</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12752,7 +12752,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G427" t="n">
-        <v>15.2373275756836</v>
+        <v>15.2373285293579</v>
       </c>
       <c r="H427" t="n">
         <v>44358</v>
@@ -12781,7 +12781,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520383834839</v>
+        <v>15.3520374298096</v>
       </c>
       <c r="H428" t="n">
         <v>49360</v>
@@ -12868,7 +12868,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H431" t="n">
         <v>30989</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314336776733</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13042,7 +13042,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9696702957153</v>
+        <v>14.9696712493896</v>
       </c>
       <c r="H437" t="n">
         <v>13330</v>
@@ -13100,7 +13100,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417369842529</v>
+        <v>15.1417360305786</v>
       </c>
       <c r="H439" t="n">
         <v>30668</v>
@@ -13129,7 +13129,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H440" t="n">
         <v>20791</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902750015259</v>
+        <v>15.3902759552002</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13187,7 +13187,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G442" t="n">
-        <v>15.2373275756836</v>
+        <v>15.2373285293579</v>
       </c>
       <c r="H442" t="n">
         <v>36186</v>
@@ -13303,7 +13303,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H446" t="n">
         <v>27084</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563980102539</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>14.0902261734009</v>
+        <v>14.0902271270752</v>
       </c>
       <c r="H448" t="n">
         <v>21910</v>
@@ -13448,7 +13448,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H451" t="n">
         <v>24187</v>
@@ -13506,7 +13506,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G453" t="n">
-        <v>13.6887407302856</v>
+        <v>13.68874168396</v>
       </c>
       <c r="H453" t="n">
         <v>37597</v>
@@ -13535,7 +13535,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G454" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H454" t="n">
         <v>51758</v>
@@ -13738,7 +13738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H461" t="n">
         <v>47646</v>
@@ -13767,7 +13767,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H462" t="n">
         <v>24475</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034046173096</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13941,7 +13941,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H468" t="n">
         <v>37228</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14115,7 +14115,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H474" t="n">
         <v>62001</v>
@@ -14144,7 +14144,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H475" t="n">
         <v>61238</v>
@@ -14173,7 +14173,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H476" t="n">
         <v>68346</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.2739839553833</v>
+        <v>12.273983001709</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14463,7 +14463,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H486" t="n">
         <v>45367</v>
@@ -14492,7 +14492,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.29310131073</v>
+        <v>12.2931022644043</v>
       </c>
       <c r="H487" t="n">
         <v>28990</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181144714355</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14550,7 +14550,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>12.0828008651733</v>
+        <v>12.082799911499</v>
       </c>
       <c r="H489" t="n">
         <v>48158</v>
@@ -14579,7 +14579,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>12.1019172668457</v>
+        <v>12.10191822052</v>
       </c>
       <c r="H490" t="n">
         <v>55351</v>
@@ -14637,7 +14637,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769060134888</v>
+        <v>11.7769069671631</v>
       </c>
       <c r="H492" t="n">
         <v>22268</v>
@@ -14724,7 +14724,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>12.0445642471313</v>
+        <v>12.044563293457</v>
       </c>
       <c r="H495" t="n">
         <v>11804</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960252761841</v>
+        <v>11.7960243225098</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.5225229263306</v>
+        <v>12.5225219726562</v>
       </c>
       <c r="H500" t="n">
         <v>76184</v>
@@ -14898,7 +14898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H501" t="n">
         <v>67973</v>
@@ -14956,7 +14956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H503" t="n">
         <v>36066</v>
@@ -15014,7 +15014,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G505" t="n">
-        <v>12.8857707977295</v>
+        <v>12.8857698440552</v>
       </c>
       <c r="H505" t="n">
         <v>58282</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15072,7 +15072,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H507" t="n">
         <v>55125</v>
@@ -15246,7 +15246,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9813632965088</v>
+        <v>12.9813623428345</v>
       </c>
       <c r="H513" t="n">
         <v>115376</v>
@@ -15304,7 +15304,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G515" t="n">
-        <v>13.2107820510864</v>
+        <v>13.2107830047607</v>
       </c>
       <c r="H515" t="n">
         <v>37142</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299003601074</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15594,7 +15594,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G525" t="n">
-        <v>13.6122674942017</v>
+        <v>13.612268447876</v>
       </c>
       <c r="H525" t="n">
         <v>28328</v>
@@ -15623,7 +15623,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H526" t="n">
         <v>18896</v>
@@ -15855,7 +15855,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G534" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H534" t="n">
         <v>25283</v>
@@ -15884,7 +15884,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H535" t="n">
         <v>118515</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16174,7 +16174,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G545" t="n">
-        <v>13.6887407302856</v>
+        <v>13.68874168396</v>
       </c>
       <c r="H545" t="n">
         <v>37826</v>
@@ -16290,7 +16290,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H549" t="n">
         <v>19079</v>
@@ -16319,7 +16319,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H550" t="n">
         <v>10006</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416881561279</v>
+        <v>13.8416872024536</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16435,7 +16435,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H554" t="n">
         <v>25672</v>
@@ -16493,7 +16493,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H556" t="n">
         <v>13812</v>
@@ -16551,7 +16551,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H558" t="n">
         <v>27948</v>
@@ -16725,7 +16725,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H564" t="n">
         <v>58797</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16957,7 +16957,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G572" t="n">
-        <v>13.554913520813</v>
+        <v>13.5549125671387</v>
       </c>
       <c r="H572" t="n">
         <v>33579</v>
@@ -16986,7 +16986,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H573" t="n">
         <v>66012</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17160,7 +17160,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005294799805</v>
+        <v>14.3005285263062</v>
       </c>
       <c r="H579" t="n">
         <v>77910</v>
@@ -17334,7 +17334,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H585" t="n">
         <v>62831</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17450,7 +17450,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G589" t="n">
-        <v>13.6122674942017</v>
+        <v>13.612268447876</v>
       </c>
       <c r="H589" t="n">
         <v>1148601</v>
@@ -17508,7 +17508,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G591" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H591" t="n">
         <v>64144</v>
@@ -17537,7 +17537,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H592" t="n">
         <v>66158</v>
@@ -17595,7 +17595,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G594" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H594" t="n">
         <v>74613</v>
@@ -17624,7 +17624,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G595" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H595" t="n">
         <v>46485</v>
@@ -17653,7 +17653,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G596" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H596" t="n">
         <v>44483</v>
@@ -17682,7 +17682,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G597" t="n">
-        <v>13.0195989608765</v>
+        <v>13.0195999145508</v>
       </c>
       <c r="H597" t="n">
         <v>36061</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137060165405</v>
+        <v>12.7137050628662</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17769,7 +17769,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>12.9240083694458</v>
+        <v>12.9240074157715</v>
       </c>
       <c r="H600" t="n">
         <v>34751</v>
@@ -17798,7 +17798,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H601" t="n">
         <v>36560</v>
@@ -17827,7 +17827,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H602" t="n">
         <v>51879</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17972,7 +17972,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H607" t="n">
         <v>33493</v>
@@ -18175,7 +18175,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H614" t="n">
         <v>147836</v>
@@ -18233,7 +18233,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>13.1151914596558</v>
+        <v>13.1151905059814</v>
       </c>
       <c r="H616" t="n">
         <v>69661</v>
@@ -18291,7 +18291,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G618" t="n">
-        <v>13.1151914596558</v>
+        <v>13.1151905059814</v>
       </c>
       <c r="H618" t="n">
         <v>52967</v>
@@ -18320,7 +18320,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G619" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H619" t="n">
         <v>185777</v>
@@ -18523,7 +18523,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G626" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H626" t="n">
         <v>25180</v>
@@ -18552,7 +18552,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H627" t="n">
         <v>64899</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18610,7 +18610,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G629" t="n">
-        <v>12.5416393280029</v>
+        <v>12.5416402816772</v>
       </c>
       <c r="H629" t="n">
         <v>54542</v>
@@ -18639,7 +18639,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>12.5607585906982</v>
+        <v>12.5607595443726</v>
       </c>
       <c r="H630" t="n">
         <v>50458</v>
@@ -18697,7 +18697,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>12.8857707977295</v>
+        <v>12.8857698440552</v>
       </c>
       <c r="H632" t="n">
         <v>24374</v>
@@ -18784,7 +18784,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H635" t="n">
         <v>124717</v>
@@ -18871,7 +18871,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H638" t="n">
         <v>21080</v>
@@ -18900,7 +18900,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H639" t="n">
         <v>40704</v>
@@ -18929,7 +18929,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H640" t="n">
         <v>101641</v>
@@ -18958,7 +18958,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047546386719</v>
+        <v>14.4047555923462</v>
       </c>
       <c r="H641" t="n">
         <v>104803</v>
@@ -19045,7 +19045,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H644" t="n">
         <v>37693</v>
@@ -19132,7 +19132,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H647" t="n">
         <v>62394</v>
@@ -19306,7 +19306,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H653" t="n">
         <v>67181</v>
@@ -19480,7 +19480,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H659" t="n">
         <v>65476</v>
@@ -19538,7 +19538,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H661" t="n">
         <v>35343</v>
@@ -19625,7 +19625,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H664" t="n">
         <v>45922</v>
@@ -19654,7 +19654,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751262664795</v>
+        <v>15.9751253128052</v>
       </c>
       <c r="H665" t="n">
         <v>60499</v>
@@ -19683,7 +19683,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108360290527</v>
+        <v>16.1108379364014</v>
       </c>
       <c r="H666" t="n">
         <v>28199</v>
@@ -19770,7 +19770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H669" t="n">
         <v>107477</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761770248413</v>
+        <v>14.6761779785156</v>
       </c>
       <c r="H672" t="n">
         <v>131068</v>
@@ -19944,7 +19944,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H675" t="n">
         <v>84935</v>
@@ -20002,7 +20002,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H677" t="n">
         <v>28484</v>
@@ -20031,7 +20031,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H678" t="n">
         <v>45965</v>
@@ -20089,7 +20089,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H680" t="n">
         <v>49932</v>
@@ -20205,7 +20205,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H684" t="n">
         <v>33213</v>
@@ -20263,7 +20263,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H686" t="n">
         <v>149634</v>
@@ -20292,7 +20292,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H687" t="n">
         <v>39470</v>
@@ -20350,7 +20350,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496105194092</v>
+        <v>16.1496124267578</v>
       </c>
       <c r="H689" t="n">
         <v>60094</v>
@@ -20553,7 +20553,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843156814575</v>
+        <v>15.6843166351318</v>
       </c>
       <c r="H696" t="n">
         <v>33104</v>
@@ -20582,7 +20582,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975763320923</v>
+        <v>15.8975772857666</v>
       </c>
       <c r="H697" t="n">
         <v>154495</v>
@@ -20611,7 +20611,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H698" t="n">
         <v>76799</v>
@@ -20640,7 +20640,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H699" t="n">
         <v>43123</v>
@@ -20727,7 +20727,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H702" t="n">
         <v>27978</v>
@@ -20843,7 +20843,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H706" t="n">
         <v>80940</v>
@@ -20872,7 +20872,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H707" t="n">
         <v>82998</v>
@@ -20988,7 +20988,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H711" t="n">
         <v>31373</v>
@@ -21046,7 +21046,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H713" t="n">
         <v>58117</v>
@@ -21191,7 +21191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H718" t="n">
         <v>55322</v>
@@ -21249,7 +21249,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833110809326</v>
+        <v>15.0833101272583</v>
       </c>
       <c r="H720" t="n">
         <v>39360</v>
@@ -21278,7 +21278,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H721" t="n">
         <v>65632</v>
@@ -21307,7 +21307,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506631851196</v>
+        <v>14.8506622314453</v>
       </c>
       <c r="H722" t="n">
         <v>53763</v>
@@ -21394,7 +21394,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078184127808</v>
+        <v>14.3078193664551</v>
       </c>
       <c r="H725" t="n">
         <v>86664</v>
@@ -21423,7 +21423,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823045730591</v>
+        <v>14.4823036193848</v>
       </c>
       <c r="H726" t="n">
         <v>87213</v>
@@ -21452,7 +21452,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H727" t="n">
         <v>73456</v>
@@ -21597,7 +21597,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H732" t="n">
         <v>67534</v>
@@ -21655,7 +21655,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H734" t="n">
         <v>45192</v>
@@ -21713,7 +21713,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H736" t="n">
         <v>101028</v>
@@ -21771,7 +21771,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965707778931</v>
+        <v>15.2965698242188</v>
       </c>
       <c r="H738" t="n">
         <v>284400</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H739" t="n">
         <v>99147</v>
@@ -21916,7 +21916,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486068725586</v>
+        <v>15.5486059188843</v>
       </c>
       <c r="H743" t="n">
         <v>51182</v>
@@ -22032,7 +22032,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H747" t="n">
         <v>39016</v>
@@ -22148,7 +22148,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H751" t="n">
         <v>131748</v>
@@ -22235,7 +22235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H754" t="n">
         <v>50268</v>
@@ -22264,7 +22264,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H755" t="n">
         <v>44022</v>
@@ -22438,7 +22438,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914949417114</v>
+        <v>14.1914958953857</v>
       </c>
       <c r="H761" t="n">
         <v>62425</v>
@@ -22496,7 +22496,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H763" t="n">
         <v>51431</v>
@@ -22525,7 +22525,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H764" t="n">
         <v>67676</v>
@@ -22583,7 +22583,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.2108821868896</v>
+        <v>14.210883140564</v>
       </c>
       <c r="H766" t="n">
         <v>97709</v>
@@ -22612,7 +22612,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H767" t="n">
         <v>48972</v>
@@ -22641,7 +22641,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976215362549</v>
+        <v>13.9976224899292</v>
       </c>
       <c r="H768" t="n">
         <v>48388</v>
@@ -22670,7 +22670,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H769" t="n">
         <v>43039</v>
@@ -22728,7 +22728,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H771" t="n">
         <v>91611</v>
@@ -22757,7 +22757,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H772" t="n">
         <v>59694</v>
@@ -22815,7 +22815,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H774" t="n">
         <v>46705</v>
@@ -22931,7 +22931,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H778" t="n">
         <v>54214</v>
@@ -22960,7 +22960,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.163969039917</v>
+        <v>13.1639680862427</v>
       </c>
       <c r="H779" t="n">
         <v>31292</v>
@@ -23047,7 +23047,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H782" t="n">
         <v>29208</v>
@@ -23076,7 +23076,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H783" t="n">
         <v>48982</v>
@@ -23105,7 +23105,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H784" t="n">
         <v>44891</v>
@@ -23192,7 +23192,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H787" t="n">
         <v>75458</v>
@@ -23221,7 +23221,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.9200735092163</v>
+        <v>13.920072555542</v>
       </c>
       <c r="H788" t="n">
         <v>161892</v>
@@ -23453,7 +23453,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H796" t="n">
         <v>130807</v>
@@ -23511,7 +23511,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H798" t="n">
         <v>24558</v>
@@ -23598,7 +23598,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H801" t="n">
         <v>52319</v>
@@ -23627,7 +23627,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H802" t="n">
         <v>34321</v>
@@ -23772,7 +23772,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H807" t="n">
         <v>77476</v>
@@ -23859,7 +23859,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H810" t="n">
         <v>292244</v>
@@ -23888,7 +23888,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210781097412</v>
+        <v>14.5210790634155</v>
       </c>
       <c r="H811" t="n">
         <v>260837</v>
@@ -23917,7 +23917,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751714706421</v>
+        <v>14.0751724243164</v>
       </c>
       <c r="H812" t="n">
         <v>95170</v>
@@ -24062,7 +24062,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098756790161</v>
+        <v>13.6098766326904</v>
       </c>
       <c r="H817" t="n">
         <v>77436</v>
@@ -24236,7 +24236,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H823" t="n">
         <v>139568</v>
@@ -24294,7 +24294,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H825" t="n">
         <v>40244</v>
@@ -24323,7 +24323,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H826" t="n">
         <v>46870</v>
@@ -24352,7 +24352,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H827" t="n">
         <v>35005</v>
@@ -24381,7 +24381,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H828" t="n">
         <v>44484</v>
@@ -24584,7 +24584,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H835" t="n">
         <v>51758</v>
@@ -24961,7 +24961,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H848" t="n">
         <v>65992</v>
@@ -24990,7 +24990,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.349702835083</v>
+        <v>12.3497018814087</v>
       </c>
       <c r="H849" t="n">
         <v>101683</v>
@@ -25193,7 +25193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.5241889953613</v>
+        <v>12.524188041687</v>
       </c>
       <c r="H856" t="n">
         <v>89742</v>
@@ -25425,7 +25425,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017370223999</v>
+        <v>12.6017379760742</v>
       </c>
       <c r="H864" t="n">
         <v>23829</v>
@@ -25454,7 +25454,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H865" t="n">
         <v>77981</v>
@@ -25512,7 +25512,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037952423096</v>
+        <v>11.9037942886353</v>
       </c>
       <c r="H867" t="n">
         <v>165052</v>
@@ -25570,7 +25570,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.5354356765747</v>
+        <v>11.535436630249</v>
       </c>
       <c r="H869" t="n">
         <v>221362</v>
@@ -25657,7 +25657,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262462615967</v>
+        <v>11.8262453079224</v>
       </c>
       <c r="H872" t="n">
         <v>56333</v>
@@ -25715,7 +25715,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129846572876</v>
+        <v>11.6129856109619</v>
       </c>
       <c r="H874" t="n">
         <v>58043</v>
@@ -25773,7 +25773,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905355453491</v>
+        <v>11.6905345916748</v>
       </c>
       <c r="H876" t="n">
         <v>76554</v>
@@ -25802,7 +25802,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201187133789</v>
+        <v>12.0201177597046</v>
       </c>
       <c r="H877" t="n">
         <v>82169</v>
@@ -25831,7 +25831,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558303833008</v>
+        <v>12.1558294296265</v>
       </c>
       <c r="H878" t="n">
         <v>210169</v>
@@ -25976,7 +25976,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H883" t="n">
         <v>63353</v>
@@ -36799,6 +36799,35 @@
         <v>66169</v>
       </c>
       <c r="I1256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1257" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>12.2399997711182</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>44692</v>
+      </c>
+      <c r="I1257" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387083053589</v>
+        <v>15.4387092590332</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -485,7 +485,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873487472534</v>
+        <v>15.2873497009277</v>
       </c>
       <c r="H4" t="n">
         <v>131763</v>
@@ -514,7 +514,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1927480697632</v>
+        <v>15.1927490234375</v>
       </c>
       <c r="H5" t="n">
         <v>64538</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846286773682</v>
+        <v>14.9846296310425</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -630,7 +630,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>14.8332691192627</v>
+        <v>14.833270072937</v>
       </c>
       <c r="H9" t="n">
         <v>13899</v>
@@ -688,7 +688,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711090087891</v>
+        <v>14.8711099624634</v>
       </c>
       <c r="H11" t="n">
         <v>77954</v>
@@ -746,7 +746,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>14.379189491272</v>
+        <v>14.3791885375977</v>
       </c>
       <c r="H13" t="n">
         <v>27473</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548683166504</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -920,7 +920,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>14.379189491272</v>
+        <v>14.3791885375977</v>
       </c>
       <c r="H19" t="n">
         <v>20715</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.246750831604</v>
+        <v>14.2467498779297</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1094,7 +1094,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H25" t="n">
         <v>54159</v>
@@ -1123,7 +1123,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.171070098877</v>
+        <v>14.1710691452026</v>
       </c>
       <c r="H26" t="n">
         <v>81706</v>
@@ -1297,7 +1297,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.6223888397217</v>
+        <v>13.622389793396</v>
       </c>
       <c r="H32" t="n">
         <v>22783</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1413,7 +1413,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H36" t="n">
         <v>8817</v>
@@ -1442,7 +1442,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H37" t="n">
         <v>21560</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1558,7 +1558,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H41" t="n">
         <v>36059</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115104675293</v>
+        <v>12.411509513855</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007108688354</v>
+        <v>12.6007099151611</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1645,7 +1645,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H44" t="n">
         <v>70236</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034309387207</v>
+        <v>12.9034299850464</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1761,7 +1761,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466701507568</v>
+        <v>12.8466711044312</v>
       </c>
       <c r="H48" t="n">
         <v>83814</v>
@@ -1848,7 +1848,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.279070854187</v>
+        <v>12.2790699005127</v>
       </c>
       <c r="H51" t="n">
         <v>54490</v>
@@ -1935,7 +1935,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H54" t="n">
         <v>41198</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357927322388</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -2051,7 +2051,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H58" t="n">
         <v>38827</v>
@@ -2080,7 +2080,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H59" t="n">
         <v>23840</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2370,7 +2370,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H69" t="n">
         <v>21775</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2515,7 +2515,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952716827393</v>
+        <v>11.9952707290649</v>
       </c>
       <c r="H74" t="n">
         <v>37444</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006311416626</v>
+        <v>11.2006320953369</v>
       </c>
       <c r="H79" t="n">
         <v>30466</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763118743896</v>
+        <v>11.276312828064</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2921,7 +2921,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736307144165</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="n">
         <v>118173</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -3066,7 +3066,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H93" t="n">
         <v>15977</v>
@@ -3095,7 +3095,7 @@
         <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>11.3519916534424</v>
+        <v>11.3519926071167</v>
       </c>
       <c r="H94" t="n">
         <v>17943</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3327,7 +3327,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H102" t="n">
         <v>39681</v>
@@ -3356,7 +3356,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H103" t="n">
         <v>112096</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357927322388</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3443,7 +3443,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H106" t="n">
         <v>19298</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3675,7 +3675,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H114" t="n">
         <v>96370</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115104675293</v>
+        <v>12.411509513855</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884923934937</v>
+        <v>11.5884914398193</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4081,7 +4081,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H128" t="n">
         <v>17714</v>
@@ -4110,7 +4110,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H129" t="n">
         <v>100100</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4197,7 +4197,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195510864258</v>
+        <v>11.2195520401001</v>
       </c>
       <c r="H132" t="n">
         <v>26501</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979518890381</v>
+        <v>11.5979509353638</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4487,7 +4487,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H142" t="n">
         <v>15956</v>
@@ -4574,7 +4574,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979917526245</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="n">
         <v>14891</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4922,7 +4922,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="n">
         <v>25916</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -5038,7 +5038,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277112960815</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H161" t="n">
         <v>34152</v>
@@ -5067,7 +5067,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H162" t="n">
         <v>39212</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.8628301620483</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5125,7 +5125,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912115097046</v>
+        <v>11.8912105560303</v>
       </c>
       <c r="H164" t="n">
         <v>18357</v>
@@ -5183,7 +5183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H166" t="n">
         <v>9153</v>
@@ -5212,7 +5212,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966108322144</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H167" t="n">
         <v>6760</v>
@@ -5270,7 +5270,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>12.3452911376953</v>
+        <v>12.345290184021</v>
       </c>
       <c r="H169" t="n">
         <v>14062</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5386,7 +5386,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H173" t="n">
         <v>21249</v>
@@ -5415,7 +5415,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H174" t="n">
         <v>9566</v>
@@ -5444,7 +5444,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H175" t="n">
         <v>13252</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925905227661</v>
+        <v>12.3925914764404</v>
       </c>
       <c r="H181" t="n">
         <v>37878</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5937,7 +5937,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H192" t="n">
         <v>9607</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6053,7 +6053,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H196" t="n">
         <v>5717</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6140,7 +6140,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.6263313293457</v>
+        <v>11.6263303756714</v>
       </c>
       <c r="H199" t="n">
         <v>12593</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695705413818</v>
+        <v>11.5695714950562</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6198,7 +6198,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209320068359</v>
+        <v>11.7209310531616</v>
       </c>
       <c r="H201" t="n">
         <v>4105</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6285,7 +6285,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776918411255</v>
+        <v>11.7776908874512</v>
       </c>
       <c r="H204" t="n">
         <v>5041</v>
@@ -6343,7 +6343,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H206" t="n">
         <v>17437</v>
@@ -6372,7 +6372,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H207" t="n">
         <v>15879</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6459,7 +6459,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749708175659</v>
+        <v>11.4749717712402</v>
       </c>
       <c r="H210" t="n">
         <v>12812</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6575,7 +6575,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371309280396</v>
+        <v>11.4371328353882</v>
       </c>
       <c r="H214" t="n">
         <v>46989</v>
@@ -6662,7 +6662,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871114730835</v>
+        <v>11.0871124267578</v>
       </c>
       <c r="H217" t="n">
         <v>62592</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208902359009</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208902359009</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6865,7 +6865,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830123901367</v>
+        <v>10.2830114364624</v>
       </c>
       <c r="H224" t="n">
         <v>15661</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316528320312</v>
+        <v>10.1316537857056</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -6952,7 +6952,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H227" t="n">
         <v>62780</v>
@@ -7010,7 +7010,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947231292725</v>
+        <v>9.81947326660156</v>
       </c>
       <c r="H229" t="n">
         <v>68277</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275926589966</v>
+        <v>10.0275936126709</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0370512008667</v>
+        <v>10.037052154541</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083377838135</v>
+        <v>9.97083187103271</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055141448975</v>
+        <v>9.80055236816406</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7242,7 +7242,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>9.79109287261963</v>
+        <v>9.79109382629395</v>
       </c>
       <c r="H237" t="n">
         <v>7777</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7300,7 +7300,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="n">
         <v>10095</v>
@@ -7387,7 +7387,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>9.98029232025146</v>
+        <v>9.98029327392578</v>
       </c>
       <c r="H242" t="n">
         <v>3631</v>
@@ -7503,7 +7503,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789522171021</v>
+        <v>10.1789531707764</v>
       </c>
       <c r="H246" t="n">
         <v>25506</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621269226074</v>
+        <v>9.52621364593506</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7706,7 +7706,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G253" t="n">
-        <v>9.28971385955811</v>
+        <v>9.28971290588379</v>
       </c>
       <c r="H253" t="n">
         <v>10943</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7938,7 +7938,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668514251709</v>
+        <v>11.2668523788452</v>
       </c>
       <c r="H261" t="n">
         <v>11841</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -7996,7 +7996,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290115356445</v>
+        <v>11.2290124893188</v>
       </c>
       <c r="H263" t="n">
         <v>3066</v>
@@ -8025,7 +8025,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>11.0681915283203</v>
+        <v>11.0681924819946</v>
       </c>
       <c r="H264" t="n">
         <v>14049</v>
@@ -8054,7 +8054,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>11.1533317565918</v>
+        <v>11.1533327102661</v>
       </c>
       <c r="H265" t="n">
         <v>1992</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8228,7 +8228,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H271" t="n">
         <v>119668</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439121246338</v>
+        <v>11.8439102172852</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8373,7 +8373,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2479314804077</v>
+        <v>11.247932434082</v>
       </c>
       <c r="H276" t="n">
         <v>32729</v>
@@ -8402,7 +8402,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H277" t="n">
         <v>39974</v>
@@ -8489,7 +8489,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046913146973</v>
+        <v>11.3046922683716</v>
       </c>
       <c r="H280" t="n">
         <v>3490</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465913772583</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8605,7 +8605,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966108322144</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H284" t="n">
         <v>13107</v>
@@ -8634,7 +8634,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H285" t="n">
         <v>8932</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101314544678</v>
+        <v>11.9101305007935</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8692,7 +8692,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993318557739</v>
+        <v>12.0993309020996</v>
       </c>
       <c r="H287" t="n">
         <v>7503</v>
@@ -8721,7 +8721,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H288" t="n">
         <v>5961</v>
@@ -8779,7 +8779,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H290" t="n">
         <v>11428</v>
@@ -8953,7 +8953,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="n">
         <v>113027</v>
@@ -8982,7 +8982,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H297" t="n">
         <v>1507</v>
@@ -9040,7 +9040,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H299" t="n">
         <v>6219</v>
@@ -9069,7 +9069,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H300" t="n">
         <v>23263</v>
@@ -9098,7 +9098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.9006719589233</v>
+        <v>11.900671005249</v>
       </c>
       <c r="H301" t="n">
         <v>4323</v>
@@ -9127,7 +9127,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249921798706</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H302" t="n">
         <v>35060</v>
@@ -9243,7 +9243,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858102798462</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H306" t="n">
         <v>22411</v>
@@ -9388,7 +9388,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H311" t="n">
         <v>118963</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H312" t="n">
         <v>60848</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9475,7 +9475,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>12.5534114837646</v>
+        <v>12.5534105300903</v>
       </c>
       <c r="H314" t="n">
         <v>97891</v>
@@ -9504,7 +9504,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H315" t="n">
         <v>31712</v>
@@ -9562,7 +9562,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G317" t="n">
-        <v>13.0642509460449</v>
+        <v>13.0642518997192</v>
       </c>
       <c r="H317" t="n">
         <v>729414</v>
@@ -9591,7 +9591,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H318" t="n">
         <v>114421</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182897567749</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9736,7 +9736,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872291564941</v>
+        <v>13.1872301101685</v>
       </c>
       <c r="H323" t="n">
         <v>10973</v>
@@ -9794,7 +9794,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H325" t="n">
         <v>89076</v>
@@ -9881,7 +9881,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804906845093</v>
       </c>
       <c r="H328" t="n">
         <v>127967</v>
@@ -9910,7 +9910,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385906219482</v>
+        <v>13.3385896682739</v>
       </c>
       <c r="H329" t="n">
         <v>198840</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467100143433</v>
+        <v>13.5467090606689</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088312149048</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439519882202</v>
+        <v>12.5439510345459</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10229,7 +10229,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.799370765686</v>
+        <v>12.7993698120117</v>
       </c>
       <c r="H340" t="n">
         <v>39580</v>
@@ -10258,7 +10258,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372097015381</v>
+        <v>12.8372106552124</v>
       </c>
       <c r="H341" t="n">
         <v>71543</v>
@@ -10345,7 +10345,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>12.7804508209229</v>
+        <v>12.7804498672485</v>
       </c>
       <c r="H344" t="n">
         <v>37993</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088701248169</v>
+        <v>13.5088691711426</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10403,7 +10403,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.7642908096313</v>
+        <v>13.764289855957</v>
       </c>
       <c r="H346" t="n">
         <v>87295</v>
@@ -10577,7 +10577,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.726450920105</v>
+        <v>13.7264499664307</v>
       </c>
       <c r="H352" t="n">
         <v>43550</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548303604126</v>
+        <v>13.7548294067383</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10635,7 +10635,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H354" t="n">
         <v>47384</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10780,7 +10780,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628709793091</v>
+        <v>12.5628700256348</v>
       </c>
       <c r="H359" t="n">
         <v>54126</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764295578003</v>
+        <v>13.3764305114746</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10867,7 +10867,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737512588501</v>
+        <v>13.7737503051758</v>
       </c>
       <c r="H362" t="n">
         <v>69104</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -10983,7 +10983,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278289794922</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H366" t="n">
         <v>130359</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548683166504</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11041,7 +11041,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684278488159</v>
+        <v>15.2684288024902</v>
       </c>
       <c r="H368" t="n">
         <v>206675</v>
@@ -11099,7 +11099,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H370" t="n">
         <v>87340</v>
@@ -11157,7 +11157,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765491485596</v>
+        <v>15.4765501022339</v>
       </c>
       <c r="H372" t="n">
         <v>24974</v>
@@ -11186,7 +11186,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H373" t="n">
         <v>58745</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.722508430481</v>
+        <v>15.7225103378296</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11244,7 +11244,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H375" t="n">
         <v>73481</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792293548584</v>
+        <v>15.0792284011841</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11563,7 +11563,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990909576416</v>
+        <v>15.1990919113159</v>
       </c>
       <c r="H386" t="n">
         <v>145295</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020149230957</v>
+        <v>14.7020139694214</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.0079078674316</v>
+        <v>15.007908821106</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12085,7 +12085,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H404" t="n">
         <v>39114</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12230,7 +12230,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G409" t="n">
-        <v>14.3578834533691</v>
+        <v>14.3578844070435</v>
       </c>
       <c r="H409" t="n">
         <v>107726</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064224243164</v>
+        <v>14.6064233779907</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299491882324</v>
+        <v>14.5299482345581</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12491,7 +12491,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4917125701904</v>
+        <v>14.4917116165161</v>
       </c>
       <c r="H418" t="n">
         <v>21147</v>
@@ -12520,7 +12520,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211332321167</v>
+        <v>14.7211322784424</v>
       </c>
       <c r="H419" t="n">
         <v>25706</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12694,7 +12694,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H425" t="n">
         <v>125301</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12752,7 +12752,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G427" t="n">
-        <v>15.2373285293579</v>
+        <v>15.2373275756836</v>
       </c>
       <c r="H427" t="n">
         <v>44358</v>
@@ -12781,7 +12781,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520374298096</v>
+        <v>15.3520383834839</v>
       </c>
       <c r="H428" t="n">
         <v>49360</v>
@@ -12868,7 +12868,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H431" t="n">
         <v>30989</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314336776733</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13042,7 +13042,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9696712493896</v>
+        <v>14.9696702957153</v>
       </c>
       <c r="H437" t="n">
         <v>13330</v>
@@ -13100,7 +13100,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417360305786</v>
+        <v>15.1417369842529</v>
       </c>
       <c r="H439" t="n">
         <v>30668</v>
@@ -13129,7 +13129,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H440" t="n">
         <v>20791</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902759552002</v>
+        <v>15.3902750015259</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13187,7 +13187,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G442" t="n">
-        <v>15.2373285293579</v>
+        <v>15.2373275756836</v>
       </c>
       <c r="H442" t="n">
         <v>36186</v>
@@ -13303,7 +13303,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H446" t="n">
         <v>27084</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563980102539</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>14.0902271270752</v>
+        <v>14.0902261734009</v>
       </c>
       <c r="H448" t="n">
         <v>21910</v>
@@ -13448,7 +13448,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H451" t="n">
         <v>24187</v>
@@ -13506,7 +13506,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G453" t="n">
-        <v>13.68874168396</v>
+        <v>13.6887407302856</v>
       </c>
       <c r="H453" t="n">
         <v>37597</v>
@@ -13535,7 +13535,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G454" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H454" t="n">
         <v>51758</v>
@@ -13738,7 +13738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H461" t="n">
         <v>47646</v>
@@ -13767,7 +13767,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H462" t="n">
         <v>24475</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034046173096</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13941,7 +13941,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H468" t="n">
         <v>37228</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14115,7 +14115,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H474" t="n">
         <v>62001</v>
@@ -14144,7 +14144,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H475" t="n">
         <v>61238</v>
@@ -14173,7 +14173,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H476" t="n">
         <v>68346</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.273983001709</v>
+        <v>12.2739839553833</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14463,7 +14463,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H486" t="n">
         <v>45367</v>
@@ -14492,7 +14492,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.2931022644043</v>
+        <v>12.29310131073</v>
       </c>
       <c r="H487" t="n">
         <v>28990</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181144714355</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14550,7 +14550,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>12.082799911499</v>
+        <v>12.0828008651733</v>
       </c>
       <c r="H489" t="n">
         <v>48158</v>
@@ -14579,7 +14579,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>12.10191822052</v>
+        <v>12.1019172668457</v>
       </c>
       <c r="H490" t="n">
         <v>55351</v>
@@ -14637,7 +14637,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>11.7769069671631</v>
+        <v>11.7769060134888</v>
       </c>
       <c r="H492" t="n">
         <v>22268</v>
@@ -14724,7 +14724,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>12.044563293457</v>
+        <v>12.0445642471313</v>
       </c>
       <c r="H495" t="n">
         <v>11804</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960243225098</v>
+        <v>11.7960252761841</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.5225219726562</v>
+        <v>12.5225229263306</v>
       </c>
       <c r="H500" t="n">
         <v>76184</v>
@@ -14898,7 +14898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H501" t="n">
         <v>67973</v>
@@ -14956,7 +14956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H503" t="n">
         <v>36066</v>
@@ -15014,7 +15014,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G505" t="n">
-        <v>12.8857698440552</v>
+        <v>12.8857707977295</v>
       </c>
       <c r="H505" t="n">
         <v>58282</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15072,7 +15072,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H507" t="n">
         <v>55125</v>
@@ -15246,7 +15246,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9813623428345</v>
+        <v>12.9813632965088</v>
       </c>
       <c r="H513" t="n">
         <v>115376</v>
@@ -15304,7 +15304,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G515" t="n">
-        <v>13.2107830047607</v>
+        <v>13.2107820510864</v>
       </c>
       <c r="H515" t="n">
         <v>37142</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299003601074</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15594,7 +15594,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G525" t="n">
-        <v>13.612268447876</v>
+        <v>13.6122674942017</v>
       </c>
       <c r="H525" t="n">
         <v>28328</v>
@@ -15623,7 +15623,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H526" t="n">
         <v>18896</v>
@@ -15855,7 +15855,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G534" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H534" t="n">
         <v>25283</v>
@@ -15884,7 +15884,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H535" t="n">
         <v>118515</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16174,7 +16174,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G545" t="n">
-        <v>13.68874168396</v>
+        <v>13.6887407302856</v>
       </c>
       <c r="H545" t="n">
         <v>37826</v>
@@ -16290,7 +16290,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>13.650505065918</v>
+        <v>13.6505041122437</v>
       </c>
       <c r="H549" t="n">
         <v>19079</v>
@@ -16319,7 +16319,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H550" t="n">
         <v>10006</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416872024536</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16435,7 +16435,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H554" t="n">
         <v>25672</v>
@@ -16493,7 +16493,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H556" t="n">
         <v>13812</v>
@@ -16551,7 +16551,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H558" t="n">
         <v>27948</v>
@@ -16725,7 +16725,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H564" t="n">
         <v>58797</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16957,7 +16957,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G572" t="n">
-        <v>13.5549125671387</v>
+        <v>13.554913520813</v>
       </c>
       <c r="H572" t="n">
         <v>33579</v>
@@ -16986,7 +16986,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H573" t="n">
         <v>66012</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17160,7 +17160,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005285263062</v>
+        <v>14.3005294799805</v>
       </c>
       <c r="H579" t="n">
         <v>77910</v>
@@ -17334,7 +17334,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H585" t="n">
         <v>62831</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17450,7 +17450,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G589" t="n">
-        <v>13.612268447876</v>
+        <v>13.6122674942017</v>
       </c>
       <c r="H589" t="n">
         <v>1148601</v>
@@ -17508,7 +17508,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G591" t="n">
-        <v>13.650505065918</v>
+        <v>13.6505041122437</v>
       </c>
       <c r="H591" t="n">
         <v>64144</v>
@@ -17537,7 +17537,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H592" t="n">
         <v>66158</v>
@@ -17595,7 +17595,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G594" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H594" t="n">
         <v>74613</v>
@@ -17624,7 +17624,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G595" t="n">
-        <v>13.1343097686768</v>
+        <v>13.1343088150024</v>
       </c>
       <c r="H595" t="n">
         <v>46485</v>
@@ -17653,7 +17653,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G596" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H596" t="n">
         <v>44483</v>
@@ -17682,7 +17682,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G597" t="n">
-        <v>13.0195999145508</v>
+        <v>13.0195989608765</v>
       </c>
       <c r="H597" t="n">
         <v>36061</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137050628662</v>
+        <v>12.7137060165405</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17769,7 +17769,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>12.9240074157715</v>
+        <v>12.9240083694458</v>
       </c>
       <c r="H600" t="n">
         <v>34751</v>
@@ -17798,7 +17798,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H601" t="n">
         <v>36560</v>
@@ -17827,7 +17827,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H602" t="n">
         <v>51879</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17972,7 +17972,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H607" t="n">
         <v>33493</v>
@@ -18175,7 +18175,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H614" t="n">
         <v>147836</v>
@@ -18233,7 +18233,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H616" t="n">
         <v>69661</v>
@@ -18291,7 +18291,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G618" t="n">
-        <v>13.1151905059814</v>
+        <v>13.1151914596558</v>
       </c>
       <c r="H618" t="n">
         <v>52967</v>
@@ -18320,7 +18320,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G619" t="n">
-        <v>13.1343097686768</v>
+        <v>13.1343088150024</v>
       </c>
       <c r="H619" t="n">
         <v>185777</v>
@@ -18523,7 +18523,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G626" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H626" t="n">
         <v>25180</v>
@@ -18552,7 +18552,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G627" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H627" t="n">
         <v>64899</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18610,7 +18610,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G629" t="n">
-        <v>12.5416402816772</v>
+        <v>12.5416393280029</v>
       </c>
       <c r="H629" t="n">
         <v>54542</v>
@@ -18639,7 +18639,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G630" t="n">
-        <v>12.5607595443726</v>
+        <v>12.5607585906982</v>
       </c>
       <c r="H630" t="n">
         <v>50458</v>
@@ -18697,7 +18697,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>12.8857698440552</v>
+        <v>12.8857707977295</v>
       </c>
       <c r="H632" t="n">
         <v>24374</v>
@@ -18784,7 +18784,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H635" t="n">
         <v>124717</v>
@@ -18871,7 +18871,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H638" t="n">
         <v>21080</v>
@@ -18900,7 +18900,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H639" t="n">
         <v>40704</v>
@@ -18929,7 +18929,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H640" t="n">
         <v>101641</v>
@@ -18958,7 +18958,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047555923462</v>
+        <v>14.4047546386719</v>
       </c>
       <c r="H641" t="n">
         <v>104803</v>
@@ -19045,7 +19045,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H644" t="n">
         <v>37693</v>
@@ -19132,7 +19132,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H647" t="n">
         <v>62394</v>
@@ -19306,7 +19306,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H653" t="n">
         <v>67181</v>
@@ -19480,7 +19480,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H659" t="n">
         <v>65476</v>
@@ -19538,7 +19538,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H661" t="n">
         <v>35343</v>
@@ -19625,7 +19625,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H664" t="n">
         <v>45922</v>
@@ -19654,7 +19654,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751253128052</v>
+        <v>15.9751262664795</v>
       </c>
       <c r="H665" t="n">
         <v>60499</v>
@@ -19683,7 +19683,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108379364014</v>
+        <v>16.1108360290527</v>
       </c>
       <c r="H666" t="n">
         <v>28199</v>
@@ -19770,7 +19770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H669" t="n">
         <v>107477</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761779785156</v>
+        <v>14.6761770248413</v>
       </c>
       <c r="H672" t="n">
         <v>131068</v>
@@ -19944,7 +19944,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H675" t="n">
         <v>84935</v>
@@ -20002,7 +20002,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H677" t="n">
         <v>28484</v>
@@ -20031,7 +20031,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H678" t="n">
         <v>45965</v>
@@ -20089,7 +20089,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H680" t="n">
         <v>49932</v>
@@ -20205,7 +20205,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H684" t="n">
         <v>33213</v>
@@ -20263,7 +20263,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H686" t="n">
         <v>149634</v>
@@ -20292,7 +20292,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H687" t="n">
         <v>39470</v>
@@ -20350,7 +20350,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496124267578</v>
+        <v>16.1496105194092</v>
       </c>
       <c r="H689" t="n">
         <v>60094</v>
@@ -20553,7 +20553,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843166351318</v>
+        <v>15.6843156814575</v>
       </c>
       <c r="H696" t="n">
         <v>33104</v>
@@ -20582,7 +20582,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975772857666</v>
+        <v>15.8975763320923</v>
       </c>
       <c r="H697" t="n">
         <v>154495</v>
@@ -20611,7 +20611,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H698" t="n">
         <v>76799</v>
@@ -20640,7 +20640,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H699" t="n">
         <v>43123</v>
@@ -20727,7 +20727,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H702" t="n">
         <v>27978</v>
@@ -20843,7 +20843,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H706" t="n">
         <v>80940</v>
@@ -20872,7 +20872,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H707" t="n">
         <v>82998</v>
@@ -20988,7 +20988,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H711" t="n">
         <v>31373</v>
@@ -21046,7 +21046,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H713" t="n">
         <v>58117</v>
@@ -21191,7 +21191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H718" t="n">
         <v>55322</v>
@@ -21249,7 +21249,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833101272583</v>
+        <v>15.0833110809326</v>
       </c>
       <c r="H720" t="n">
         <v>39360</v>
@@ -21278,7 +21278,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H721" t="n">
         <v>65632</v>
@@ -21307,7 +21307,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506622314453</v>
+        <v>14.8506631851196</v>
       </c>
       <c r="H722" t="n">
         <v>53763</v>
@@ -21394,7 +21394,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078193664551</v>
+        <v>14.3078184127808</v>
       </c>
       <c r="H725" t="n">
         <v>86664</v>
@@ -21423,7 +21423,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823036193848</v>
+        <v>14.4823045730591</v>
       </c>
       <c r="H726" t="n">
         <v>87213</v>
@@ -21452,7 +21452,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H727" t="n">
         <v>73456</v>
@@ -21597,7 +21597,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H732" t="n">
         <v>67534</v>
@@ -21655,7 +21655,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H734" t="n">
         <v>45192</v>
@@ -21713,7 +21713,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H736" t="n">
         <v>101028</v>
@@ -21771,7 +21771,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965698242188</v>
+        <v>15.2965707778931</v>
       </c>
       <c r="H738" t="n">
         <v>284400</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H739" t="n">
         <v>99147</v>
@@ -21916,7 +21916,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486059188843</v>
+        <v>15.5486068725586</v>
       </c>
       <c r="H743" t="n">
         <v>51182</v>
@@ -22032,7 +22032,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H747" t="n">
         <v>39016</v>
@@ -22148,7 +22148,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H751" t="n">
         <v>131748</v>
@@ -22235,7 +22235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H754" t="n">
         <v>50268</v>
@@ -22264,7 +22264,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H755" t="n">
         <v>44022</v>
@@ -22438,7 +22438,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914958953857</v>
+        <v>14.1914949417114</v>
       </c>
       <c r="H761" t="n">
         <v>62425</v>
@@ -22496,7 +22496,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H763" t="n">
         <v>51431</v>
@@ -22525,7 +22525,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H764" t="n">
         <v>67676</v>
@@ -22583,7 +22583,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.210883140564</v>
+        <v>14.2108821868896</v>
       </c>
       <c r="H766" t="n">
         <v>97709</v>
@@ -22612,7 +22612,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H767" t="n">
         <v>48972</v>
@@ -22641,7 +22641,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976224899292</v>
+        <v>13.9976215362549</v>
       </c>
       <c r="H768" t="n">
         <v>48388</v>
@@ -22670,7 +22670,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H769" t="n">
         <v>43039</v>
@@ -22728,7 +22728,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H771" t="n">
         <v>91611</v>
@@ -22757,7 +22757,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H772" t="n">
         <v>59694</v>
@@ -22815,7 +22815,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H774" t="n">
         <v>46705</v>
@@ -22931,7 +22931,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H778" t="n">
         <v>54214</v>
@@ -22960,7 +22960,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.1639680862427</v>
+        <v>13.163969039917</v>
       </c>
       <c r="H779" t="n">
         <v>31292</v>
@@ -23047,7 +23047,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H782" t="n">
         <v>29208</v>
@@ -23076,7 +23076,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H783" t="n">
         <v>48982</v>
@@ -23105,7 +23105,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H784" t="n">
         <v>44891</v>
@@ -23192,7 +23192,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H787" t="n">
         <v>75458</v>
@@ -23221,7 +23221,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.920072555542</v>
+        <v>13.9200735092163</v>
       </c>
       <c r="H788" t="n">
         <v>161892</v>
@@ -23453,7 +23453,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H796" t="n">
         <v>130807</v>
@@ -23511,7 +23511,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H798" t="n">
         <v>24558</v>
@@ -23598,7 +23598,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H801" t="n">
         <v>52319</v>
@@ -23627,7 +23627,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H802" t="n">
         <v>34321</v>
@@ -23772,7 +23772,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H807" t="n">
         <v>77476</v>
@@ -23859,7 +23859,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H810" t="n">
         <v>292244</v>
@@ -23888,7 +23888,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210790634155</v>
+        <v>14.5210781097412</v>
       </c>
       <c r="H811" t="n">
         <v>260837</v>
@@ -23917,7 +23917,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751724243164</v>
+        <v>14.0751714706421</v>
       </c>
       <c r="H812" t="n">
         <v>95170</v>
@@ -24062,7 +24062,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098766326904</v>
+        <v>13.6098756790161</v>
       </c>
       <c r="H817" t="n">
         <v>77436</v>
@@ -24236,7 +24236,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H823" t="n">
         <v>139568</v>
@@ -24294,7 +24294,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H825" t="n">
         <v>40244</v>
@@ -24323,7 +24323,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H826" t="n">
         <v>46870</v>
@@ -24352,7 +24352,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H827" t="n">
         <v>35005</v>
@@ -24381,7 +24381,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H828" t="n">
         <v>44484</v>
@@ -24584,7 +24584,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H835" t="n">
         <v>51758</v>
@@ -24961,7 +24961,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H848" t="n">
         <v>65992</v>
@@ -24990,7 +24990,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.3497018814087</v>
+        <v>12.349702835083</v>
       </c>
       <c r="H849" t="n">
         <v>101683</v>
@@ -25193,7 +25193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.524188041687</v>
+        <v>12.5241889953613</v>
       </c>
       <c r="H856" t="n">
         <v>89742</v>
@@ -25425,7 +25425,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017379760742</v>
+        <v>12.6017370223999</v>
       </c>
       <c r="H864" t="n">
         <v>23829</v>
@@ -25454,7 +25454,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H865" t="n">
         <v>77981</v>
@@ -25512,7 +25512,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037942886353</v>
+        <v>11.9037952423096</v>
       </c>
       <c r="H867" t="n">
         <v>165052</v>
@@ -25570,7 +25570,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.535436630249</v>
+        <v>11.5354356765747</v>
       </c>
       <c r="H869" t="n">
         <v>221362</v>
@@ -25657,7 +25657,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262453079224</v>
+        <v>11.8262462615967</v>
       </c>
       <c r="H872" t="n">
         <v>56333</v>
@@ -25715,7 +25715,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129856109619</v>
+        <v>11.6129846572876</v>
       </c>
       <c r="H874" t="n">
         <v>58043</v>
@@ -25773,7 +25773,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905345916748</v>
+        <v>11.6905355453491</v>
       </c>
       <c r="H876" t="n">
         <v>76554</v>
@@ -25802,7 +25802,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201177597046</v>
+        <v>12.0201187133789</v>
       </c>
       <c r="H877" t="n">
         <v>82169</v>
@@ -25831,7 +25831,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558294296265</v>
+        <v>12.1558303833008</v>
       </c>
       <c r="H878" t="n">
         <v>210169</v>
@@ -25976,7 +25976,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H883" t="n">
         <v>63353</v>
@@ -36828,6 +36828,35 @@
         <v>44692</v>
       </c>
       <c r="I1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1258" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>50911</v>
+      </c>
+      <c r="I1258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387092590332</v>
+        <v>15.4387073516846</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954292297363</v>
+        <v>14.7954301834106</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -514,7 +514,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1927490234375</v>
+        <v>15.1927480697632</v>
       </c>
       <c r="H5" t="n">
         <v>64538</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846296310425</v>
+        <v>14.9846286773682</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -601,7 +601,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H8" t="n">
         <v>69786</v>
@@ -659,7 +659,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008295059204</v>
+        <v>14.7008285522461</v>
       </c>
       <c r="H10" t="n">
         <v>75622</v>
@@ -717,7 +717,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197504043579</v>
+        <v>14.7197494506836</v>
       </c>
       <c r="H12" t="n">
         <v>31842</v>
@@ -746,7 +746,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>14.3791885375977</v>
+        <v>14.379189491272</v>
       </c>
       <c r="H13" t="n">
         <v>27473</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.454870223999</v>
+        <v>14.4548683166504</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -833,7 +833,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359502792358</v>
+        <v>14.4359493255615</v>
       </c>
       <c r="H16" t="n">
         <v>13170</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -920,7 +920,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>14.3791885375977</v>
+        <v>14.379189491272</v>
       </c>
       <c r="H19" t="n">
         <v>20715</v>
@@ -978,7 +978,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H21" t="n">
         <v>20677</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845907211304</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2467498779297</v>
+        <v>14.246750831604</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1123,7 +1123,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710691452026</v>
+        <v>14.1710681915283</v>
       </c>
       <c r="H26" t="n">
         <v>81706</v>
@@ -1152,7 +1152,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115901947021</v>
+        <v>13.8115911483765</v>
       </c>
       <c r="H27" t="n">
         <v>47594</v>
@@ -1297,7 +1297,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.622389793396</v>
+        <v>13.6223888397217</v>
       </c>
       <c r="H32" t="n">
         <v>22783</v>
@@ -1355,7 +1355,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H34" t="n">
         <v>28912</v>
@@ -1471,7 +1471,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H38" t="n">
         <v>18250</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547904968262</v>
+        <v>13.0547895431519</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.411509513855</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007099151611</v>
+        <v>12.6007108688354</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1645,7 +1645,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H44" t="n">
         <v>70236</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034299850464</v>
+        <v>12.903431892395</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1761,7 +1761,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>12.8466711044312</v>
+        <v>12.8466701507568</v>
       </c>
       <c r="H48" t="n">
         <v>83814</v>
@@ -1790,7 +1790,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H49" t="n">
         <v>62308</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.616870880127</v>
+        <v>11.6168718338013</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1935,7 +1935,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H54" t="n">
         <v>41198</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357917785645</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -1993,7 +1993,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H56" t="n">
         <v>71712</v>
@@ -2022,7 +2022,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H57" t="n">
         <v>59171</v>
@@ -2109,7 +2109,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H60" t="n">
         <v>20661</v>
@@ -2138,7 +2138,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358306884766</v>
+        <v>12.3358316421509</v>
       </c>
       <c r="H61" t="n">
         <v>27576</v>
@@ -2167,7 +2167,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H62" t="n">
         <v>17275</v>
@@ -2225,7 +2225,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H64" t="n">
         <v>59204</v>
@@ -2283,7 +2283,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H66" t="n">
         <v>68260</v>
@@ -2312,7 +2312,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H67" t="n">
         <v>16328</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2399,7 +2399,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H70" t="n">
         <v>77040</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2457,7 +2457,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H72" t="n">
         <v>14203</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006320953369</v>
+        <v>11.2006311416626</v>
       </c>
       <c r="H79" t="n">
         <v>30466</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.276312828064</v>
+        <v>11.2763118743896</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2834,7 +2834,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>10.9735918045044</v>
+        <v>10.9735927581787</v>
       </c>
       <c r="H85" t="n">
         <v>273384</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -3095,7 +3095,7 @@
         <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>11.3519926071167</v>
+        <v>11.3519916534424</v>
       </c>
       <c r="H94" t="n">
         <v>17943</v>
@@ -3153,7 +3153,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H96" t="n">
         <v>230549</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3211,7 +3211,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H98" t="n">
         <v>58338</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276714324951</v>
+        <v>11.4276723861694</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628301620483</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357917785645</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3501,7 +3501,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G108" t="n">
-        <v>11.5601110458374</v>
+        <v>11.5601119995117</v>
       </c>
       <c r="H108" t="n">
         <v>51913</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.5506505966187</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3559,7 +3559,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.834451675415</v>
+        <v>11.8344526290894</v>
       </c>
       <c r="H110" t="n">
         <v>21276</v>
@@ -3675,7 +3675,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H114" t="n">
         <v>96370</v>
@@ -3704,7 +3704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H115" t="n">
         <v>10754</v>
@@ -3733,7 +3733,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H116" t="n">
         <v>29281</v>
@@ -3762,7 +3762,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H117" t="n">
         <v>50078</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.411509513855</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3849,7 +3849,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H120" t="n">
         <v>18650</v>
@@ -4052,7 +4052,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H127" t="n">
         <v>53178</v>
@@ -4197,7 +4197,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195520401001</v>
+        <v>11.2195501327515</v>
       </c>
       <c r="H132" t="n">
         <v>26501</v>
@@ -4226,7 +4226,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168329238892</v>
+        <v>10.9168319702148</v>
       </c>
       <c r="H133" t="n">
         <v>53035</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979509353638</v>
+        <v>11.5979518890381</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4429,7 +4429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H140" t="n">
         <v>24892</v>
@@ -4545,7 +4545,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H144" t="n">
         <v>9829</v>
@@ -4603,7 +4603,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G146" t="n">
-        <v>12.5155696868896</v>
+        <v>12.515570640564</v>
       </c>
       <c r="H146" t="n">
         <v>29207</v>
@@ -4632,7 +4632,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H147" t="n">
         <v>23423</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4690,7 +4690,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H149" t="n">
         <v>57560</v>
@@ -4719,7 +4719,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H150" t="n">
         <v>63375</v>
@@ -4748,7 +4748,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614910125732</v>
+        <v>12.0614919662476</v>
       </c>
       <c r="H151" t="n">
         <v>41978</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4835,7 +4835,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899112701416</v>
+        <v>12.7899103164673</v>
       </c>
       <c r="H154" t="n">
         <v>1088974</v>
@@ -4864,7 +4864,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H155" t="n">
         <v>41701</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5009,7 +5009,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H160" t="n">
         <v>44574</v>
@@ -5067,7 +5067,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H162" t="n">
         <v>39212</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628301620483</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5154,7 +5154,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722915649414</v>
+        <v>11.8722906112671</v>
       </c>
       <c r="H165" t="n">
         <v>6548</v>
@@ -5241,7 +5241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H168" t="n">
         <v>17974</v>
@@ -5270,7 +5270,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>12.345290184021</v>
+        <v>12.3452911376953</v>
       </c>
       <c r="H169" t="n">
         <v>14062</v>
@@ -5386,7 +5386,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H173" t="n">
         <v>21249</v>
@@ -5444,7 +5444,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H175" t="n">
         <v>13252</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5531,7 +5531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223110198975</v>
+        <v>12.2223119735718</v>
       </c>
       <c r="H178" t="n">
         <v>16515</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.420970916748</v>
+        <v>12.4209699630737</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5734,7 +5734,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H185" t="n">
         <v>18304</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5792,7 +5792,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H187" t="n">
         <v>3679</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5850,7 +5850,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H189" t="n">
         <v>22438</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452512741089</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -6024,7 +6024,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H195" t="n">
         <v>9323</v>
@@ -6053,7 +6053,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H196" t="n">
         <v>5717</v>
@@ -6111,7 +6111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H198" t="n">
         <v>9999</v>
@@ -6198,7 +6198,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209310531616</v>
+        <v>11.7209320068359</v>
       </c>
       <c r="H201" t="n">
         <v>4105</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6372,7 +6372,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H207" t="n">
         <v>15879</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452512741089</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6575,7 +6575,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371328353882</v>
+        <v>11.4371318817139</v>
       </c>
       <c r="H214" t="n">
         <v>46989</v>
@@ -6604,7 +6604,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G215" t="n">
-        <v>11.5601110458374</v>
+        <v>11.5601119995117</v>
       </c>
       <c r="H215" t="n">
         <v>5494</v>
@@ -6691,7 +6691,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587320327759</v>
+        <v>11.0587310791016</v>
       </c>
       <c r="H218" t="n">
         <v>37998</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6778,7 +6778,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789930343628</v>
+        <v>10.8789920806885</v>
       </c>
       <c r="H221" t="n">
         <v>10402</v>
@@ -6807,7 +6807,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059925079346</v>
+        <v>10.4059915542603</v>
       </c>
       <c r="H222" t="n">
         <v>8716</v>
@@ -6865,7 +6865,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830114364624</v>
+        <v>10.2830123901367</v>
       </c>
       <c r="H224" t="n">
         <v>15661</v>
@@ -6894,7 +6894,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H225" t="n">
         <v>12232</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316537857056</v>
+        <v>10.1316518783569</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H228" t="n">
         <v>31580</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275936126709</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7184,7 +7184,7 @@
         <v>10.5</v>
       </c>
       <c r="G235" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H235" t="n">
         <v>4261</v>
@@ -7242,7 +7242,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>9.79109382629395</v>
+        <v>9.79109287261963</v>
       </c>
       <c r="H237" t="n">
         <v>7777</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7300,7 +7300,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.349232673645</v>
+        <v>10.3492317199707</v>
       </c>
       <c r="H239" t="n">
         <v>10095</v>
@@ -7358,7 +7358,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0086736679077</v>
+        <v>10.0086727142334</v>
       </c>
       <c r="H241" t="n">
         <v>11515</v>
@@ -7474,7 +7474,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H245" t="n">
         <v>17542</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167930603027</v>
+        <v>10.2167921066284</v>
       </c>
       <c r="H247" t="n">
         <v>2146</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621364593506</v>
+        <v>9.52621269226074</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729370117188</v>
+        <v>9.50729274749756</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7648,7 +7648,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647274017334</v>
+        <v>9.34647369384766</v>
       </c>
       <c r="H251" t="n">
         <v>15863</v>
@@ -7677,7 +7677,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701324462891</v>
+        <v>9.33701229095459</v>
       </c>
       <c r="H252" t="n">
         <v>8169</v>
@@ -7764,7 +7764,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.9613733291626</v>
+        <v>9.96137237548828</v>
       </c>
       <c r="H255" t="n">
         <v>77427</v>
@@ -7793,7 +7793,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884515762329</v>
+        <v>10.8884525299072</v>
       </c>
       <c r="H256" t="n">
         <v>68311</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7996,7 +7996,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290124893188</v>
+        <v>11.2290115356445</v>
       </c>
       <c r="H263" t="n">
         <v>3066</v>
@@ -8054,7 +8054,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>11.1533327102661</v>
+        <v>11.1533317565918</v>
       </c>
       <c r="H265" t="n">
         <v>1992</v>
@@ -8112,7 +8112,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H267" t="n">
         <v>6337</v>
@@ -8141,7 +8141,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H268" t="n">
         <v>7750</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8228,7 +8228,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H271" t="n">
         <v>119668</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439102172852</v>
+        <v>11.8439121246338</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8286,7 +8286,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H273" t="n">
         <v>9792</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H275" t="n">
         <v>6258</v>
@@ -8431,7 +8431,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G278" t="n">
-        <v>11.7020111083984</v>
+        <v>11.7020120620728</v>
       </c>
       <c r="H278" t="n">
         <v>6135</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992929458618</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8489,7 +8489,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046922683716</v>
+        <v>11.3046913146973</v>
       </c>
       <c r="H280" t="n">
         <v>3490</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465923309326</v>
+        <v>11.4465913772583</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8634,7 +8634,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H285" t="n">
         <v>8932</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101305007935</v>
+        <v>11.9101314544678</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8721,7 +8721,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155307769775</v>
+        <v>11.8155317306519</v>
       </c>
       <c r="H288" t="n">
         <v>5961</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8866,7 +8866,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885303497314</v>
+        <v>12.2885313034058</v>
       </c>
       <c r="H293" t="n">
         <v>19905</v>
@@ -8895,7 +8895,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H294" t="n">
         <v>39678</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750106811523</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -9011,7 +9011,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520305633545</v>
+        <v>12.0520315170288</v>
       </c>
       <c r="H298" t="n">
         <v>4631</v>
@@ -9069,7 +9069,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493114471436</v>
+        <v>11.7493104934692</v>
       </c>
       <c r="H300" t="n">
         <v>23263</v>
@@ -9127,7 +9127,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H302" t="n">
         <v>35060</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939306259155</v>
+        <v>12.1939315795898</v>
       </c>
       <c r="H304" t="n">
         <v>1793</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9359,7 +9359,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H310" t="n">
         <v>86708</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H312" t="n">
         <v>60848</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9475,7 +9475,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>12.5534105300903</v>
+        <v>12.5534114837646</v>
       </c>
       <c r="H314" t="n">
         <v>97891</v>
@@ -9504,7 +9504,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H315" t="n">
         <v>31712</v>
@@ -9533,7 +9533,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818307876587</v>
+        <v>13.2818298339844</v>
       </c>
       <c r="H316" t="n">
         <v>52099</v>
@@ -9562,7 +9562,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G317" t="n">
-        <v>13.0642518997192</v>
+        <v>13.0642509460449</v>
       </c>
       <c r="H317" t="n">
         <v>729414</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182897567749</v>
+        <v>12.8182907104492</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9707,7 +9707,7 @@
         <v>14</v>
       </c>
       <c r="G322" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H322" t="n">
         <v>121250</v>
@@ -9794,7 +9794,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H325" t="n">
         <v>89076</v>
@@ -9823,7 +9823,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075300216675</v>
+        <v>13.7075290679932</v>
       </c>
       <c r="H326" t="n">
         <v>108302</v>
@@ -9852,7 +9852,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669700622559</v>
+        <v>13.3669710159302</v>
       </c>
       <c r="H327" t="n">
         <v>36337</v>
@@ -9881,7 +9881,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.4804906845093</v>
+        <v>13.480489730835</v>
       </c>
       <c r="H328" t="n">
         <v>127967</v>
@@ -9910,7 +9910,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385896682739</v>
+        <v>13.3385906219482</v>
       </c>
       <c r="H329" t="n">
         <v>198840</v>
@@ -9939,7 +9939,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.6980695724487</v>
+        <v>13.698070526123</v>
       </c>
       <c r="H330" t="n">
         <v>268725</v>
@@ -9968,7 +9968,7 @@
         <v>14</v>
       </c>
       <c r="G331" t="n">
-        <v>13.243989944458</v>
+        <v>13.2439908981323</v>
       </c>
       <c r="H331" t="n">
         <v>50115</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467090606689</v>
+        <v>13.5467100143433</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10026,7 +10026,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912902832031</v>
+        <v>13.2912912368774</v>
       </c>
       <c r="H333" t="n">
         <v>23303</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088293075562</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10171,7 +10171,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142295837402</v>
+        <v>12.7142305374146</v>
       </c>
       <c r="H338" t="n">
         <v>27898</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439510345459</v>
+        <v>12.5439500808716</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10229,7 +10229,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.7993698120117</v>
+        <v>12.799370765686</v>
       </c>
       <c r="H340" t="n">
         <v>39580</v>
@@ -10316,7 +10316,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723304748535</v>
+        <v>12.5723314285278</v>
       </c>
       <c r="H343" t="n">
         <v>71453</v>
@@ -10345,7 +10345,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>12.7804498672485</v>
+        <v>12.7804508209229</v>
       </c>
       <c r="H344" t="n">
         <v>37993</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088691711426</v>
+        <v>13.5088701248169</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10548,7 +10548,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426498413086</v>
+        <v>13.4426488876343</v>
       </c>
       <c r="H351" t="n">
         <v>59237</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548294067383</v>
+        <v>13.7548303604126</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10635,7 +10635,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H354" t="n">
         <v>47384</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764305114746</v>
+        <v>13.3764295578003</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845907211304</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.454870223999</v>
+        <v>14.4548683166504</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11041,7 +11041,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684288024902</v>
+        <v>15.2684278488159</v>
       </c>
       <c r="H368" t="n">
         <v>206675</v>
@@ -11157,7 +11157,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765501022339</v>
+        <v>15.4765491485596</v>
       </c>
       <c r="H372" t="n">
         <v>24974</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225103378296</v>
+        <v>15.7225074768066</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792284011841</v>
+        <v>15.0792293548584</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927091598511</v>
+        <v>14.4927101135254</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11331,7 +11331,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H378" t="n">
         <v>85275</v>
@@ -11360,7 +11360,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549100875854</v>
+        <v>15.1549091339111</v>
       </c>
       <c r="H379" t="n">
         <v>175080</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11476,7 +11476,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H383" t="n">
         <v>42204</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11679,7 +11679,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843811035156</v>
+        <v>15.0843820571899</v>
       </c>
       <c r="H390" t="n">
         <v>50895</v>
@@ -11708,7 +11708,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H391" t="n">
         <v>32365</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020139694214</v>
+        <v>14.7020149230957</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.007908821106</v>
+        <v>15.0079078674316</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -11911,7 +11911,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.9505529403687</v>
+        <v>14.950553894043</v>
       </c>
       <c r="H398" t="n">
         <v>35897</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593688964844</v>
+        <v>14.7593698501587</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12201,7 +12201,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108308792114</v>
+        <v>14.5108318328857</v>
       </c>
       <c r="H408" t="n">
         <v>38004</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064233779907</v>
+        <v>14.6064224243164</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12346,7 +12346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H413" t="n">
         <v>34048</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12404,7 +12404,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H415" t="n">
         <v>18337</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299482345581</v>
+        <v>14.5299501419067</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12491,7 +12491,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4917116165161</v>
+        <v>14.4917125701904</v>
       </c>
       <c r="H418" t="n">
         <v>21147</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12752,7 +12752,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G427" t="n">
-        <v>15.2373275756836</v>
+        <v>15.2373285293579</v>
       </c>
       <c r="H427" t="n">
         <v>44358</v>
@@ -12897,7 +12897,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H432" t="n">
         <v>28274</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314336776733</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13042,7 +13042,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9696702957153</v>
+        <v>14.9696712493896</v>
       </c>
       <c r="H437" t="n">
         <v>13330</v>
@@ -13071,7 +13071,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H438" t="n">
         <v>18515</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902750015259</v>
+        <v>15.3902759552002</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13187,7 +13187,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G442" t="n">
-        <v>15.2373275756836</v>
+        <v>15.2373285293579</v>
       </c>
       <c r="H442" t="n">
         <v>36186</v>
@@ -13216,7 +13216,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H443" t="n">
         <v>45829</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563999176025</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>14.0902261734009</v>
+        <v>14.0902271270752</v>
       </c>
       <c r="H448" t="n">
         <v>21910</v>
@@ -13419,7 +13419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711088180542</v>
+        <v>14.0711097717285</v>
       </c>
       <c r="H450" t="n">
         <v>16818</v>
@@ -13506,7 +13506,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G453" t="n">
-        <v>13.6887407302856</v>
+        <v>13.68874168396</v>
       </c>
       <c r="H453" t="n">
         <v>37597</v>
@@ -13564,7 +13564,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H455" t="n">
         <v>15285</v>
@@ -13709,7 +13709,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431257247925</v>
+        <v>12.9431247711182</v>
       </c>
       <c r="H460" t="n">
         <v>31924</v>
@@ -13796,7 +13796,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H463" t="n">
         <v>22702</v>
@@ -13825,7 +13825,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H464" t="n">
         <v>16431</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034027099609</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14086,7 +14086,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G473" t="n">
-        <v>12.3886938095093</v>
+        <v>12.388692855835</v>
       </c>
       <c r="H473" t="n">
         <v>30946</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14289,7 +14289,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.9872074127197</v>
+        <v>11.987208366394</v>
       </c>
       <c r="H480" t="n">
         <v>47163</v>
@@ -14318,7 +14318,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.063681602478</v>
+        <v>12.0636806488037</v>
       </c>
       <c r="H481" t="n">
         <v>28977</v>
@@ -14347,7 +14347,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.025444984436</v>
+        <v>12.0254440307617</v>
       </c>
       <c r="H482" t="n">
         <v>53386</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.2739839553833</v>
+        <v>12.273983001709</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181125640869</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14550,7 +14550,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>12.0828008651733</v>
+        <v>12.082799911499</v>
       </c>
       <c r="H489" t="n">
         <v>48158</v>
@@ -14579,7 +14579,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>12.1019172668457</v>
+        <v>12.10191822052</v>
       </c>
       <c r="H490" t="n">
         <v>55351</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151426315308</v>
+        <v>11.8151416778564</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -14724,7 +14724,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G495" t="n">
-        <v>12.0445642471313</v>
+        <v>12.044563293457</v>
       </c>
       <c r="H495" t="n">
         <v>11804</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960252761841</v>
+        <v>11.7960243225098</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14811,7 +14811,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239595413208</v>
+        <v>11.6239585876465</v>
       </c>
       <c r="H498" t="n">
         <v>38500</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14869,7 +14869,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>12.5225229263306</v>
+        <v>12.5225219726562</v>
       </c>
       <c r="H500" t="n">
         <v>76184</v>
@@ -15014,7 +15014,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G505" t="n">
-        <v>12.8857707977295</v>
+        <v>12.8857698440552</v>
       </c>
       <c r="H505" t="n">
         <v>58282</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15101,7 +15101,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.3446111679077</v>
+        <v>13.344612121582</v>
       </c>
       <c r="H508" t="n">
         <v>57867</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H512" t="n">
         <v>20590</v>
@@ -15246,7 +15246,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9813632965088</v>
+        <v>12.9813623428345</v>
       </c>
       <c r="H513" t="n">
         <v>115376</v>
@@ -15304,7 +15304,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G515" t="n">
-        <v>13.2107820510864</v>
+        <v>13.2107830047607</v>
       </c>
       <c r="H515" t="n">
         <v>37142</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299022674561</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15420,7 +15420,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H519" t="n">
         <v>40078</v>
@@ -15449,7 +15449,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H520" t="n">
         <v>21758</v>
@@ -15478,7 +15478,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H521" t="n">
         <v>64754</v>
@@ -15507,7 +15507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H522" t="n">
         <v>13016</v>
@@ -15565,7 +15565,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.4402027130127</v>
+        <v>13.440203666687</v>
       </c>
       <c r="H524" t="n">
         <v>10410</v>
@@ -15594,7 +15594,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G525" t="n">
-        <v>13.6122674942017</v>
+        <v>13.612268447876</v>
       </c>
       <c r="H525" t="n">
         <v>28328</v>
@@ -15826,7 +15826,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H533" t="n">
         <v>18743</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16000,7 +16000,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H539" t="n">
         <v>78221</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16116,7 +16116,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.593150138855</v>
+        <v>13.5931510925293</v>
       </c>
       <c r="H543" t="n">
         <v>40682</v>
@@ -16174,7 +16174,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G545" t="n">
-        <v>13.6887407302856</v>
+        <v>13.68874168396</v>
       </c>
       <c r="H545" t="n">
         <v>37826</v>
@@ -16290,7 +16290,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H549" t="n">
         <v>19079</v>
@@ -16348,7 +16348,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H551" t="n">
         <v>11098</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416881561279</v>
+        <v>13.8416891098022</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16406,7 +16406,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225698471069</v>
+        <v>13.8225708007812</v>
       </c>
       <c r="H553" t="n">
         <v>12102</v>
@@ -16522,7 +16522,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H557" t="n">
         <v>24397</v>
@@ -16580,7 +16580,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H559" t="n">
         <v>22244</v>
@@ -16609,7 +16609,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H560" t="n">
         <v>16756</v>
@@ -16638,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H561" t="n">
         <v>10223</v>
@@ -16754,7 +16754,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H565" t="n">
         <v>66135</v>
@@ -16783,7 +16783,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H566" t="n">
         <v>38521</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16841,7 +16841,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H568" t="n">
         <v>46017</v>
@@ -16899,7 +16899,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H570" t="n">
         <v>219173</v>
@@ -16928,7 +16928,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H571" t="n">
         <v>178522</v>
@@ -17044,7 +17044,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H575" t="n">
         <v>33781</v>
@@ -17073,7 +17073,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H576" t="n">
         <v>20626</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17450,7 +17450,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G589" t="n">
-        <v>13.6122674942017</v>
+        <v>13.612268447876</v>
       </c>
       <c r="H589" t="n">
         <v>1148601</v>
@@ -17479,7 +17479,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H590" t="n">
         <v>109158</v>
@@ -17508,7 +17508,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G591" t="n">
-        <v>13.6505041122437</v>
+        <v>13.650505065918</v>
       </c>
       <c r="H591" t="n">
         <v>64144</v>
@@ -17624,7 +17624,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G595" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H595" t="n">
         <v>46485</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137060165405</v>
+        <v>12.7137050628662</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17740,7 +17740,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H599" t="n">
         <v>76279</v>
@@ -17769,7 +17769,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G600" t="n">
-        <v>12.9240083694458</v>
+        <v>12.9240074157715</v>
       </c>
       <c r="H600" t="n">
         <v>34751</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17943,7 +17943,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.254864692688</v>
+        <v>12.2548637390137</v>
       </c>
       <c r="H606" t="n">
         <v>57474</v>
@@ -18030,7 +18030,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H609" t="n">
         <v>88111</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H611" t="n">
         <v>86158</v>
@@ -18262,7 +18262,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H617" t="n">
         <v>46574</v>
@@ -18320,7 +18320,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G619" t="n">
-        <v>13.1343088150024</v>
+        <v>13.1343097686768</v>
       </c>
       <c r="H619" t="n">
         <v>185777</v>
@@ -18494,7 +18494,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754693984985</v>
+        <v>12.6754684448242</v>
       </c>
       <c r="H625" t="n">
         <v>51174</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18610,7 +18610,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G629" t="n">
-        <v>12.5416393280029</v>
+        <v>12.5416402816772</v>
       </c>
       <c r="H629" t="n">
         <v>54542</v>
@@ -18668,7 +18668,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H631" t="n">
         <v>69447</v>
@@ -18697,7 +18697,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>12.8857707977295</v>
+        <v>12.8857698440552</v>
       </c>
       <c r="H632" t="n">
         <v>24374</v>
@@ -36857,6 +36857,35 @@
         <v>50911</v>
       </c>
       <c r="I1258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1259" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>12.3199996948242</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>54422</v>
+      </c>
+      <c r="I1259" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387073516846</v>
+        <v>15.4387092590332</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954301834106</v>
+        <v>14.7954292297363</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -485,7 +485,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2873497009277</v>
+        <v>15.2873487472534</v>
       </c>
       <c r="H4" t="n">
         <v>131763</v>
@@ -572,7 +572,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738300323486</v>
+        <v>15.1738290786743</v>
       </c>
       <c r="H7" t="n">
         <v>90407</v>
@@ -659,7 +659,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008285522461</v>
+        <v>14.7008295059204</v>
       </c>
       <c r="H10" t="n">
         <v>75622</v>
@@ -688,7 +688,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711099624634</v>
+        <v>14.8711090087891</v>
       </c>
       <c r="H11" t="n">
         <v>77954</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548683166504</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -891,7 +891,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.0007905960083</v>
+        <v>14.000789642334</v>
       </c>
       <c r="H18" t="n">
         <v>7979</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819095611572</v>
+        <v>14.6819086074829</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927082061768</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.246750831604</v>
+        <v>14.2467498779297</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1152,7 +1152,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115911483765</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="n">
         <v>47594</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1355,7 +1355,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H34" t="n">
         <v>28912</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547895431519</v>
+        <v>13.0547904968262</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.903431892395</v>
+        <v>12.9034309387207</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1848,7 +1848,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2790699005127</v>
+        <v>12.279070854187</v>
       </c>
       <c r="H51" t="n">
         <v>54490</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.6168718338013</v>
+        <v>11.616870880127</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1935,7 +1935,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.8249912261963</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H54" t="n">
         <v>41198</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -1993,7 +1993,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H56" t="n">
         <v>71712</v>
@@ -2022,7 +2022,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H57" t="n">
         <v>59171</v>
@@ -2109,7 +2109,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H60" t="n">
         <v>20661</v>
@@ -2138,7 +2138,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358316421509</v>
+        <v>12.3358306884766</v>
       </c>
       <c r="H61" t="n">
         <v>27576</v>
@@ -2196,7 +2196,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G63" t="n">
-        <v>11.9385108947754</v>
+        <v>11.9385118484497</v>
       </c>
       <c r="H63" t="n">
         <v>22454</v>
@@ -2225,7 +2225,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H64" t="n">
         <v>59204</v>
@@ -2283,7 +2283,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H66" t="n">
         <v>68260</v>
@@ -2312,7 +2312,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H67" t="n">
         <v>16328</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2457,7 +2457,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H72" t="n">
         <v>14203</v>
@@ -2544,7 +2544,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G75" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H75" t="n">
         <v>23088</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763118743896</v>
+        <v>11.276312828064</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951919555664</v>
+        <v>10.5951929092407</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2776,7 +2776,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303127288818</v>
+        <v>10.3303117752075</v>
       </c>
       <c r="H83" t="n">
         <v>41339</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2834,7 +2834,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>10.9735927581787</v>
+        <v>10.9735918045044</v>
       </c>
       <c r="H85" t="n">
         <v>273384</v>
@@ -2863,7 +2863,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>11.1249523162842</v>
+        <v>11.1249513626099</v>
       </c>
       <c r="H86" t="n">
         <v>95057</v>
@@ -3008,7 +3008,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H91" t="n">
         <v>194662</v>
@@ -3037,7 +3037,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G92" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H92" t="n">
         <v>21761</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3153,7 +3153,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H96" t="n">
         <v>230549</v>
@@ -3211,7 +3211,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H98" t="n">
         <v>58338</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357917785645</v>
+        <v>11.6357908248901</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3617,7 +3617,7 @@
         <v>13.5</v>
       </c>
       <c r="G112" t="n">
-        <v>12.7709903717041</v>
+        <v>12.7709913253784</v>
       </c>
       <c r="H112" t="n">
         <v>246829</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3704,7 +3704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H115" t="n">
         <v>10754</v>
@@ -3762,7 +3762,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H117" t="n">
         <v>50078</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884914398193</v>
+        <v>11.588490486145</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4023,7 +4023,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G126" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H126" t="n">
         <v>54519</v>
@@ -4081,7 +4081,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H128" t="n">
         <v>17714</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4197,7 +4197,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195501327515</v>
+        <v>11.2195510864258</v>
       </c>
       <c r="H132" t="n">
         <v>26501</v>
@@ -4226,7 +4226,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168319702148</v>
+        <v>10.9168329238892</v>
       </c>
       <c r="H133" t="n">
         <v>53035</v>
@@ -4400,7 +4400,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G139" t="n">
-        <v>11.9385108947754</v>
+        <v>11.9385118484497</v>
       </c>
       <c r="H139" t="n">
         <v>13065</v>
@@ -4487,7 +4487,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H142" t="n">
         <v>15956</v>
@@ -4632,7 +4632,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H147" t="n">
         <v>23423</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4690,7 +4690,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H149" t="n">
         <v>57560</v>
@@ -4719,7 +4719,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H150" t="n">
         <v>63375</v>
@@ -4748,7 +4748,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614919662476</v>
+        <v>12.0614910125732</v>
       </c>
       <c r="H151" t="n">
         <v>41978</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642120361328</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5009,7 +5009,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601499557495</v>
+        <v>12.2601509094238</v>
       </c>
       <c r="H160" t="n">
         <v>44574</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5183,7 +5183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H166" t="n">
         <v>9153</v>
@@ -5241,7 +5241,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G168" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H168" t="n">
         <v>17974</v>
@@ -5299,7 +5299,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169116973877</v>
+        <v>12.3169107437134</v>
       </c>
       <c r="H170" t="n">
         <v>6203</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5357,7 +5357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>12.2317714691162</v>
+        <v>12.2317705154419</v>
       </c>
       <c r="H172" t="n">
         <v>6977</v>
@@ -5386,7 +5386,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.8249912261963</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H173" t="n">
         <v>21249</v>
@@ -5415,7 +5415,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H174" t="n">
         <v>9566</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209699630737</v>
+        <v>12.420970916748</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5705,7 +5705,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344896316528</v>
       </c>
       <c r="H184" t="n">
         <v>90193</v>
@@ -5734,7 +5734,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H185" t="n">
         <v>18304</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5792,7 +5792,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H187" t="n">
         <v>3679</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398519515991</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6053,7 +6053,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.8249912261963</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H196" t="n">
         <v>5717</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398519515991</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6140,7 +6140,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.6263303756714</v>
+        <v>11.6263313293457</v>
       </c>
       <c r="H199" t="n">
         <v>12593</v>
@@ -6198,7 +6198,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209320068359</v>
+        <v>11.7209310531616</v>
       </c>
       <c r="H201" t="n">
         <v>4105</v>
@@ -6256,7 +6256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033512115479</v>
+        <v>11.5033502578735</v>
       </c>
       <c r="H203" t="n">
         <v>16925</v>
@@ -6314,7 +6314,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G205" t="n">
-        <v>11.7114715576172</v>
+        <v>11.7114725112915</v>
       </c>
       <c r="H205" t="n">
         <v>14567</v>
@@ -6343,7 +6343,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H206" t="n">
         <v>17437</v>
@@ -6372,7 +6372,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.8249912261963</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H207" t="n">
         <v>15879</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6633,7 +6633,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G216" t="n">
-        <v>11.1249523162842</v>
+        <v>11.1249513626099</v>
       </c>
       <c r="H216" t="n">
         <v>42920</v>
@@ -6662,7 +6662,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871124267578</v>
+        <v>11.0871133804321</v>
       </c>
       <c r="H217" t="n">
         <v>62592</v>
@@ -6691,7 +6691,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587310791016</v>
+        <v>11.0587320327759</v>
       </c>
       <c r="H218" t="n">
         <v>37998</v>
@@ -6807,7 +6807,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059915542603</v>
+        <v>10.4059925079346</v>
       </c>
       <c r="H222" t="n">
         <v>8716</v>
@@ -6865,7 +6865,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G224" t="n">
-        <v>10.2830123901367</v>
+        <v>10.2830114364624</v>
       </c>
       <c r="H224" t="n">
         <v>15661</v>
@@ -6894,7 +6894,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H225" t="n">
         <v>12232</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.037052154541</v>
+        <v>10.0370512008667</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083187103271</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7300,7 +7300,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.3492317199707</v>
+        <v>10.349232673645</v>
       </c>
       <c r="H239" t="n">
         <v>10095</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032743453979</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032743453979</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7474,7 +7474,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H245" t="n">
         <v>17542</v>
@@ -7503,7 +7503,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789531707764</v>
+        <v>10.1789522171021</v>
       </c>
       <c r="H246" t="n">
         <v>25506</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>10.2167921066284</v>
+        <v>10.2167930603027</v>
       </c>
       <c r="H247" t="n">
         <v>2146</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621269226074</v>
+        <v>9.52621173858643</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7677,7 +7677,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701229095459</v>
+        <v>9.33701324462891</v>
       </c>
       <c r="H252" t="n">
         <v>8169</v>
@@ -7735,7 +7735,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917335510254</v>
+        <v>9.29917240142822</v>
       </c>
       <c r="H254" t="n">
         <v>10680</v>
@@ -7764,7 +7764,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.96137237548828</v>
+        <v>9.9613733291626</v>
       </c>
       <c r="H255" t="n">
         <v>77427</v>
@@ -7793,7 +7793,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884525299072</v>
+        <v>10.8884515762329</v>
       </c>
       <c r="H256" t="n">
         <v>68311</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7938,7 +7938,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668523788452</v>
+        <v>11.2668514251709</v>
       </c>
       <c r="H261" t="n">
         <v>11841</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -8025,7 +8025,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>11.0681924819946</v>
+        <v>11.0681915283203</v>
       </c>
       <c r="H264" t="n">
         <v>14049</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141527175903</v>
+        <v>11.3141508102417</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8112,7 +8112,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H267" t="n">
         <v>6337</v>
@@ -8141,7 +8141,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H268" t="n">
         <v>7750</v>
@@ -8228,7 +8228,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H271" t="n">
         <v>119668</v>
@@ -8286,7 +8286,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H273" t="n">
         <v>9792</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H275" t="n">
         <v>6258</v>
@@ -8431,7 +8431,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G278" t="n">
-        <v>11.7020120620728</v>
+        <v>11.7020111083984</v>
       </c>
       <c r="H278" t="n">
         <v>6135</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992919921875</v>
+        <v>11.3992910385132</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8489,7 +8489,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046913146973</v>
+        <v>11.3046922683716</v>
       </c>
       <c r="H280" t="n">
         <v>3490</v>
@@ -8634,7 +8634,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H285" t="n">
         <v>8932</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101314544678</v>
+        <v>11.9101305007935</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8779,7 +8779,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H290" t="n">
         <v>11428</v>
@@ -8866,7 +8866,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885313034058</v>
+        <v>12.2885303497314</v>
       </c>
       <c r="H293" t="n">
         <v>19905</v>
@@ -8982,7 +8982,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074512481689</v>
+        <v>12.3074522018433</v>
       </c>
       <c r="H297" t="n">
         <v>1507</v>
@@ -9011,7 +9011,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>12.0520315170288</v>
+        <v>12.0520305633545</v>
       </c>
       <c r="H298" t="n">
         <v>4631</v>
@@ -9040,7 +9040,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H299" t="n">
         <v>6219</v>
@@ -9069,7 +9069,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.7493104934692</v>
+        <v>11.7493114471436</v>
       </c>
       <c r="H300" t="n">
         <v>23263</v>
@@ -9098,7 +9098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.900671005249</v>
+        <v>11.9006719589233</v>
       </c>
       <c r="H301" t="n">
         <v>4323</v>
@@ -9127,7 +9127,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.8249912261963</v>
+        <v>11.824990272522</v>
       </c>
       <c r="H302" t="n">
         <v>35060</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9243,7 +9243,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858112335205</v>
+        <v>11.9858121871948</v>
       </c>
       <c r="H306" t="n">
         <v>22411</v>
@@ -9359,7 +9359,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H310" t="n">
         <v>86708</v>
@@ -9533,7 +9533,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818298339844</v>
+        <v>13.2818307876587</v>
       </c>
       <c r="H316" t="n">
         <v>52099</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182907104492</v>
+        <v>12.8182916641235</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9649,7 +9649,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966896057129</v>
+        <v>13.1966905593872</v>
       </c>
       <c r="H320" t="n">
         <v>115939</v>
@@ -9736,7 +9736,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872301101685</v>
+        <v>13.1872291564941</v>
       </c>
       <c r="H323" t="n">
         <v>10973</v>
@@ -9881,7 +9881,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804906845093</v>
       </c>
       <c r="H328" t="n">
         <v>127967</v>
@@ -9939,7 +9939,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G330" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980695724487</v>
       </c>
       <c r="H330" t="n">
         <v>268725</v>
@@ -10084,7 +10084,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H335" t="n">
         <v>11048</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439500808716</v>
+        <v>12.5439510345459</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10287,7 +10287,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344905853271</v>
+        <v>12.5344896316528</v>
       </c>
       <c r="H342" t="n">
         <v>31055</v>
@@ -10316,7 +10316,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723314285278</v>
+        <v>12.5723304748535</v>
       </c>
       <c r="H343" t="n">
         <v>71453</v>
@@ -10461,7 +10461,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629117965698</v>
       </c>
       <c r="H348" t="n">
         <v>46007</v>
@@ -10490,7 +10490,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629117965698</v>
       </c>
       <c r="H349" t="n">
         <v>74321</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10548,7 +10548,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426488876343</v>
+        <v>13.4426498413086</v>
       </c>
       <c r="H351" t="n">
         <v>59237</v>
@@ -10751,7 +10751,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196308135986</v>
+        <v>12.6196298599243</v>
       </c>
       <c r="H358" t="n">
         <v>55009</v>
@@ -10809,7 +10809,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H360" t="n">
         <v>130944</v>
@@ -10867,7 +10867,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737503051758</v>
+        <v>13.7737512588501</v>
       </c>
       <c r="H362" t="n">
         <v>69104</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845907211304</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548683166504</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11041,7 +11041,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G368" t="n">
-        <v>15.2684278488159</v>
+        <v>15.2684288024902</v>
       </c>
       <c r="H368" t="n">
         <v>206675</v>
@@ -11099,7 +11099,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H370" t="n">
         <v>87340</v>
@@ -11157,7 +11157,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765491485596</v>
+        <v>15.4765481948853</v>
       </c>
       <c r="H372" t="n">
         <v>24974</v>
@@ -11186,7 +11186,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H373" t="n">
         <v>58745</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225074768066</v>
+        <v>15.722508430481</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11244,7 +11244,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522289276123</v>
+        <v>15.552227973938</v>
       </c>
       <c r="H375" t="n">
         <v>73481</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927101135254</v>
+        <v>14.4927082061768</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11360,7 +11360,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549091339111</v>
+        <v>15.1549081802368</v>
       </c>
       <c r="H379" t="n">
         <v>175080</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.9123163223267</v>
+        <v>14.912317276001</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11563,7 +11563,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990919113159</v>
+        <v>15.1990909576416</v>
       </c>
       <c r="H386" t="n">
         <v>145295</v>
@@ -11679,7 +11679,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843820571899</v>
+        <v>15.0843811035156</v>
       </c>
       <c r="H390" t="n">
         <v>50895</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -12114,7 +12114,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H405" t="n">
         <v>30505</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12520,7 +12520,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211322784424</v>
+        <v>14.7211332321167</v>
       </c>
       <c r="H419" t="n">
         <v>25706</v>
@@ -12694,7 +12694,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H425" t="n">
         <v>125301</v>
@@ -12868,7 +12868,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H431" t="n">
         <v>30989</v>
@@ -12897,7 +12897,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H432" t="n">
         <v>28274</v>
@@ -12984,7 +12984,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976055145264</v>
+        <v>14.7976064682007</v>
       </c>
       <c r="H435" t="n">
         <v>58027</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9314346313477</v>
+        <v>14.931435585022</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13129,7 +13129,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608543395996</v>
+        <v>15.1608552932739</v>
       </c>
       <c r="H440" t="n">
         <v>20791</v>
@@ -13216,7 +13216,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H443" t="n">
         <v>45829</v>
@@ -13303,7 +13303,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H446" t="n">
         <v>27084</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563999176025</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13448,7 +13448,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H451" t="n">
         <v>24187</v>
@@ -13564,7 +13564,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H455" t="n">
         <v>15285</v>
@@ -13680,7 +13680,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="n">
         <v>13373</v>
@@ -13709,7 +13709,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431247711182</v>
+        <v>12.9431257247925</v>
       </c>
       <c r="H460" t="n">
         <v>31924</v>
@@ -13796,7 +13796,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H463" t="n">
         <v>22702</v>
@@ -13825,7 +13825,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H464" t="n">
         <v>16431</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034027099609</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13941,7 +13941,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H468" t="n">
         <v>37228</v>
@@ -13970,7 +13970,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H469" t="n">
         <v>10375</v>
@@ -14028,7 +14028,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.3504571914673</v>
+        <v>12.350456237793</v>
       </c>
       <c r="H471" t="n">
         <v>12026</v>
@@ -14115,7 +14115,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H474" t="n">
         <v>62001</v>
@@ -14202,7 +14202,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533782958984</v>
       </c>
       <c r="H477" t="n">
         <v>44549</v>
@@ -14289,7 +14289,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.987208366394</v>
+        <v>11.9872074127197</v>
       </c>
       <c r="H480" t="n">
         <v>47163</v>
@@ -14347,7 +14347,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.0254440307617</v>
+        <v>12.025444984436</v>
       </c>
       <c r="H482" t="n">
         <v>53386</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181125640869</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151416778564</v>
+        <v>11.8151426315308</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -15275,7 +15275,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H514" t="n">
         <v>83965</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299022674561</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15623,7 +15623,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H526" t="n">
         <v>18896</v>
@@ -15710,7 +15710,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="n">
         <v>14580</v>
@@ -15826,7 +15826,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.4210844039917</v>
+        <v>13.421085357666</v>
       </c>
       <c r="H533" t="n">
         <v>18743</v>
@@ -15942,7 +15942,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H537" t="n">
         <v>90113</v>
@@ -16000,7 +16000,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H539" t="n">
         <v>78221</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16087,7 +16087,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H542" t="n">
         <v>31099</v>
@@ -16145,7 +16145,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H544" t="n">
         <v>20063</v>
@@ -16203,7 +16203,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.669623374939</v>
+        <v>13.6696243286133</v>
       </c>
       <c r="H546" t="n">
         <v>15340</v>
@@ -16319,7 +16319,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H550" t="n">
         <v>10006</v>
@@ -16348,7 +16348,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H551" t="n">
         <v>11098</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416891098022</v>
+        <v>13.8416881561279</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16406,7 +16406,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225708007812</v>
+        <v>13.8225698471069</v>
       </c>
       <c r="H553" t="n">
         <v>12102</v>
@@ -16435,7 +16435,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H554" t="n">
         <v>25672</v>
@@ -16725,7 +16725,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.49755859375</v>
+        <v>13.4975576400757</v>
       </c>
       <c r="H564" t="n">
         <v>58797</v>
@@ -16783,7 +16783,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H566" t="n">
         <v>38521</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799266815186</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16841,7 +16841,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H568" t="n">
         <v>46017</v>
@@ -16899,7 +16899,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H570" t="n">
         <v>219173</v>
@@ -16986,7 +16986,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034515380859</v>
+        <v>13.8034524917603</v>
       </c>
       <c r="H573" t="n">
         <v>66012</v>
@@ -17073,7 +17073,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608064651489</v>
+        <v>13.8608074188232</v>
       </c>
       <c r="H576" t="n">
         <v>20626</v>
@@ -17189,7 +17189,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725942611694</v>
+        <v>14.4725952148438</v>
       </c>
       <c r="H580" t="n">
         <v>84048</v>
@@ -17218,7 +17218,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137538909912</v>
+        <v>14.0137548446655</v>
       </c>
       <c r="H581" t="n">
         <v>92704</v>
@@ -17247,7 +17247,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093454360962</v>
+        <v>14.1093463897705</v>
       </c>
       <c r="H582" t="n">
         <v>56656</v>
@@ -17334,7 +17334,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049369812012</v>
+        <v>14.2049379348755</v>
       </c>
       <c r="H585" t="n">
         <v>62831</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946355819702</v>
+        <v>13.9946365356445</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17537,7 +17537,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.7078609466553</v>
+        <v>13.707859992981</v>
       </c>
       <c r="H592" t="n">
         <v>66158</v>
@@ -17740,7 +17740,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H599" t="n">
         <v>76279</v>
@@ -17856,7 +17856,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H603" t="n">
         <v>43650</v>
@@ -17885,7 +17885,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H604" t="n">
         <v>96008</v>
@@ -17972,7 +17972,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.426929473877</v>
+        <v>12.4269304275513</v>
       </c>
       <c r="H607" t="n">
         <v>33493</v>
@@ -18001,7 +18001,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798768997192</v>
+        <v>12.5798759460449</v>
       </c>
       <c r="H608" t="n">
         <v>23155</v>
@@ -18030,7 +18030,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H609" t="n">
         <v>88111</v>
@@ -18117,7 +18117,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048891067505</v>
+        <v>12.9048881530762</v>
       </c>
       <c r="H612" t="n">
         <v>92138</v>
@@ -18262,7 +18262,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H617" t="n">
         <v>46574</v>
@@ -18407,7 +18407,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H622" t="n">
         <v>40402</v>
@@ -18436,7 +18436,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H623" t="n">
         <v>82380</v>
@@ -18465,7 +18465,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710590362549</v>
       </c>
       <c r="H624" t="n">
         <v>62905</v>
@@ -18668,7 +18668,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H631" t="n">
         <v>69447</v>
@@ -18784,7 +18784,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H635" t="n">
         <v>124717</v>
@@ -18871,7 +18871,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H638" t="n">
         <v>21080</v>
@@ -18900,7 +18900,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H639" t="n">
         <v>40704</v>
@@ -18929,7 +18929,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H640" t="n">
         <v>101641</v>
@@ -18958,7 +18958,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047546386719</v>
+        <v>14.4047555923462</v>
       </c>
       <c r="H641" t="n">
         <v>104803</v>
@@ -19045,7 +19045,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H644" t="n">
         <v>37693</v>
@@ -19132,7 +19132,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H647" t="n">
         <v>62394</v>
@@ -19306,7 +19306,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H653" t="n">
         <v>67181</v>
@@ -19480,7 +19480,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H659" t="n">
         <v>65476</v>
@@ -19538,7 +19538,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H661" t="n">
         <v>35343</v>
@@ -19625,7 +19625,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H664" t="n">
         <v>45922</v>
@@ -19654,7 +19654,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751262664795</v>
+        <v>15.9751253128052</v>
       </c>
       <c r="H665" t="n">
         <v>60499</v>
@@ -19683,7 +19683,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108360290527</v>
+        <v>16.1108379364014</v>
       </c>
       <c r="H666" t="n">
         <v>28199</v>
@@ -19770,7 +19770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H669" t="n">
         <v>107477</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761770248413</v>
+        <v>14.6761779785156</v>
       </c>
       <c r="H672" t="n">
         <v>131068</v>
@@ -19944,7 +19944,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H675" t="n">
         <v>84935</v>
@@ -20002,7 +20002,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H677" t="n">
         <v>28484</v>
@@ -20031,7 +20031,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H678" t="n">
         <v>45965</v>
@@ -20089,7 +20089,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H680" t="n">
         <v>49932</v>
@@ -20205,7 +20205,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H684" t="n">
         <v>33213</v>
@@ -20263,7 +20263,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H686" t="n">
         <v>149634</v>
@@ -20292,7 +20292,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H687" t="n">
         <v>39470</v>
@@ -20350,7 +20350,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496105194092</v>
+        <v>16.1496124267578</v>
       </c>
       <c r="H689" t="n">
         <v>60094</v>
@@ -20553,7 +20553,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843156814575</v>
+        <v>15.6843166351318</v>
       </c>
       <c r="H696" t="n">
         <v>33104</v>
@@ -20582,7 +20582,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975763320923</v>
+        <v>15.8975772857666</v>
       </c>
       <c r="H697" t="n">
         <v>154495</v>
@@ -20611,7 +20611,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H698" t="n">
         <v>76799</v>
@@ -20640,7 +20640,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H699" t="n">
         <v>43123</v>
@@ -20727,7 +20727,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H702" t="n">
         <v>27978</v>
@@ -20843,7 +20843,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H706" t="n">
         <v>80940</v>
@@ -20872,7 +20872,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H707" t="n">
         <v>82998</v>
@@ -20988,7 +20988,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H711" t="n">
         <v>31373</v>
@@ -21046,7 +21046,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H713" t="n">
         <v>58117</v>
@@ -21191,7 +21191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H718" t="n">
         <v>55322</v>
@@ -21249,7 +21249,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833110809326</v>
+        <v>15.0833101272583</v>
       </c>
       <c r="H720" t="n">
         <v>39360</v>
@@ -21278,7 +21278,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H721" t="n">
         <v>65632</v>
@@ -21307,7 +21307,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506631851196</v>
+        <v>14.8506622314453</v>
       </c>
       <c r="H722" t="n">
         <v>53763</v>
@@ -21394,7 +21394,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078184127808</v>
+        <v>14.3078193664551</v>
       </c>
       <c r="H725" t="n">
         <v>86664</v>
@@ -21423,7 +21423,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823045730591</v>
+        <v>14.4823036193848</v>
       </c>
       <c r="H726" t="n">
         <v>87213</v>
@@ -21452,7 +21452,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H727" t="n">
         <v>73456</v>
@@ -21597,7 +21597,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H732" t="n">
         <v>67534</v>
@@ -21655,7 +21655,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H734" t="n">
         <v>45192</v>
@@ -21713,7 +21713,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H736" t="n">
         <v>101028</v>
@@ -21771,7 +21771,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965707778931</v>
+        <v>15.2965698242188</v>
       </c>
       <c r="H738" t="n">
         <v>284400</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H739" t="n">
         <v>99147</v>
@@ -21916,7 +21916,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486068725586</v>
+        <v>15.5486059188843</v>
       </c>
       <c r="H743" t="n">
         <v>51182</v>
@@ -22032,7 +22032,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H747" t="n">
         <v>39016</v>
@@ -22148,7 +22148,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H751" t="n">
         <v>131748</v>
@@ -22235,7 +22235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H754" t="n">
         <v>50268</v>
@@ -22264,7 +22264,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H755" t="n">
         <v>44022</v>
@@ -22438,7 +22438,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914949417114</v>
+        <v>14.1914958953857</v>
       </c>
       <c r="H761" t="n">
         <v>62425</v>
@@ -22496,7 +22496,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H763" t="n">
         <v>51431</v>
@@ -22525,7 +22525,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H764" t="n">
         <v>67676</v>
@@ -22583,7 +22583,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.2108821868896</v>
+        <v>14.210883140564</v>
       </c>
       <c r="H766" t="n">
         <v>97709</v>
@@ -22612,7 +22612,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H767" t="n">
         <v>48972</v>
@@ -22641,7 +22641,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976215362549</v>
+        <v>13.9976224899292</v>
       </c>
       <c r="H768" t="n">
         <v>48388</v>
@@ -22670,7 +22670,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H769" t="n">
         <v>43039</v>
@@ -22728,7 +22728,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H771" t="n">
         <v>91611</v>
@@ -22757,7 +22757,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H772" t="n">
         <v>59694</v>
@@ -22815,7 +22815,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H774" t="n">
         <v>46705</v>
@@ -22931,7 +22931,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H778" t="n">
         <v>54214</v>
@@ -22960,7 +22960,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.163969039917</v>
+        <v>13.1639680862427</v>
       </c>
       <c r="H779" t="n">
         <v>31292</v>
@@ -23047,7 +23047,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H782" t="n">
         <v>29208</v>
@@ -23076,7 +23076,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H783" t="n">
         <v>48982</v>
@@ -23105,7 +23105,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H784" t="n">
         <v>44891</v>
@@ -23192,7 +23192,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H787" t="n">
         <v>75458</v>
@@ -23221,7 +23221,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.9200735092163</v>
+        <v>13.920072555542</v>
       </c>
       <c r="H788" t="n">
         <v>161892</v>
@@ -23453,7 +23453,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H796" t="n">
         <v>130807</v>
@@ -23511,7 +23511,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H798" t="n">
         <v>24558</v>
@@ -23598,7 +23598,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H801" t="n">
         <v>52319</v>
@@ -23627,7 +23627,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H802" t="n">
         <v>34321</v>
@@ -23772,7 +23772,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H807" t="n">
         <v>77476</v>
@@ -23859,7 +23859,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H810" t="n">
         <v>292244</v>
@@ -23888,7 +23888,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210781097412</v>
+        <v>14.5210790634155</v>
       </c>
       <c r="H811" t="n">
         <v>260837</v>
@@ -23917,7 +23917,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751714706421</v>
+        <v>14.0751724243164</v>
       </c>
       <c r="H812" t="n">
         <v>95170</v>
@@ -24062,7 +24062,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098756790161</v>
+        <v>13.6098766326904</v>
       </c>
       <c r="H817" t="n">
         <v>77436</v>
@@ -24236,7 +24236,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H823" t="n">
         <v>139568</v>
@@ -24294,7 +24294,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H825" t="n">
         <v>40244</v>
@@ -24323,7 +24323,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H826" t="n">
         <v>46870</v>
@@ -24352,7 +24352,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H827" t="n">
         <v>35005</v>
@@ -24381,7 +24381,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H828" t="n">
         <v>44484</v>
@@ -24584,7 +24584,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H835" t="n">
         <v>51758</v>
@@ -24961,7 +24961,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H848" t="n">
         <v>65992</v>
@@ -24990,7 +24990,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.349702835083</v>
+        <v>12.3497018814087</v>
       </c>
       <c r="H849" t="n">
         <v>101683</v>
@@ -25193,7 +25193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.5241889953613</v>
+        <v>12.524188041687</v>
       </c>
       <c r="H856" t="n">
         <v>89742</v>
@@ -25425,7 +25425,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017370223999</v>
+        <v>12.6017379760742</v>
       </c>
       <c r="H864" t="n">
         <v>23829</v>
@@ -25454,7 +25454,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H865" t="n">
         <v>77981</v>
@@ -25512,7 +25512,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037952423096</v>
+        <v>11.9037942886353</v>
       </c>
       <c r="H867" t="n">
         <v>165052</v>
@@ -25570,7 +25570,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.5354356765747</v>
+        <v>11.535436630249</v>
       </c>
       <c r="H869" t="n">
         <v>221362</v>
@@ -25657,7 +25657,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262462615967</v>
+        <v>11.8262453079224</v>
       </c>
       <c r="H872" t="n">
         <v>56333</v>
@@ -25715,7 +25715,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129846572876</v>
+        <v>11.6129856109619</v>
       </c>
       <c r="H874" t="n">
         <v>58043</v>
@@ -25773,7 +25773,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905355453491</v>
+        <v>11.6905345916748</v>
       </c>
       <c r="H876" t="n">
         <v>76554</v>
@@ -25802,7 +25802,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201187133789</v>
+        <v>12.0201177597046</v>
       </c>
       <c r="H877" t="n">
         <v>82169</v>
@@ -25831,7 +25831,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558303833008</v>
+        <v>12.1558294296265</v>
       </c>
       <c r="H878" t="n">
         <v>210169</v>
@@ -25976,7 +25976,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H883" t="n">
         <v>63353</v>
@@ -36886,6 +36886,35 @@
         <v>54422</v>
       </c>
       <c r="I1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1260" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>51538</v>
+      </c>
+      <c r="I1260" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387092590332</v>
+        <v>15.4387083053589</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954292297363</v>
+        <v>14.7954301834106</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -572,7 +572,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>15.1738290786743</v>
+        <v>15.1738300323486</v>
       </c>
       <c r="H7" t="n">
         <v>90407</v>
@@ -601,7 +601,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H8" t="n">
         <v>69786</v>
@@ -833,7 +833,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359493255615</v>
+        <v>14.4359502792358</v>
       </c>
       <c r="H16" t="n">
         <v>13170</v>
@@ -891,7 +891,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007905960083</v>
       </c>
       <c r="H18" t="n">
         <v>7979</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819086074829</v>
+        <v>14.6819095611572</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -978,7 +978,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H21" t="n">
         <v>20677</v>
@@ -1007,7 +1007,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4927082061768</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H22" t="n">
         <v>10989</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845907211304</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1065,7 +1065,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2467498779297</v>
+        <v>14.246750831604</v>
       </c>
       <c r="H24" t="n">
         <v>35369</v>
@@ -1094,7 +1094,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278308868408</v>
       </c>
       <c r="H25" t="n">
         <v>54159</v>
@@ -1123,7 +1123,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1710681915283</v>
+        <v>14.1710691452026</v>
       </c>
       <c r="H26" t="n">
         <v>81706</v>
@@ -1297,7 +1297,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.6223888397217</v>
+        <v>13.622389793396</v>
       </c>
       <c r="H32" t="n">
         <v>22783</v>
@@ -1413,7 +1413,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H36" t="n">
         <v>8817</v>
@@ -1442,7 +1442,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H37" t="n">
         <v>21560</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547904968262</v>
+        <v>13.0547914505005</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1558,7 +1558,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H41" t="n">
         <v>36059</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034309387207</v>
+        <v>12.9034299850464</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1790,7 +1790,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H49" t="n">
         <v>62308</v>
@@ -1848,7 +1848,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G51" t="n">
-        <v>12.279070854187</v>
+        <v>12.2790699005127</v>
       </c>
       <c r="H51" t="n">
         <v>54490</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.616870880127</v>
+        <v>11.6168718338013</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1935,7 +1935,7 @@
         <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H54" t="n">
         <v>41198</v>
@@ -1964,7 +1964,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357917785645</v>
       </c>
       <c r="H55" t="n">
         <v>44815</v>
@@ -2051,7 +2051,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277122497559</v>
       </c>
       <c r="H58" t="n">
         <v>38827</v>
@@ -2080,7 +2080,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277122497559</v>
       </c>
       <c r="H59" t="n">
         <v>23840</v>
@@ -2138,7 +2138,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358306884766</v>
+        <v>12.3358316421509</v>
       </c>
       <c r="H61" t="n">
         <v>27576</v>
@@ -2196,7 +2196,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G63" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H63" t="n">
         <v>22454</v>
@@ -2312,7 +2312,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H67" t="n">
         <v>16328</v>
@@ -2370,7 +2370,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277122497559</v>
       </c>
       <c r="H69" t="n">
         <v>21775</v>
@@ -2515,7 +2515,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9952707290649</v>
+        <v>11.9952716827393</v>
       </c>
       <c r="H74" t="n">
         <v>37444</v>
@@ -2544,7 +2544,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G75" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H75" t="n">
         <v>23088</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.276312828064</v>
+        <v>11.2763118743896</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951929092407</v>
+        <v>10.5951919555664</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2863,7 +2863,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>11.1249513626099</v>
+        <v>11.1249523162842</v>
       </c>
       <c r="H86" t="n">
         <v>95057</v>
@@ -2921,7 +2921,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736316680908</v>
+        <v>11.6736307144165</v>
       </c>
       <c r="H88" t="n">
         <v>118173</v>
@@ -3008,7 +3008,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H91" t="n">
         <v>194662</v>
@@ -3037,7 +3037,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G92" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H92" t="n">
         <v>21761</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.3141508102417</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276723861694</v>
+        <v>11.4276714324951</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3385,7 +3385,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>11.6357908248901</v>
+        <v>11.6357917785645</v>
       </c>
       <c r="H104" t="n">
         <v>75979</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.550651550293</v>
+        <v>11.5506505966187</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3733,7 +3733,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H116" t="n">
         <v>29281</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3849,7 +3849,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H120" t="n">
         <v>18650</v>
@@ -3907,7 +3907,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>11.6641712188721</v>
+        <v>11.6641721725464</v>
       </c>
       <c r="H122" t="n">
         <v>38398</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.588490486145</v>
+        <v>11.5884914398193</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4023,7 +4023,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G126" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H126" t="n">
         <v>54519</v>
@@ -4052,7 +4052,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H127" t="n">
         <v>53178</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4197,7 +4197,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195510864258</v>
+        <v>11.2195501327515</v>
       </c>
       <c r="H132" t="n">
         <v>26501</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979518890381</v>
+        <v>11.5979509353638</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4371,7 +4371,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195919036865</v>
+        <v>11.9195909500122</v>
       </c>
       <c r="H138" t="n">
         <v>19683</v>
@@ -4400,7 +4400,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G139" t="n">
-        <v>11.9385118484497</v>
+        <v>11.9385108947754</v>
       </c>
       <c r="H139" t="n">
         <v>13065</v>
@@ -4429,7 +4429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H140" t="n">
         <v>24892</v>
@@ -4458,7 +4458,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H141" t="n">
         <v>37220</v>
@@ -4516,7 +4516,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>12.0898714065552</v>
+        <v>12.0898704528809</v>
       </c>
       <c r="H143" t="n">
         <v>1847</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642120361328</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4835,7 +4835,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G154" t="n">
-        <v>12.7899103164673</v>
+        <v>12.7899112701416</v>
       </c>
       <c r="H154" t="n">
         <v>1088974</v>
@@ -4864,7 +4864,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H155" t="n">
         <v>41701</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4922,7 +4922,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H157" t="n">
         <v>25916</v>
@@ -5038,7 +5038,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277122497559</v>
       </c>
       <c r="H161" t="n">
         <v>34152</v>
@@ -5125,7 +5125,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G164" t="n">
-        <v>11.8912105560303</v>
+        <v>11.8912115097046</v>
       </c>
       <c r="H164" t="n">
         <v>18357</v>
@@ -5154,7 +5154,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>11.8722906112671</v>
+        <v>11.8722915649414</v>
       </c>
       <c r="H165" t="n">
         <v>6548</v>
@@ -5212,7 +5212,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966117858887</v>
+        <v>11.796612739563</v>
       </c>
       <c r="H167" t="n">
         <v>6760</v>
@@ -5299,7 +5299,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169107437134</v>
+        <v>12.316912651062</v>
       </c>
       <c r="H170" t="n">
         <v>6203</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412309646606</v>
+        <v>12.2412300109863</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5357,7 +5357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>12.2317705154419</v>
+        <v>12.2317714691162</v>
       </c>
       <c r="H172" t="n">
         <v>6977</v>
@@ -5386,7 +5386,7 @@
         <v>12.5</v>
       </c>
       <c r="G173" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H173" t="n">
         <v>21249</v>
@@ -5415,7 +5415,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G174" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H174" t="n">
         <v>9566</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5531,7 +5531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223119735718</v>
+        <v>12.2223110198975</v>
       </c>
       <c r="H178" t="n">
         <v>16515</v>
@@ -5560,7 +5560,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G179" t="n">
-        <v>12.3547515869141</v>
+        <v>12.3547525405884</v>
       </c>
       <c r="H179" t="n">
         <v>21056</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925914764404</v>
+        <v>12.3925905227661</v>
       </c>
       <c r="H181" t="n">
         <v>37878</v>
@@ -5705,7 +5705,7 @@
         <v>13.25</v>
       </c>
       <c r="G184" t="n">
-        <v>12.5344896316528</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H184" t="n">
         <v>90193</v>
@@ -5850,7 +5850,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.2033910751343</v>
+        <v>12.20339012146</v>
       </c>
       <c r="H189" t="n">
         <v>22438</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6024,7 +6024,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H195" t="n">
         <v>9323</v>
@@ -6053,7 +6053,7 @@
         <v>12.5</v>
       </c>
       <c r="G196" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H196" t="n">
         <v>5717</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398519515991</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6111,7 +6111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H198" t="n">
         <v>9999</v>
@@ -6140,7 +6140,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.6263313293457</v>
+        <v>11.62633228302</v>
       </c>
       <c r="H199" t="n">
         <v>12593</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695714950562</v>
+        <v>11.5695705413818</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6256,7 +6256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033502578735</v>
+        <v>11.5033512115479</v>
       </c>
       <c r="H203" t="n">
         <v>16925</v>
@@ -6314,7 +6314,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G205" t="n">
-        <v>11.7114725112915</v>
+        <v>11.7114715576172</v>
       </c>
       <c r="H205" t="n">
         <v>14567</v>
@@ -6372,7 +6372,7 @@
         <v>12.5</v>
       </c>
       <c r="G207" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H207" t="n">
         <v>15879</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452531814575</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.3141508102417</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6633,7 +6633,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G216" t="n">
-        <v>11.1249513626099</v>
+        <v>11.1249523162842</v>
       </c>
       <c r="H216" t="n">
         <v>42920</v>
@@ -6691,7 +6691,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587320327759</v>
+        <v>11.0587310791016</v>
       </c>
       <c r="H218" t="n">
         <v>37998</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316528320312</v>
+        <v>10.1316518783569</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -7010,7 +7010,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947326660156</v>
+        <v>9.81947231292725</v>
       </c>
       <c r="H229" t="n">
         <v>68277</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275926589966</v>
+        <v>10.0275917053223</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0370512008667</v>
+        <v>10.037052154541</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055236816406</v>
+        <v>9.80055141448975</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7300,7 +7300,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G239" t="n">
-        <v>10.349232673645</v>
+        <v>10.3492317199707</v>
       </c>
       <c r="H239" t="n">
         <v>10095</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032743453979</v>
+        <v>10.1032733917236</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032743453979</v>
+        <v>10.1032733917236</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731315612793</v>
+        <v>9.85731220245361</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621173858643</v>
+        <v>9.52621364593506</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729370117188</v>
+        <v>9.50729274749756</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7648,7 +7648,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647369384766</v>
+        <v>9.34647274017334</v>
       </c>
       <c r="H251" t="n">
         <v>15863</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.3141508102417</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.3141508102417</v>
+        <v>11.314151763916</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8286,7 +8286,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H273" t="n">
         <v>9792</v>
@@ -8373,7 +8373,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.247932434082</v>
+        <v>11.2479314804077</v>
       </c>
       <c r="H276" t="n">
         <v>32729</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992910385132</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8489,7 +8489,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>11.3046922683716</v>
+        <v>11.3046913146973</v>
       </c>
       <c r="H280" t="n">
         <v>3490</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8605,7 +8605,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966117858887</v>
+        <v>11.796612739563</v>
       </c>
       <c r="H284" t="n">
         <v>13107</v>
@@ -8750,7 +8750,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H289" t="n">
         <v>18611</v>
@@ -8779,7 +8779,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H290" t="n">
         <v>11428</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -8953,7 +8953,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H296" t="n">
         <v>113027</v>
@@ -9127,7 +9127,7 @@
         <v>12.5</v>
       </c>
       <c r="G302" t="n">
-        <v>11.824990272522</v>
+        <v>11.8249912261963</v>
       </c>
       <c r="H302" t="n">
         <v>35060</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939315795898</v>
+        <v>12.1939306259155</v>
       </c>
       <c r="H304" t="n">
         <v>1793</v>
@@ -9214,7 +9214,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>12.3547515869141</v>
+        <v>12.3547525405884</v>
       </c>
       <c r="H305" t="n">
         <v>7507</v>
@@ -9243,7 +9243,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.9858121871948</v>
+        <v>11.9858112335205</v>
       </c>
       <c r="H306" t="n">
         <v>22411</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9533,7 +9533,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G316" t="n">
-        <v>13.2818307876587</v>
+        <v>13.2818298339844</v>
       </c>
       <c r="H316" t="n">
         <v>52099</v>
@@ -9562,7 +9562,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G317" t="n">
-        <v>13.0642509460449</v>
+        <v>13.0642518997192</v>
       </c>
       <c r="H317" t="n">
         <v>729414</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182907104492</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9736,7 +9736,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>13.1872291564941</v>
+        <v>13.1872301101685</v>
       </c>
       <c r="H323" t="n">
         <v>10973</v>
@@ -9823,7 +9823,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075290679932</v>
+        <v>13.7075309753418</v>
       </c>
       <c r="H326" t="n">
         <v>108302</v>
@@ -9852,7 +9852,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G327" t="n">
-        <v>13.3669710159302</v>
+        <v>13.3669700622559</v>
       </c>
       <c r="H327" t="n">
         <v>36337</v>
@@ -9910,7 +9910,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385906219482</v>
+        <v>13.3385896682739</v>
       </c>
       <c r="H329" t="n">
         <v>198840</v>
@@ -10055,7 +10055,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399307250977</v>
+        <v>13.1399297714233</v>
       </c>
       <c r="H334" t="n">
         <v>35387</v>
@@ -10084,7 +10084,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H335" t="n">
         <v>11048</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088293075562</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10171,7 +10171,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142305374146</v>
+        <v>12.7142295837402</v>
       </c>
       <c r="H338" t="n">
         <v>27898</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439510345459</v>
+        <v>12.5439519882202</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10229,7 +10229,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.799370765686</v>
+        <v>12.7993698120117</v>
       </c>
       <c r="H340" t="n">
         <v>39580</v>
@@ -10258,7 +10258,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372106552124</v>
+        <v>12.8372116088867</v>
       </c>
       <c r="H341" t="n">
         <v>71543</v>
@@ -10287,7 +10287,7 @@
         <v>13.25</v>
       </c>
       <c r="G342" t="n">
-        <v>12.5344896316528</v>
+        <v>12.5344905853271</v>
       </c>
       <c r="H342" t="n">
         <v>31055</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088701248169</v>
+        <v>13.5088691711426</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10403,7 +10403,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.764289855957</v>
+        <v>13.7642908096313</v>
       </c>
       <c r="H346" t="n">
         <v>87295</v>
@@ -10461,7 +10461,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629117965698</v>
+        <v>13.2629108428955</v>
       </c>
       <c r="H348" t="n">
         <v>46007</v>
@@ -10490,7 +10490,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629117965698</v>
+        <v>13.2629108428955</v>
       </c>
       <c r="H349" t="n">
         <v>74321</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10577,7 +10577,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.7264499664307</v>
+        <v>13.726450920105</v>
       </c>
       <c r="H352" t="n">
         <v>43550</v>
@@ -10780,7 +10780,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G359" t="n">
-        <v>12.5628700256348</v>
+        <v>12.5628709793091</v>
       </c>
       <c r="H359" t="n">
         <v>54126</v>
@@ -10809,7 +10809,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H360" t="n">
         <v>130944</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764295578003</v>
+        <v>13.3764305114746</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845907211304</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -10983,7 +10983,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278299331665</v>
+        <v>14.2278308868408</v>
       </c>
       <c r="H366" t="n">
         <v>130359</v>
@@ -11099,7 +11099,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H370" t="n">
         <v>87340</v>
@@ -11157,7 +11157,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G372" t="n">
-        <v>15.4765481948853</v>
+        <v>15.4765491485596</v>
       </c>
       <c r="H372" t="n">
         <v>24974</v>
@@ -11186,7 +11186,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H373" t="n">
         <v>58745</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.722508430481</v>
+        <v>15.7225093841553</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11244,7 +11244,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.552227973938</v>
+        <v>15.5522298812866</v>
       </c>
       <c r="H375" t="n">
         <v>73481</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792293548584</v>
+        <v>15.0792284011841</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11302,7 +11302,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G377" t="n">
-        <v>14.4927082061768</v>
+        <v>14.4927091598511</v>
       </c>
       <c r="H377" t="n">
         <v>57843</v>
@@ -11331,7 +11331,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H378" t="n">
         <v>85275</v>
@@ -11360,7 +11360,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>15.1549081802368</v>
+        <v>15.1549091339111</v>
       </c>
       <c r="H379" t="n">
         <v>175080</v>
@@ -11418,7 +11418,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>14.912317276001</v>
+        <v>14.9123163223267</v>
       </c>
       <c r="H381" t="n">
         <v>66187</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11476,7 +11476,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H383" t="n">
         <v>42204</v>
@@ -11563,7 +11563,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>15.1990909576416</v>
+        <v>15.1990919113159</v>
       </c>
       <c r="H386" t="n">
         <v>145295</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11708,7 +11708,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H391" t="n">
         <v>32365</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020149230957</v>
+        <v>14.7020139694214</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.0079078674316</v>
+        <v>15.007908821106</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11824,7 +11824,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H395" t="n">
         <v>27692</v>
@@ -11882,7 +11882,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G397" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H397" t="n">
         <v>32947</v>
@@ -11911,7 +11911,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.950553894043</v>
+        <v>14.9505529403687</v>
       </c>
       <c r="H398" t="n">
         <v>35897</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12114,7 +12114,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H405" t="n">
         <v>30505</v>
@@ -12201,7 +12201,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108318328857</v>
+        <v>14.5108308792114</v>
       </c>
       <c r="H408" t="n">
         <v>38004</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064224243164</v>
+        <v>14.6064233779907</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12346,7 +12346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H413" t="n">
         <v>34048</v>
@@ -12404,7 +12404,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H415" t="n">
         <v>18337</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299501419067</v>
+        <v>14.5299491882324</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12520,7 +12520,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>14.7211332321167</v>
+        <v>14.7211322784424</v>
       </c>
       <c r="H419" t="n">
         <v>25706</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12694,7 +12694,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H425" t="n">
         <v>125301</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12781,7 +12781,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520383834839</v>
+        <v>15.3520374298096</v>
       </c>
       <c r="H428" t="n">
         <v>49360</v>
@@ -12839,7 +12839,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G430" t="n">
-        <v>15.1799736022949</v>
+        <v>15.1799726486206</v>
       </c>
       <c r="H430" t="n">
         <v>15809</v>
@@ -12868,7 +12868,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G431" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H431" t="n">
         <v>30989</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -12984,7 +12984,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7976064682007</v>
+        <v>14.7976055145264</v>
       </c>
       <c r="H435" t="n">
         <v>58027</v>
@@ -13013,7 +13013,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G436" t="n">
-        <v>14.931435585022</v>
+        <v>14.9314346313477</v>
       </c>
       <c r="H436" t="n">
         <v>23363</v>
@@ -13071,7 +13071,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H438" t="n">
         <v>18515</v>
@@ -13100,7 +13100,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417369842529</v>
+        <v>15.1417360305786</v>
       </c>
       <c r="H439" t="n">
         <v>30668</v>
@@ -13129,7 +13129,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1608552932739</v>
+        <v>15.1608543395996</v>
       </c>
       <c r="H440" t="n">
         <v>20791</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902759552002</v>
+        <v>15.3902750015259</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13303,7 +13303,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G446" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H446" t="n">
         <v>27084</v>
@@ -13419,7 +13419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711097717285</v>
+        <v>14.0711088180542</v>
       </c>
       <c r="H450" t="n">
         <v>16818</v>
@@ -13448,7 +13448,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G451" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H451" t="n">
         <v>24187</v>
@@ -13564,7 +13564,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G455" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H455" t="n">
         <v>15285</v>
@@ -13738,7 +13738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H461" t="n">
         <v>47646</v>
@@ -13767,7 +13767,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H462" t="n">
         <v>24475</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13941,7 +13941,7 @@
         <v>13</v>
       </c>
       <c r="G468" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H468" t="n">
         <v>37228</v>
@@ -13970,7 +13970,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H469" t="n">
         <v>10375</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14028,7 +14028,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G471" t="n">
-        <v>12.350456237793</v>
+        <v>12.3504571914673</v>
       </c>
       <c r="H471" t="n">
         <v>12026</v>
@@ -14115,7 +14115,7 @@
         <v>13</v>
       </c>
       <c r="G474" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H474" t="n">
         <v>62001</v>
@@ -14144,7 +14144,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H475" t="n">
         <v>61238</v>
@@ -14202,7 +14202,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533782958984</v>
+        <v>11.8533802032471</v>
       </c>
       <c r="H477" t="n">
         <v>44549</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14318,7 +14318,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.0636806488037</v>
+        <v>12.063681602478</v>
       </c>
       <c r="H481" t="n">
         <v>28977</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.273983001709</v>
+        <v>12.2739839553833</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14463,7 +14463,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H486" t="n">
         <v>45367</v>
@@ -14492,7 +14492,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.29310131073</v>
+        <v>12.2931022644043</v>
       </c>
       <c r="H487" t="n">
         <v>28990</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151426315308</v>
+        <v>11.8151435852051</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960243225098</v>
+        <v>11.7960252761841</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14811,7 +14811,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239585876465</v>
+        <v>11.6239595413208</v>
       </c>
       <c r="H498" t="n">
         <v>38500</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14898,7 +14898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H501" t="n">
         <v>67973</v>
@@ -14956,7 +14956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H503" t="n">
         <v>36066</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15101,7 +15101,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.344612121582</v>
+        <v>13.3446111679077</v>
       </c>
       <c r="H508" t="n">
         <v>57867</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H512" t="n">
         <v>20590</v>
@@ -15275,7 +15275,7 @@
         <v>13.5</v>
       </c>
       <c r="G514" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H514" t="n">
         <v>83965</v>
@@ -15420,7 +15420,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H519" t="n">
         <v>40078</v>
@@ -15449,7 +15449,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H520" t="n">
         <v>21758</v>
@@ -15478,7 +15478,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H521" t="n">
         <v>64754</v>
@@ -15507,7 +15507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H522" t="n">
         <v>13016</v>
@@ -15565,7 +15565,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.440203666687</v>
+        <v>13.4402027130127</v>
       </c>
       <c r="H524" t="n">
         <v>10410</v>
@@ -15623,7 +15623,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G526" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H526" t="n">
         <v>18896</v>
@@ -15826,7 +15826,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G533" t="n">
-        <v>13.421085357666</v>
+        <v>13.4210844039917</v>
       </c>
       <c r="H533" t="n">
         <v>18743</v>
@@ -15884,7 +15884,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H535" t="n">
         <v>118515</v>
@@ -15942,7 +15942,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H537" t="n">
         <v>90113</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16087,7 +16087,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H542" t="n">
         <v>31099</v>
@@ -16116,7 +16116,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.5931510925293</v>
+        <v>13.593150138855</v>
       </c>
       <c r="H543" t="n">
         <v>40682</v>
@@ -16145,7 +16145,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H544" t="n">
         <v>20063</v>
@@ -16203,7 +16203,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>13.6696243286133</v>
+        <v>13.669623374939</v>
       </c>
       <c r="H546" t="n">
         <v>15340</v>
@@ -16319,7 +16319,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G550" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H550" t="n">
         <v>10006</v>
@@ -16348,7 +16348,7 @@
         <v>14.5</v>
       </c>
       <c r="G551" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H551" t="n">
         <v>11098</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416881561279</v>
+        <v>13.8416872024536</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16435,7 +16435,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G554" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H554" t="n">
         <v>25672</v>
@@ -16493,7 +16493,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H556" t="n">
         <v>13812</v>
@@ -16522,7 +16522,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H557" t="n">
         <v>24397</v>
@@ -16551,7 +16551,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H558" t="n">
         <v>27948</v>
@@ -16580,7 +16580,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H559" t="n">
         <v>22244</v>
@@ -16609,7 +16609,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H560" t="n">
         <v>16756</v>
@@ -16638,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H561" t="n">
         <v>10223</v>
@@ -16725,7 +16725,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G564" t="n">
-        <v>13.4975576400757</v>
+        <v>13.49755859375</v>
       </c>
       <c r="H564" t="n">
         <v>58797</v>
@@ -16754,7 +16754,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H565" t="n">
         <v>66135</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799266815186</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16841,7 +16841,7 @@
         <v>14.5</v>
       </c>
       <c r="G568" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H568" t="n">
         <v>46017</v>
@@ -16928,7 +16928,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H571" t="n">
         <v>178522</v>
@@ -16986,7 +16986,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>13.8034524917603</v>
+        <v>13.8034515380859</v>
       </c>
       <c r="H573" t="n">
         <v>66012</v>
@@ -17044,7 +17044,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H575" t="n">
         <v>33781</v>
@@ -17073,7 +17073,7 @@
         <v>14.5</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8608074188232</v>
+        <v>13.8608064651489</v>
       </c>
       <c r="H576" t="n">
         <v>20626</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17160,7 +17160,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005294799805</v>
+        <v>14.3005285263062</v>
       </c>
       <c r="H579" t="n">
         <v>77910</v>
@@ -17189,7 +17189,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G580" t="n">
-        <v>14.4725952148438</v>
+        <v>14.4725942611694</v>
       </c>
       <c r="H580" t="n">
         <v>84048</v>
@@ -17218,7 +17218,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G581" t="n">
-        <v>14.0137548446655</v>
+        <v>14.0137538909912</v>
       </c>
       <c r="H581" t="n">
         <v>92704</v>
@@ -17247,7 +17247,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1093463897705</v>
+        <v>14.1093454360962</v>
       </c>
       <c r="H582" t="n">
         <v>56656</v>
@@ -17334,7 +17334,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G585" t="n">
-        <v>14.2049379348755</v>
+        <v>14.2049369812012</v>
       </c>
       <c r="H585" t="n">
         <v>62831</v>
@@ -17392,7 +17392,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H587" t="n">
         <v>43952</v>
@@ -17421,7 +17421,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G588" t="n">
-        <v>13.9946365356445</v>
+        <v>13.9946355819702</v>
       </c>
       <c r="H588" t="n">
         <v>110884</v>
@@ -17479,7 +17479,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H590" t="n">
         <v>109158</v>
@@ -17537,7 +17537,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>13.707859992981</v>
+        <v>13.7078609466553</v>
       </c>
       <c r="H592" t="n">
         <v>66158</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137050628662</v>
+        <v>12.7137060165405</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17798,7 +17798,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H601" t="n">
         <v>36560</v>
@@ -17827,7 +17827,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H602" t="n">
         <v>51879</v>
@@ -17856,7 +17856,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G603" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H603" t="n">
         <v>43650</v>
@@ -17885,7 +17885,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G604" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H604" t="n">
         <v>96008</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17943,7 +17943,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.2548637390137</v>
+        <v>12.2548656463623</v>
       </c>
       <c r="H606" t="n">
         <v>57474</v>
@@ -17972,7 +17972,7 @@
         <v>13</v>
       </c>
       <c r="G607" t="n">
-        <v>12.4269304275513</v>
+        <v>12.426929473877</v>
       </c>
       <c r="H607" t="n">
         <v>33493</v>
@@ -18001,7 +18001,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G608" t="n">
-        <v>12.5798759460449</v>
+        <v>12.5798768997192</v>
       </c>
       <c r="H608" t="n">
         <v>23155</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H611" t="n">
         <v>86158</v>
@@ -18117,7 +18117,7 @@
         <v>13.5</v>
       </c>
       <c r="G612" t="n">
-        <v>12.9048881530762</v>
+        <v>12.9048891067505</v>
       </c>
       <c r="H612" t="n">
         <v>92138</v>
@@ -18175,7 +18175,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H614" t="n">
         <v>147836</v>
@@ -18407,7 +18407,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H622" t="n">
         <v>40402</v>
@@ -18436,7 +18436,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H623" t="n">
         <v>82380</v>
@@ -18465,7 +18465,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710590362549</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H624" t="n">
         <v>62905</v>
@@ -18494,7 +18494,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754684448242</v>
+        <v>12.6754693984985</v>
       </c>
       <c r="H625" t="n">
         <v>51174</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -36915,6 +36915,35 @@
         <v>51538</v>
       </c>
       <c r="I1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1261" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>12.7200002670288</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>80739</v>
+      </c>
+      <c r="I1261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954301834106</v>
+        <v>14.7954292297363</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846286773682</v>
+        <v>14.9846277236938</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -688,7 +688,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8711090087891</v>
+        <v>14.8711099624634</v>
       </c>
       <c r="H11" t="n">
         <v>77954</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548692703247</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899909973145</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899900436401</v>
+        <v>14.1899909973145</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819095611572</v>
+        <v>14.6819105148315</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -1094,7 +1094,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2278308868408</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H25" t="n">
         <v>54159</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547914505005</v>
+        <v>13.0547904968262</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1645,7 +1645,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H44" t="n">
         <v>70236</v>
@@ -1674,7 +1674,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G45" t="n">
-        <v>12.9412708282471</v>
+        <v>12.9412717819214</v>
       </c>
       <c r="H45" t="n">
         <v>41877</v>
@@ -1703,7 +1703,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>12.9791107177734</v>
+        <v>12.9791116714478</v>
       </c>
       <c r="H46" t="n">
         <v>54666</v>
@@ -1819,7 +1819,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G50" t="n">
-        <v>12.7520704269409</v>
+        <v>12.7520713806152</v>
       </c>
       <c r="H50" t="n">
         <v>24333</v>
@@ -1906,7 +1906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G53" t="n">
-        <v>11.6168718338013</v>
+        <v>11.616870880127</v>
       </c>
       <c r="H53" t="n">
         <v>55554</v>
@@ -1993,7 +1993,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H56" t="n">
         <v>71712</v>
@@ -2167,7 +2167,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H62" t="n">
         <v>17275</v>
@@ -2312,7 +2312,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H67" t="n">
         <v>16328</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2399,7 +2399,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655511856079</v>
+        <v>12.1655502319336</v>
       </c>
       <c r="H70" t="n">
         <v>77040</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2631,7 +2631,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H78" t="n">
         <v>9685</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951919555664</v>
+        <v>10.5951910018921</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2776,7 +2776,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>10.3303117752075</v>
+        <v>10.3303127288818</v>
       </c>
       <c r="H83" t="n">
         <v>41339</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465913772583</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -2979,7 +2979,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H90" t="n">
         <v>13547</v>
@@ -3211,7 +3211,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H98" t="n">
         <v>58338</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453319549561</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3675,7 +3675,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H114" t="n">
         <v>96370</v>
@@ -3762,7 +3762,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H117" t="n">
         <v>50078</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884914398193</v>
+        <v>11.5884923934937</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -4081,7 +4081,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H128" t="n">
         <v>17714</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979509353638</v>
+        <v>11.5979518890381</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4342,7 +4342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H137" t="n">
         <v>33734</v>
@@ -4371,7 +4371,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195909500122</v>
+        <v>11.9195919036865</v>
       </c>
       <c r="H138" t="n">
         <v>19683</v>
@@ -4516,7 +4516,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G143" t="n">
-        <v>12.0898704528809</v>
+        <v>12.0898714065552</v>
       </c>
       <c r="H143" t="n">
         <v>1847</v>
@@ -4545,7 +4545,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H144" t="n">
         <v>9829</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4719,7 +4719,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506904602051</v>
+        <v>12.2506914138794</v>
       </c>
       <c r="H150" t="n">
         <v>63375</v>
@@ -4748,7 +4748,7 @@
         <v>12.75</v>
       </c>
       <c r="G151" t="n">
-        <v>12.0614910125732</v>
+        <v>12.0614919662476</v>
       </c>
       <c r="H151" t="n">
         <v>41978</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4922,7 +4922,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H157" t="n">
         <v>25916</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.070951461792</v>
+        <v>12.0709505081177</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750106811523</v>
+        <v>12.175009727478</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.420970916748</v>
+        <v>12.4209718704224</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925905227661</v>
+        <v>12.3925914764404</v>
       </c>
       <c r="H181" t="n">
         <v>37878</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398509979248</v>
+        <v>11.7398500442505</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695705413818</v>
+        <v>11.5695714950562</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547117233276</v>
+        <v>11.6547107696533</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6256,7 +6256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033512115479</v>
+        <v>11.5033521652222</v>
       </c>
       <c r="H203" t="n">
         <v>16925</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452531814575</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6662,7 +6662,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G217" t="n">
-        <v>11.0871133804321</v>
+        <v>11.0871124267578</v>
       </c>
       <c r="H217" t="n">
         <v>62592</v>
@@ -6778,7 +6778,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789920806885</v>
+        <v>10.8789930343628</v>
       </c>
       <c r="H221" t="n">
         <v>10402</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -7097,7 +7097,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>10.0275917053223</v>
+        <v>10.0275926589966</v>
       </c>
       <c r="H232" t="n">
         <v>1928</v>
@@ -7126,7 +7126,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G233" t="n">
-        <v>10.037052154541</v>
+        <v>10.0370512008667</v>
       </c>
       <c r="H233" t="n">
         <v>3717</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083282470703</v>
+        <v>9.97083187103271</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055141448975</v>
+        <v>9.80055236816406</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7271,7 +7271,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G238" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H238" t="n">
         <v>13101</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7561,7 +7561,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G248" t="n">
-        <v>9.85731220245361</v>
+        <v>9.85731315612793</v>
       </c>
       <c r="H248" t="n">
         <v>19141</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7735,7 +7735,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917240142822</v>
+        <v>9.29917335510254</v>
       </c>
       <c r="H254" t="n">
         <v>10680</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465913772583</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100915908813</v>
+        <v>11.2100925445557</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -8112,7 +8112,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H267" t="n">
         <v>6337</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439121246338</v>
+        <v>11.8439111709595</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8286,7 +8286,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060712814331</v>
+        <v>11.8060703277588</v>
       </c>
       <c r="H273" t="n">
         <v>9792</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411911010742</v>
+        <v>11.5411920547485</v>
       </c>
       <c r="H275" t="n">
         <v>6258</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992919921875</v>
+        <v>11.3992929458618</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465913772583</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087514877319</v>
+        <v>11.4087524414062</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8866,7 +8866,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885303497314</v>
+        <v>12.2885313034058</v>
       </c>
       <c r="H293" t="n">
         <v>19905</v>
@@ -8895,7 +8895,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H294" t="n">
         <v>39678</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750106811523</v>
+        <v>12.175009727478</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -8953,7 +8953,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.1371717453003</v>
+        <v>12.137170791626</v>
       </c>
       <c r="H296" t="n">
         <v>113027</v>
@@ -8982,7 +8982,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3074522018433</v>
+        <v>12.3074512481689</v>
       </c>
       <c r="H297" t="n">
         <v>1507</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9185,7 +9185,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1939306259155</v>
+        <v>12.1939315795898</v>
       </c>
       <c r="H304" t="n">
         <v>1793</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H312" t="n">
         <v>60848</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9504,7 +9504,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H315" t="n">
         <v>31712</v>
@@ -9649,7 +9649,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966905593872</v>
+        <v>13.1966896057129</v>
       </c>
       <c r="H320" t="n">
         <v>115939</v>
@@ -9678,7 +9678,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G321" t="n">
-        <v>13.3102102279663</v>
+        <v>13.3102111816406</v>
       </c>
       <c r="H321" t="n">
         <v>28336</v>
@@ -9794,7 +9794,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H325" t="n">
         <v>89076</v>
@@ -9823,7 +9823,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075309753418</v>
+        <v>13.7075300216675</v>
       </c>
       <c r="H326" t="n">
         <v>108302</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467100143433</v>
+        <v>13.5467090606689</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10055,7 +10055,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399297714233</v>
+        <v>13.1399307250977</v>
       </c>
       <c r="H334" t="n">
         <v>35387</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088302612305</v>
+        <v>12.8088312149048</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453310012817</v>
+        <v>13.0453319549561</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10548,7 +10548,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426498413086</v>
+        <v>13.4426488876343</v>
       </c>
       <c r="H351" t="n">
         <v>59237</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548303604126</v>
+        <v>13.7548294067383</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10635,7 +10635,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H354" t="n">
         <v>47384</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763906478882</v>
+        <v>12.6763896942139</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10693,7 +10693,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.5817909240723</v>
+        <v>12.5817918777466</v>
       </c>
       <c r="H356" t="n">
         <v>162095</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.591251373291</v>
+        <v>12.5912504196167</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10751,7 +10751,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>12.6196298599243</v>
+        <v>12.6196308135986</v>
       </c>
       <c r="H358" t="n">
         <v>55009</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.7926692962646</v>
+        <v>13.792670249939</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -10983,7 +10983,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>14.2278308868408</v>
+        <v>14.2278299331665</v>
       </c>
       <c r="H366" t="n">
         <v>130359</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548692703247</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11128,7 +11128,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G371" t="n">
-        <v>15.344108581543</v>
+        <v>15.3441076278687</v>
       </c>
       <c r="H371" t="n">
         <v>38672</v>
@@ -36944,6 +36944,35 @@
         <v>80739</v>
       </c>
       <c r="I1261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1262" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>12.8599996566772</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>12.8599996566772</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>12.5600004196167</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>12.5600004196167</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>39909</v>
+      </c>
+      <c r="I1262" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387083053589</v>
+        <v>15.4387073516846</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954292297363</v>
+        <v>14.7954301834106</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -514,7 +514,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1927480697632</v>
+        <v>15.1927490234375</v>
       </c>
       <c r="H5" t="n">
         <v>64538</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846277236938</v>
+        <v>14.9846286773682</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -601,7 +601,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H8" t="n">
         <v>69786</v>
@@ -659,7 +659,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008295059204</v>
+        <v>14.7008285522461</v>
       </c>
       <c r="H10" t="n">
         <v>75622</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.454870223999</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899909973145</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -833,7 +833,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359502792358</v>
+        <v>14.4359493255615</v>
       </c>
       <c r="H16" t="n">
         <v>13170</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899909973145</v>
+        <v>14.1899890899658</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -891,7 +891,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.0007905960083</v>
+        <v>14.000789642334</v>
       </c>
       <c r="H18" t="n">
         <v>7979</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819105148315</v>
+        <v>14.6819095611572</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -978,7 +978,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H21" t="n">
         <v>20677</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1152,7 +1152,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115901947021</v>
+        <v>13.8115911483765</v>
       </c>
       <c r="H27" t="n">
         <v>47594</v>
@@ -1210,7 +1210,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G29" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250709533691</v>
       </c>
       <c r="H29" t="n">
         <v>69505</v>
@@ -1239,7 +1239,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250709533691</v>
       </c>
       <c r="H30" t="n">
         <v>34219</v>
@@ -1297,7 +1297,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>13.622389793396</v>
+        <v>13.6223888397217</v>
       </c>
       <c r="H32" t="n">
         <v>22783</v>
@@ -1413,7 +1413,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H36" t="n">
         <v>8817</v>
@@ -1442,7 +1442,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007507324219</v>
+        <v>13.3007497787476</v>
       </c>
       <c r="H37" t="n">
         <v>21560</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547904968262</v>
+        <v>13.0547895431519</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1529,7 +1529,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H40" t="n">
         <v>41427</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007108688354</v>
+        <v>12.6007099151611</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1645,7 +1645,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H44" t="n">
         <v>70236</v>
@@ -1674,7 +1674,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G45" t="n">
-        <v>12.9412717819214</v>
+        <v>12.9412698745728</v>
       </c>
       <c r="H45" t="n">
         <v>41877</v>
@@ -1703,7 +1703,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>12.9791116714478</v>
+        <v>12.9791107177734</v>
       </c>
       <c r="H46" t="n">
         <v>54666</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9034299850464</v>
+        <v>12.903431892395</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1790,7 +1790,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H49" t="n">
         <v>62308</v>
@@ -1819,7 +1819,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G50" t="n">
-        <v>12.7520713806152</v>
+        <v>12.7520704269409</v>
       </c>
       <c r="H50" t="n">
         <v>24333</v>
@@ -1877,7 +1877,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817529678345</v>
       </c>
       <c r="H52" t="n">
         <v>30733</v>
@@ -2051,7 +2051,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277122497559</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H58" t="n">
         <v>38827</v>
@@ -2080,7 +2080,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277122497559</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H59" t="n">
         <v>23840</v>
@@ -2109,7 +2109,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H60" t="n">
         <v>20661</v>
@@ -2138,7 +2138,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358316421509</v>
+        <v>12.3358306884766</v>
       </c>
       <c r="H61" t="n">
         <v>27576</v>
@@ -2167,7 +2167,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H62" t="n">
         <v>17275</v>
@@ -2225,7 +2225,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G64" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H64" t="n">
         <v>59204</v>
@@ -2254,7 +2254,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1844711303711</v>
+        <v>12.1844720840454</v>
       </c>
       <c r="H65" t="n">
         <v>17790</v>
@@ -2341,7 +2341,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G68" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H68" t="n">
         <v>28303</v>
@@ -2370,7 +2370,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277122497559</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H69" t="n">
         <v>21775</v>
@@ -2399,7 +2399,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G70" t="n">
-        <v>12.1655502319336</v>
+        <v>12.1655511856079</v>
       </c>
       <c r="H70" t="n">
         <v>77040</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2486,7 +2486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G73" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H73" t="n">
         <v>17505</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2602,7 +2602,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817529678345</v>
       </c>
       <c r="H77" t="n">
         <v>19525</v>
@@ -2631,7 +2631,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H78" t="n">
         <v>9685</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006311416626</v>
+        <v>11.2006320953369</v>
       </c>
       <c r="H79" t="n">
         <v>30466</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763118743896</v>
+        <v>11.2763109207153</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951910018921</v>
+        <v>10.5951919555664</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005922317505</v>
+        <v>10.5005931854248</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.446590423584</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2921,7 +2921,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>11.6736307144165</v>
+        <v>11.6736316680908</v>
       </c>
       <c r="H88" t="n">
         <v>118173</v>
@@ -2950,7 +2950,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H89" t="n">
         <v>24361</v>
@@ -2979,7 +2979,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H90" t="n">
         <v>13547</v>
@@ -3066,7 +3066,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H93" t="n">
         <v>15977</v>
@@ -3153,7 +3153,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H96" t="n">
         <v>230549</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276714324951</v>
+        <v>11.4276723861694</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.5506505966187</v>
+        <v>11.5506525039673</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3327,7 +3327,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H102" t="n">
         <v>39681</v>
@@ -3356,7 +3356,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H103" t="n">
         <v>112096</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3443,7 +3443,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H106" t="n">
         <v>19298</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.5506505966187</v>
+        <v>11.5506525039673</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3588,7 +3588,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817529678345</v>
       </c>
       <c r="H111" t="n">
         <v>18000</v>
@@ -3617,7 +3617,7 @@
         <v>13.5</v>
       </c>
       <c r="G112" t="n">
-        <v>12.7709913253784</v>
+        <v>12.7709903717041</v>
       </c>
       <c r="H112" t="n">
         <v>246829</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453319549561</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3675,7 +3675,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H114" t="n">
         <v>96370</v>
@@ -3704,7 +3704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H115" t="n">
         <v>10754</v>
@@ -3733,7 +3733,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H116" t="n">
         <v>29281</v>
@@ -3762,7 +3762,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H117" t="n">
         <v>50078</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115104675293</v>
+        <v>12.4115114212036</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3820,7 +3820,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H119" t="n">
         <v>57830</v>
@@ -3849,7 +3849,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033920288086</v>
       </c>
       <c r="H120" t="n">
         <v>18650</v>
@@ -3907,7 +3907,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>11.6641721725464</v>
+        <v>11.6641712188721</v>
       </c>
       <c r="H122" t="n">
         <v>38398</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.5884923934937</v>
+        <v>11.588490486145</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4052,7 +4052,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033920288086</v>
       </c>
       <c r="H127" t="n">
         <v>53178</v>
@@ -4110,7 +4110,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H129" t="n">
         <v>100100</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4197,7 +4197,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.2195501327515</v>
+        <v>11.2195510864258</v>
       </c>
       <c r="H132" t="n">
         <v>26501</v>
@@ -4226,7 +4226,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G133" t="n">
-        <v>10.9168329238892</v>
+        <v>10.9168319702148</v>
       </c>
       <c r="H133" t="n">
         <v>53035</v>
@@ -4255,7 +4255,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>11.1627922058105</v>
+        <v>11.1627931594849</v>
       </c>
       <c r="H134" t="n">
         <v>35125</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979518890381</v>
+        <v>11.5979509353638</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4313,7 +4313,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G136" t="n">
-        <v>11.5317306518555</v>
+        <v>11.5317316055298</v>
       </c>
       <c r="H136" t="n">
         <v>34461</v>
@@ -4342,7 +4342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303915023804</v>
+        <v>11.7303905487061</v>
       </c>
       <c r="H137" t="n">
         <v>33734</v>
@@ -4371,7 +4371,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>11.9195919036865</v>
+        <v>11.9195909500122</v>
       </c>
       <c r="H138" t="n">
         <v>19683</v>
@@ -4429,7 +4429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033920288086</v>
       </c>
       <c r="H140" t="n">
         <v>24892</v>
@@ -4458,7 +4458,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H141" t="n">
         <v>37220</v>
@@ -4487,7 +4487,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H142" t="n">
         <v>15956</v>
@@ -4545,7 +4545,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H144" t="n">
         <v>9829</v>
@@ -4574,7 +4574,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979898452759</v>
+        <v>12.2979907989502</v>
       </c>
       <c r="H145" t="n">
         <v>14891</v>
@@ -4632,7 +4632,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H147" t="n">
         <v>23423</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4690,7 +4690,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H149" t="n">
         <v>57560</v>
@@ -4719,7 +4719,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G150" t="n">
-        <v>12.2506914138794</v>
+        <v>12.2506904602051</v>
       </c>
       <c r="H150" t="n">
         <v>63375</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642101287842</v>
+        <v>12.3642110824585</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4806,7 +4806,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H153" t="n">
         <v>40723</v>
@@ -4864,7 +4864,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682703018188</v>
+        <v>12.4682712554932</v>
       </c>
       <c r="H155" t="n">
         <v>41701</v>
@@ -4893,7 +4893,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G156" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H156" t="n">
         <v>44631</v>
@@ -4951,7 +4951,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G158" t="n">
-        <v>12.0709505081177</v>
+        <v>12.070951461792</v>
       </c>
       <c r="H158" t="n">
         <v>20475</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5009,7 +5009,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>12.2601509094238</v>
+        <v>12.2601499557495</v>
       </c>
       <c r="H160" t="n">
         <v>44574</v>
@@ -5038,7 +5038,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277122497559</v>
+        <v>12.1277103424072</v>
       </c>
       <c r="H161" t="n">
         <v>34152</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.8628311157227</v>
+        <v>11.862832069397</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5183,7 +5183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H166" t="n">
         <v>9153</v>
@@ -5212,7 +5212,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.796612739563</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H167" t="n">
         <v>6760</v>
@@ -5299,7 +5299,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.316912651062</v>
+        <v>12.3169107437134</v>
       </c>
       <c r="H170" t="n">
         <v>6203</v>
@@ -5328,7 +5328,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>12.2412300109863</v>
+        <v>12.2412309646606</v>
       </c>
       <c r="H171" t="n">
         <v>17308</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.175009727478</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5531,7 +5531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223110198975</v>
+        <v>12.2223119735718</v>
       </c>
       <c r="H178" t="n">
         <v>16515</v>
@@ -5560,7 +5560,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G179" t="n">
-        <v>12.3547525405884</v>
+        <v>12.3547506332397</v>
       </c>
       <c r="H179" t="n">
         <v>21056</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209718704224</v>
+        <v>12.4209699630737</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5647,7 +5647,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H182" t="n">
         <v>17429</v>
@@ -5676,7 +5676,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G183" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H183" t="n">
         <v>26678</v>
@@ -5734,7 +5734,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.4493503570557</v>
+        <v>12.44935131073</v>
       </c>
       <c r="H185" t="n">
         <v>18304</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5850,7 +5850,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.20339012146</v>
+        <v>12.2033920288086</v>
       </c>
       <c r="H189" t="n">
         <v>22438</v>
@@ -5908,7 +5908,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G191" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817529678345</v>
       </c>
       <c r="H191" t="n">
         <v>5115</v>
@@ -5937,7 +5937,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H192" t="n">
         <v>9607</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -5995,7 +5995,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G194" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H194" t="n">
         <v>5770</v>
@@ -6024,7 +6024,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H195" t="n">
         <v>9323</v>
@@ -6082,7 +6082,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G197" t="n">
-        <v>11.7398500442505</v>
+        <v>11.7398509979248</v>
       </c>
       <c r="H197" t="n">
         <v>21094</v>
@@ -6111,7 +6111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830911636353</v>
+        <v>11.6830921173096</v>
       </c>
       <c r="H198" t="n">
         <v>9999</v>
@@ -6140,7 +6140,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.62633228302</v>
+        <v>11.6263303756714</v>
       </c>
       <c r="H199" t="n">
         <v>12593</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695714950562</v>
+        <v>11.5695724487305</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6198,7 +6198,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G201" t="n">
-        <v>11.7209310531616</v>
+        <v>11.7209320068359</v>
       </c>
       <c r="H201" t="n">
         <v>4105</v>
@@ -6227,7 +6227,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>11.6547107696533</v>
+        <v>11.6547117233276</v>
       </c>
       <c r="H202" t="n">
         <v>11030</v>
@@ -6256,7 +6256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5033521652222</v>
+        <v>11.5033512115479</v>
       </c>
       <c r="H203" t="n">
         <v>16925</v>
@@ -6285,7 +6285,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7776908874512</v>
+        <v>11.7776918411255</v>
       </c>
       <c r="H204" t="n">
         <v>5041</v>
@@ -6343,7 +6343,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.692551612854</v>
+        <v>11.6925506591797</v>
       </c>
       <c r="H206" t="n">
         <v>17437</v>
@@ -6401,7 +6401,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G208" t="n">
-        <v>11.8817520141602</v>
+        <v>11.8817529678345</v>
       </c>
       <c r="H208" t="n">
         <v>15504</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452522277832</v>
+        <v>11.6452512741089</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6459,7 +6459,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749717712402</v>
+        <v>11.4749727249146</v>
       </c>
       <c r="H210" t="n">
         <v>12812</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938907623291</v>
+        <v>11.4938917160034</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6691,7 +6691,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587310791016</v>
+        <v>11.0587320327759</v>
       </c>
       <c r="H218" t="n">
         <v>37998</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208911895752</v>
+        <v>11.0208921432495</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6778,7 +6778,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789930343628</v>
+        <v>10.8789920806885</v>
       </c>
       <c r="H221" t="n">
         <v>10402</v>
@@ -6836,7 +6836,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1221923828125</v>
+        <v>10.1221933364868</v>
       </c>
       <c r="H223" t="n">
         <v>18441</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316528320312</v>
+        <v>10.1316518783569</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93299293518066</v>
+        <v>9.93299198150635</v>
       </c>
       <c r="H228" t="n">
         <v>31580</v>
@@ -7010,7 +7010,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G229" t="n">
-        <v>9.81947231292725</v>
+        <v>9.81947326660156</v>
       </c>
       <c r="H229" t="n">
         <v>68277</v>
@@ -7039,7 +7039,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>9.88569259643555</v>
+        <v>9.88569355010986</v>
       </c>
       <c r="H230" t="n">
         <v>38389</v>
@@ -7068,7 +7068,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>10.1221923828125</v>
+        <v>10.1221933364868</v>
       </c>
       <c r="H231" t="n">
         <v>19711</v>
@@ -7184,7 +7184,7 @@
         <v>10.5</v>
       </c>
       <c r="G235" t="n">
-        <v>9.93299293518066</v>
+        <v>9.93299198150635</v>
       </c>
       <c r="H235" t="n">
         <v>4261</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055236816406</v>
+        <v>9.80055332183838</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032733917236</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032724380493</v>
+        <v>10.1032733917236</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7503,7 +7503,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789522171021</v>
+        <v>10.1789531707764</v>
       </c>
       <c r="H246" t="n">
         <v>25506</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621364593506</v>
+        <v>9.52621269226074</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729370117188</v>
+        <v>9.50729274749756</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7648,7 +7648,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647274017334</v>
+        <v>9.34647369384766</v>
       </c>
       <c r="H251" t="n">
         <v>15863</v>
@@ -7677,7 +7677,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>9.33701324462891</v>
+        <v>9.33701229095459</v>
       </c>
       <c r="H252" t="n">
         <v>8169</v>
@@ -7735,7 +7735,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917335510254</v>
+        <v>9.29917240142822</v>
       </c>
       <c r="H254" t="n">
         <v>10680</v>
@@ -7764,7 +7764,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.9613733291626</v>
+        <v>9.96137237548828</v>
       </c>
       <c r="H255" t="n">
         <v>77427</v>
@@ -7793,7 +7793,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G256" t="n">
-        <v>10.8884515762329</v>
+        <v>10.8884525299072</v>
       </c>
       <c r="H256" t="n">
         <v>68311</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.446590423584</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7938,7 +7938,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668514251709</v>
+        <v>11.2668523788452</v>
       </c>
       <c r="H261" t="n">
         <v>11841</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952318191528</v>
+        <v>11.2952308654785</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -7996,7 +7996,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290115356445</v>
+        <v>11.2290124893188</v>
       </c>
       <c r="H263" t="n">
         <v>3066</v>
@@ -8141,7 +8141,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330717086792</v>
+        <v>11.3330707550049</v>
       </c>
       <c r="H268" t="n">
         <v>7750</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.484432220459</v>
+        <v>11.4844312667847</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439111709595</v>
+        <v>11.8439121246338</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8373,7 +8373,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G276" t="n">
-        <v>11.2479314804077</v>
+        <v>11.247932434082</v>
       </c>
       <c r="H276" t="n">
         <v>32729</v>
@@ -8402,7 +8402,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790309906006</v>
+        <v>11.5790319442749</v>
       </c>
       <c r="H277" t="n">
         <v>39974</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992929458618</v>
+        <v>11.3992910385132</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.446590423584</v>
+        <v>11.4465923309326</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8605,7 +8605,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.796612739563</v>
+        <v>11.7966117858887</v>
       </c>
       <c r="H284" t="n">
         <v>13107</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101305007935</v>
+        <v>11.9101314544678</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8692,7 +8692,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G287" t="n">
-        <v>12.0993309020996</v>
+        <v>12.0993318557739</v>
       </c>
       <c r="H287" t="n">
         <v>7503</v>
@@ -8750,7 +8750,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.212851524353</v>
+        <v>12.2128505706787</v>
       </c>
       <c r="H289" t="n">
         <v>18611</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8895,7 +8895,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398908615112</v>
+        <v>12.4398899078369</v>
       </c>
       <c r="H294" t="n">
         <v>39678</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.175009727478</v>
+        <v>12.1750116348267</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -9040,7 +9040,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331115722656</v>
+        <v>12.0331106185913</v>
       </c>
       <c r="H299" t="n">
         <v>6219</v>
@@ -9098,7 +9098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.9006719589233</v>
+        <v>11.900671005249</v>
       </c>
       <c r="H301" t="n">
         <v>4323</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087923049927</v>
+        <v>12.1087913513184</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9214,7 +9214,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>12.3547525405884</v>
+        <v>12.3547506332397</v>
       </c>
       <c r="H305" t="n">
         <v>7507</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141906738281</v>
+        <v>12.0141897201538</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9359,7 +9359,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831300735474</v>
+        <v>12.3831310272217</v>
       </c>
       <c r="H310" t="n">
         <v>86708</v>
@@ -9388,7 +9388,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H311" t="n">
         <v>118963</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H312" t="n">
         <v>60848</v>
@@ -9446,7 +9446,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H313" t="n">
         <v>15378</v>
@@ -9504,7 +9504,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.86559009552</v>
+        <v>12.8655910491943</v>
       </c>
       <c r="H315" t="n">
         <v>31712</v>
@@ -9562,7 +9562,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G317" t="n">
-        <v>13.0642518997192</v>
+        <v>13.0642509460449</v>
       </c>
       <c r="H317" t="n">
         <v>729414</v>
@@ -9591,7 +9591,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601907730103</v>
+        <v>12.9601898193359</v>
       </c>
       <c r="H318" t="n">
         <v>114421</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182907104492</v>
+        <v>12.8182916641235</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9649,7 +9649,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966896057129</v>
+        <v>13.1966905593872</v>
       </c>
       <c r="H320" t="n">
         <v>115939</v>
@@ -9678,7 +9678,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G321" t="n">
-        <v>13.3102111816406</v>
+        <v>13.3102102279663</v>
       </c>
       <c r="H321" t="n">
         <v>28336</v>
@@ -9765,7 +9765,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G324" t="n">
-        <v>13.2250699996948</v>
+        <v>13.2250709533691</v>
       </c>
       <c r="H324" t="n">
         <v>19992</v>
@@ -9794,7 +9794,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H325" t="n">
         <v>89076</v>
@@ -9823,7 +9823,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075300216675</v>
+        <v>13.7075290679932</v>
       </c>
       <c r="H326" t="n">
         <v>108302</v>
@@ -9881,7 +9881,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.4804906845093</v>
+        <v>13.480489730835</v>
       </c>
       <c r="H328" t="n">
         <v>127967</v>
@@ -9910,7 +9910,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385896682739</v>
+        <v>13.3385906219482</v>
       </c>
       <c r="H329" t="n">
         <v>198840</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467090606689</v>
+        <v>13.5467109680176</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10026,7 +10026,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912912368774</v>
+        <v>13.2912902832031</v>
       </c>
       <c r="H333" t="n">
         <v>23303</v>
@@ -10084,7 +10084,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H335" t="n">
         <v>11048</v>
@@ -10142,7 +10142,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8088312149048</v>
+        <v>12.8088302612305</v>
       </c>
       <c r="H337" t="n">
         <v>37780</v>
@@ -10171,7 +10171,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142295837402</v>
+        <v>12.7142305374146</v>
       </c>
       <c r="H338" t="n">
         <v>27898</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439519882202</v>
+        <v>12.5439510345459</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10229,7 +10229,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.7993698120117</v>
+        <v>12.799370765686</v>
       </c>
       <c r="H340" t="n">
         <v>39580</v>
@@ -10258,7 +10258,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8372116088867</v>
+        <v>12.8372106552124</v>
       </c>
       <c r="H341" t="n">
         <v>71543</v>
@@ -10316,7 +10316,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5723304748535</v>
+        <v>12.5723314285278</v>
       </c>
       <c r="H343" t="n">
         <v>71453</v>
@@ -10374,7 +10374,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>13.5088691711426</v>
+        <v>13.5088701248169</v>
       </c>
       <c r="H345" t="n">
         <v>166787</v>
@@ -10403,7 +10403,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.7642908096313</v>
+        <v>13.764289855957</v>
       </c>
       <c r="H346" t="n">
         <v>87295</v>
@@ -10461,7 +10461,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629098892212</v>
       </c>
       <c r="H348" t="n">
         <v>46007</v>
@@ -10490,7 +10490,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629108428955</v>
+        <v>13.2629098892212</v>
       </c>
       <c r="H349" t="n">
         <v>74321</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453319549561</v>
+        <v>13.0453300476074</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10548,7 +10548,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4426488876343</v>
+        <v>13.4426498413086</v>
       </c>
       <c r="H351" t="n">
         <v>59237</v>
@@ -10577,7 +10577,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G352" t="n">
-        <v>13.726450920105</v>
+        <v>13.7264499664307</v>
       </c>
       <c r="H352" t="n">
         <v>43550</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548294067383</v>
+        <v>13.7548303604126</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10635,7 +10635,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.3858890533447</v>
+        <v>13.385890007019</v>
       </c>
       <c r="H354" t="n">
         <v>47384</v>
@@ -10664,7 +10664,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>12.6763896942139</v>
+        <v>12.6763906478882</v>
       </c>
       <c r="H355" t="n">
         <v>403446</v>
@@ -10693,7 +10693,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.5817918777466</v>
+        <v>12.5817909240723</v>
       </c>
       <c r="H356" t="n">
         <v>162095</v>
@@ -10722,7 +10722,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>12.5912504196167</v>
+        <v>12.591251373291</v>
       </c>
       <c r="H357" t="n">
         <v>126277</v>
@@ -10809,7 +10809,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115493774414</v>
+        <v>13.1115503311157</v>
       </c>
       <c r="H360" t="n">
         <v>130944</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764305114746</v>
+        <v>13.3764295578003</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10867,7 +10867,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737512588501</v>
+        <v>13.7737503051758</v>
       </c>
       <c r="H362" t="n">
         <v>69104</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845897674561</v>
+        <v>14.2845888137817</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.454870223999</v>
+        <v>14.4548692703247</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792284011841</v>
+        <v>15.0792293548584</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11331,7 +11331,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.662989616394</v>
+        <v>14.6629886627197</v>
       </c>
       <c r="H378" t="n">
         <v>85275</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11476,7 +11476,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H383" t="n">
         <v>42204</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11679,7 +11679,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843811035156</v>
+        <v>15.0843820571899</v>
       </c>
       <c r="H390" t="n">
         <v>50895</v>
@@ -11708,7 +11708,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H391" t="n">
         <v>32365</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020139694214</v>
+        <v>14.7020149230957</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.007908821106</v>
+        <v>15.0079078674316</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11911,7 +11911,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.9505529403687</v>
+        <v>14.950553894043</v>
       </c>
       <c r="H398" t="n">
         <v>35897</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593688964844</v>
+        <v>14.7593698501587</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12201,7 +12201,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108308792114</v>
+        <v>14.5108318328857</v>
       </c>
       <c r="H408" t="n">
         <v>38004</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064233779907</v>
+        <v>14.6064224243164</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12346,7 +12346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H413" t="n">
         <v>34048</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446590423584</v>
+        <v>14.6446599960327</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12404,7 +12404,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255407333374</v>
+        <v>14.6255416870117</v>
       </c>
       <c r="H415" t="n">
         <v>18337</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299491882324</v>
+        <v>14.5299501419067</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1034994125366</v>
+        <v>15.1035003662109</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12781,7 +12781,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520374298096</v>
+        <v>15.3520383834839</v>
       </c>
       <c r="H428" t="n">
         <v>49360</v>
@@ -12839,7 +12839,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G430" t="n">
-        <v>15.1799726486206</v>
+        <v>15.1799736022949</v>
       </c>
       <c r="H430" t="n">
         <v>15809</v>
@@ -12897,7 +12897,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H432" t="n">
         <v>28274</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226177215576</v>
+        <v>15.1226186752319</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13071,7 +13071,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.8358430862427</v>
+        <v>14.835844039917</v>
       </c>
       <c r="H438" t="n">
         <v>18515</v>
@@ -13100,7 +13100,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417360305786</v>
+        <v>15.1417369842529</v>
       </c>
       <c r="H439" t="n">
         <v>30668</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902750015259</v>
+        <v>15.3902759552002</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13216,7 +13216,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755641937256</v>
+        <v>15.2755651473999</v>
       </c>
       <c r="H443" t="n">
         <v>45829</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563989639282</v>
+        <v>13.9563999176025</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13419,7 +13419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711088180542</v>
+        <v>14.0711097717285</v>
       </c>
       <c r="H450" t="n">
         <v>16818</v>
@@ -13680,7 +13680,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H459" t="n">
         <v>13373</v>
@@ -13709,7 +13709,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431257247925</v>
+        <v>12.9431247711182</v>
       </c>
       <c r="H460" t="n">
         <v>31924</v>
@@ -13738,7 +13738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H461" t="n">
         <v>47646</v>
@@ -13767,7 +13767,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H462" t="n">
         <v>24475</v>
@@ -13796,7 +13796,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H463" t="n">
         <v>22702</v>
@@ -13825,7 +13825,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666524887085</v>
+        <v>12.8666515350342</v>
       </c>
       <c r="H464" t="n">
         <v>16431</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034036636353</v>
+        <v>12.5034027099609</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14144,7 +14144,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H475" t="n">
         <v>61238</v>
@@ -14202,7 +14202,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533802032471</v>
+        <v>11.8533792495728</v>
       </c>
       <c r="H477" t="n">
         <v>44549</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14289,7 +14289,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.9872074127197</v>
+        <v>11.987208366394</v>
       </c>
       <c r="H480" t="n">
         <v>47163</v>
@@ -14318,7 +14318,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.063681602478</v>
+        <v>12.0636806488037</v>
       </c>
       <c r="H481" t="n">
         <v>28977</v>
@@ -14347,7 +14347,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.025444984436</v>
+        <v>12.0254440307617</v>
       </c>
       <c r="H482" t="n">
         <v>53386</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.2739839553833</v>
+        <v>12.273983001709</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14463,7 +14463,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H486" t="n">
         <v>45367</v>
@@ -14492,7 +14492,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.2931022644043</v>
+        <v>12.29310131073</v>
       </c>
       <c r="H487" t="n">
         <v>28990</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181135177612</v>
+        <v>12.6181125640869</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151435852051</v>
+        <v>11.8151416778564</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960252761841</v>
+        <v>11.7960243225098</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14811,7 +14811,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239595413208</v>
+        <v>11.6239585876465</v>
       </c>
       <c r="H498" t="n">
         <v>38500</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.2166290283203</v>
+        <v>12.216628074646</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14898,7 +14898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.3313388824463</v>
+        <v>12.331337928772</v>
       </c>
       <c r="H501" t="n">
         <v>67973</v>
@@ -14956,7 +14956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H503" t="n">
         <v>36066</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15101,7 +15101,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.3446111679077</v>
+        <v>13.344612121582</v>
       </c>
       <c r="H508" t="n">
         <v>57867</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H512" t="n">
         <v>20590</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299013137817</v>
+        <v>13.2299022674561</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15420,7 +15420,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H519" t="n">
         <v>40078</v>
@@ -15449,7 +15449,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H520" t="n">
         <v>21758</v>
@@ -15478,7 +15478,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H521" t="n">
         <v>64754</v>
@@ -15507,7 +15507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.4593210220337</v>
+        <v>13.459321975708</v>
       </c>
       <c r="H522" t="n">
         <v>13016</v>
@@ -15565,7 +15565,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.4402027130127</v>
+        <v>13.440203666687</v>
       </c>
       <c r="H524" t="n">
         <v>10410</v>
@@ -15710,7 +15710,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725463867188</v>
+        <v>13.1725454330444</v>
       </c>
       <c r="H529" t="n">
         <v>14580</v>
@@ -15884,7 +15884,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H535" t="n">
         <v>118515</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16000,7 +16000,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H539" t="n">
         <v>78221</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16116,7 +16116,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.593150138855</v>
+        <v>13.5931510925293</v>
       </c>
       <c r="H543" t="n">
         <v>40682</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416872024536</v>
+        <v>13.8416891098022</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16406,7 +16406,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225698471069</v>
+        <v>13.8225708007812</v>
       </c>
       <c r="H553" t="n">
         <v>12102</v>
@@ -16493,7 +16493,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H556" t="n">
         <v>13812</v>
@@ -16522,7 +16522,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H557" t="n">
         <v>24397</v>
@@ -16551,7 +16551,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.4019660949707</v>
+        <v>13.401967048645</v>
       </c>
       <c r="H558" t="n">
         <v>27948</v>
@@ -16580,7 +16580,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H559" t="n">
         <v>22244</v>
@@ -16609,7 +16609,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H560" t="n">
         <v>16756</v>
@@ -16638,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H561" t="n">
         <v>10223</v>
@@ -16754,7 +16754,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H565" t="n">
         <v>66135</v>
@@ -16783,7 +16783,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.726978302002</v>
+        <v>13.7269792556763</v>
       </c>
       <c r="H566" t="n">
         <v>38521</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799247741699</v>
+        <v>13.8799257278442</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16899,7 +16899,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H570" t="n">
         <v>219173</v>
@@ -16928,7 +16928,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H571" t="n">
         <v>178522</v>
@@ -17044,7 +17044,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843332290649</v>
+        <v>13.7843341827393</v>
       </c>
       <c r="H575" t="n">
         <v>33781</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681867599487</v>
+        <v>14.5681858062744</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622919082642</v>
+        <v>14.2622928619385</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17160,7 +17160,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005285263062</v>
+        <v>14.3005294799805</v>
       </c>
       <c r="H579" t="n">
         <v>77910</v>
@@ -17479,7 +17479,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.3828477859497</v>
+        <v>13.382848739624</v>
       </c>
       <c r="H590" t="n">
         <v>109158</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137060165405</v>
+        <v>12.7137050628662</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17740,7 +17740,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H599" t="n">
         <v>76279</v>
@@ -17798,7 +17798,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328243255615</v>
+        <v>12.7328233718872</v>
       </c>
       <c r="H601" t="n">
         <v>36560</v>
@@ -17827,7 +17827,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092975616455</v>
+        <v>12.8092966079712</v>
       </c>
       <c r="H602" t="n">
         <v>51879</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.3122205734253</v>
+        <v>12.312219619751</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17943,7 +17943,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.2548656463623</v>
+        <v>12.2548637390137</v>
       </c>
       <c r="H606" t="n">
         <v>57474</v>
@@ -18030,7 +18030,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H609" t="n">
         <v>88111</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.2681379318237</v>
+        <v>13.268138885498</v>
       </c>
       <c r="H611" t="n">
         <v>86158</v>
@@ -18175,7 +18175,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637285232544</v>
+        <v>13.3637294769287</v>
       </c>
       <c r="H614" t="n">
         <v>147836</v>
@@ -18262,7 +18262,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387172698975</v>
+        <v>13.0387182235718</v>
       </c>
       <c r="H617" t="n">
         <v>46574</v>
@@ -18407,7 +18407,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710609436035</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H622" t="n">
         <v>40402</v>
@@ -18436,7 +18436,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710609436035</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H623" t="n">
         <v>82380</v>
@@ -18465,7 +18465,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710609436035</v>
+        <v>12.7710599899292</v>
       </c>
       <c r="H624" t="n">
         <v>62905</v>
@@ -18494,7 +18494,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754693984985</v>
+        <v>12.6754684448242</v>
       </c>
       <c r="H625" t="n">
         <v>51174</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563510894775</v>
+        <v>12.6563501358032</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18668,7 +18668,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284158706665</v>
+        <v>12.8284149169922</v>
       </c>
       <c r="H631" t="n">
         <v>69447</v>
@@ -18784,7 +18784,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H635" t="n">
         <v>124717</v>
@@ -18871,7 +18871,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H638" t="n">
         <v>21080</v>
@@ -18900,7 +18900,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H639" t="n">
         <v>40704</v>
@@ -18929,7 +18929,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H640" t="n">
         <v>101641</v>
@@ -18958,7 +18958,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047555923462</v>
+        <v>14.4047546386719</v>
       </c>
       <c r="H641" t="n">
         <v>104803</v>
@@ -19045,7 +19045,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H644" t="n">
         <v>37693</v>
@@ -19132,7 +19132,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H647" t="n">
         <v>62394</v>
@@ -19306,7 +19306,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H653" t="n">
         <v>67181</v>
@@ -19480,7 +19480,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H659" t="n">
         <v>65476</v>
@@ -19538,7 +19538,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H661" t="n">
         <v>35343</v>
@@ -19625,7 +19625,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H664" t="n">
         <v>45922</v>
@@ -19654,7 +19654,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751253128052</v>
+        <v>15.9751262664795</v>
       </c>
       <c r="H665" t="n">
         <v>60499</v>
@@ -19683,7 +19683,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108379364014</v>
+        <v>16.1108360290527</v>
       </c>
       <c r="H666" t="n">
         <v>28199</v>
@@ -19770,7 +19770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220855712891</v>
+        <v>15.1220846176147</v>
       </c>
       <c r="H669" t="n">
         <v>107477</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761779785156</v>
+        <v>14.6761770248413</v>
       </c>
       <c r="H672" t="n">
         <v>131068</v>
@@ -19944,7 +19944,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H675" t="n">
         <v>84935</v>
@@ -20002,7 +20002,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H677" t="n">
         <v>28484</v>
@@ -20031,7 +20031,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H678" t="n">
         <v>45965</v>
@@ -20089,7 +20089,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H680" t="n">
         <v>49932</v>
@@ -20205,7 +20205,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H684" t="n">
         <v>33213</v>
@@ -20263,7 +20263,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H686" t="n">
         <v>149634</v>
@@ -20292,7 +20292,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394145965576</v>
+        <v>15.8394155502319</v>
       </c>
       <c r="H687" t="n">
         <v>39470</v>
@@ -20350,7 +20350,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496124267578</v>
+        <v>16.1496105194092</v>
       </c>
       <c r="H689" t="n">
         <v>60094</v>
@@ -20553,7 +20553,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843166351318</v>
+        <v>15.6843156814575</v>
       </c>
       <c r="H696" t="n">
         <v>33104</v>
@@ -20582,7 +20582,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975772857666</v>
+        <v>15.8975763320923</v>
       </c>
       <c r="H697" t="n">
         <v>154495</v>
@@ -20611,7 +20611,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H698" t="n">
         <v>76799</v>
@@ -20640,7 +20640,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.374119758606</v>
+        <v>15.3741188049316</v>
       </c>
       <c r="H699" t="n">
         <v>43123</v>
@@ -20727,7 +20727,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H702" t="n">
         <v>27978</v>
@@ -20843,7 +20843,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H706" t="n">
         <v>80940</v>
@@ -20872,7 +20872,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H707" t="n">
         <v>82998</v>
@@ -20988,7 +20988,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128932952881</v>
+        <v>15.4128942489624</v>
       </c>
       <c r="H711" t="n">
         <v>31373</v>
@@ -21046,7 +21046,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H713" t="n">
         <v>58117</v>
@@ -21191,7 +21191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.1414728164673</v>
+        <v>15.141471862793</v>
       </c>
       <c r="H718" t="n">
         <v>55322</v>
@@ -21249,7 +21249,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833101272583</v>
+        <v>15.0833110809326</v>
       </c>
       <c r="H720" t="n">
         <v>39360</v>
@@ -21278,7 +21278,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.9669857025146</v>
+        <v>14.966986656189</v>
       </c>
       <c r="H721" t="n">
         <v>65632</v>
@@ -21307,7 +21307,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506622314453</v>
+        <v>14.8506631851196</v>
       </c>
       <c r="H722" t="n">
         <v>53763</v>
@@ -21394,7 +21394,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078193664551</v>
+        <v>14.3078184127808</v>
       </c>
       <c r="H725" t="n">
         <v>86664</v>
@@ -21423,7 +21423,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823036193848</v>
+        <v>14.4823045730591</v>
       </c>
       <c r="H726" t="n">
         <v>87213</v>
@@ -21452,7 +21452,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H727" t="n">
         <v>73456</v>
@@ -21597,7 +21597,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H732" t="n">
         <v>67534</v>
@@ -21655,7 +21655,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302694320679</v>
+        <v>14.2302703857422</v>
       </c>
       <c r="H734" t="n">
         <v>45192</v>
@@ -21713,7 +21713,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771825790405</v>
+        <v>15.2771835327148</v>
       </c>
       <c r="H736" t="n">
         <v>101028</v>
@@ -21771,7 +21771,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965698242188</v>
+        <v>15.2965707778931</v>
       </c>
       <c r="H738" t="n">
         <v>284400</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700504302979</v>
+        <v>14.8700494766235</v>
       </c>
       <c r="H739" t="n">
         <v>99147</v>
@@ -21916,7 +21916,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486059188843</v>
+        <v>15.5486068725586</v>
       </c>
       <c r="H743" t="n">
         <v>51182</v>
@@ -22032,7 +22032,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781890869141</v>
+        <v>15.8781871795654</v>
       </c>
       <c r="H747" t="n">
         <v>39016</v>
@@ -22148,7 +22148,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577962875366</v>
+        <v>15.2577953338623</v>
       </c>
       <c r="H751" t="n">
         <v>131748</v>
@@ -22235,7 +22235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H754" t="n">
         <v>50268</v>
@@ -22264,7 +22264,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282121658325</v>
+        <v>14.9282112121582</v>
       </c>
       <c r="H755" t="n">
         <v>44022</v>
@@ -22438,7 +22438,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914958953857</v>
+        <v>14.1914949417114</v>
       </c>
       <c r="H761" t="n">
         <v>62425</v>
@@ -22496,7 +22496,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H763" t="n">
         <v>51431</v>
@@ -22525,7 +22525,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H764" t="n">
         <v>67676</v>
@@ -22583,7 +22583,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.210883140564</v>
+        <v>14.2108821868896</v>
       </c>
       <c r="H766" t="n">
         <v>97709</v>
@@ -22612,7 +22612,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H767" t="n">
         <v>48972</v>
@@ -22641,7 +22641,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976224899292</v>
+        <v>13.9976215362549</v>
       </c>
       <c r="H768" t="n">
         <v>48388</v>
@@ -22670,7 +22670,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557842254639</v>
+        <v>14.0557832717896</v>
       </c>
       <c r="H769" t="n">
         <v>43039</v>
@@ -22728,7 +22728,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.687424659729</v>
+        <v>13.6874256134033</v>
       </c>
       <c r="H771" t="n">
         <v>91611</v>
@@ -22757,7 +22757,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H772" t="n">
         <v>59694</v>
@@ -22815,7 +22815,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H774" t="n">
         <v>46705</v>
@@ -22931,7 +22931,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H778" t="n">
         <v>54214</v>
@@ -22960,7 +22960,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.1639680862427</v>
+        <v>13.163969039917</v>
       </c>
       <c r="H779" t="n">
         <v>31292</v>
@@ -23047,7 +23047,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.2221307754517</v>
+        <v>13.222131729126</v>
       </c>
       <c r="H782" t="n">
         <v>29208</v>
@@ -23076,7 +23076,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H783" t="n">
         <v>48982</v>
@@ -23105,7 +23105,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H784" t="n">
         <v>44891</v>
@@ -23192,7 +23192,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H787" t="n">
         <v>75458</v>
@@ -23221,7 +23221,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.920072555542</v>
+        <v>13.9200735092163</v>
       </c>
       <c r="H788" t="n">
         <v>161892</v>
@@ -23453,7 +23453,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H796" t="n">
         <v>130807</v>
@@ -23511,7 +23511,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H798" t="n">
         <v>24558</v>
@@ -23598,7 +23598,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H801" t="n">
         <v>52319</v>
@@ -23627,7 +23627,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578414916992</v>
+        <v>13.3578405380249</v>
       </c>
       <c r="H802" t="n">
         <v>34321</v>
@@ -23772,7 +23772,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.280291557312</v>
+        <v>13.2802925109863</v>
       </c>
       <c r="H807" t="n">
         <v>77476</v>
@@ -23859,7 +23859,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619117736816</v>
+        <v>13.8619108200073</v>
       </c>
       <c r="H810" t="n">
         <v>292244</v>
@@ -23888,7 +23888,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210790634155</v>
+        <v>14.5210781097412</v>
       </c>
       <c r="H811" t="n">
         <v>260837</v>
@@ -23917,7 +23917,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751724243164</v>
+        <v>14.0751714706421</v>
       </c>
       <c r="H812" t="n">
         <v>95170</v>
@@ -24062,7 +24062,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098766326904</v>
+        <v>13.6098756790161</v>
       </c>
       <c r="H817" t="n">
         <v>77436</v>
@@ -24236,7 +24236,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088710784912</v>
+        <v>13.0088701248169</v>
       </c>
       <c r="H823" t="n">
         <v>139568</v>
@@ -24294,7 +24294,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251945495605</v>
+        <v>13.1251935958862</v>
       </c>
       <c r="H825" t="n">
         <v>40244</v>
@@ -24323,7 +24323,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507074356079</v>
+        <v>12.9507083892822</v>
       </c>
       <c r="H826" t="n">
         <v>46870</v>
@@ -24352,7 +24352,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700956344604</v>
+        <v>12.9700965881348</v>
       </c>
       <c r="H827" t="n">
         <v>35005</v>
@@ -24381,7 +24381,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H828" t="n">
         <v>44484</v>
@@ -24584,7 +24584,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160032272339</v>
+        <v>13.4160041809082</v>
       </c>
       <c r="H835" t="n">
         <v>51758</v>
@@ -24961,7 +24961,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H848" t="n">
         <v>65992</v>
@@ -24990,7 +24990,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.3497018814087</v>
+        <v>12.349702835083</v>
       </c>
       <c r="H849" t="n">
         <v>101683</v>
@@ -25193,7 +25193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.524188041687</v>
+        <v>12.5241889953613</v>
       </c>
       <c r="H856" t="n">
         <v>89742</v>
@@ -25425,7 +25425,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017379760742</v>
+        <v>12.6017370223999</v>
       </c>
       <c r="H864" t="n">
         <v>23829</v>
@@ -25454,7 +25454,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435752868652</v>
+        <v>12.5435743331909</v>
       </c>
       <c r="H865" t="n">
         <v>77981</v>
@@ -25512,7 +25512,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037942886353</v>
+        <v>11.9037952423096</v>
       </c>
       <c r="H867" t="n">
         <v>165052</v>
@@ -25570,7 +25570,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.535436630249</v>
+        <v>11.5354356765747</v>
       </c>
       <c r="H869" t="n">
         <v>221362</v>
@@ -25657,7 +25657,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262453079224</v>
+        <v>11.8262462615967</v>
       </c>
       <c r="H872" t="n">
         <v>56333</v>
@@ -25715,7 +25715,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129856109619</v>
+        <v>11.6129846572876</v>
       </c>
       <c r="H874" t="n">
         <v>58043</v>
@@ -25773,7 +25773,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905345916748</v>
+        <v>11.6905355453491</v>
       </c>
       <c r="H876" t="n">
         <v>76554</v>
@@ -25802,7 +25802,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201177597046</v>
+        <v>12.0201187133789</v>
       </c>
       <c r="H877" t="n">
         <v>82169</v>
@@ -25831,7 +25831,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558294296265</v>
+        <v>12.1558303833008</v>
       </c>
       <c r="H878" t="n">
         <v>210169</v>
@@ -25976,7 +25976,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864191055298</v>
+        <v>13.0864200592041</v>
       </c>
       <c r="H883" t="n">
         <v>63353</v>
@@ -36973,6 +36973,35 @@
         <v>39909</v>
       </c>
       <c r="I1262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1263" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>12.460000038147</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>76785</v>
+      </c>
+      <c r="I1263" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICOS.MI.xlsx
+++ b/data/ICOS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4387073516846</v>
+        <v>15.4387083053589</v>
       </c>
       <c r="H2" t="n">
         <v>106930</v>
@@ -456,7 +456,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7954301834106</v>
+        <v>14.7954292297363</v>
       </c>
       <c r="H3" t="n">
         <v>88539</v>
@@ -543,7 +543,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9846286773682</v>
+        <v>14.9846277236938</v>
       </c>
       <c r="H6" t="n">
         <v>11909</v>
@@ -601,7 +601,7 @@
         <v>15.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H8" t="n">
         <v>69786</v>
@@ -659,7 +659,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7008285522461</v>
+        <v>14.7008295059204</v>
       </c>
       <c r="H10" t="n">
         <v>75622</v>
@@ -717,7 +717,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7197494506836</v>
+        <v>14.7197504043579</v>
       </c>
       <c r="H12" t="n">
         <v>31842</v>
@@ -775,7 +775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G14" t="n">
-        <v>14.4548692703247</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H14" t="n">
         <v>22167</v>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H15" t="n">
         <v>11081</v>
@@ -833,7 +833,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G16" t="n">
-        <v>14.4359493255615</v>
+        <v>14.4359502792358</v>
       </c>
       <c r="H16" t="n">
         <v>13170</v>
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1899890899658</v>
+        <v>14.1899900436401</v>
       </c>
       <c r="H17" t="n">
         <v>10708</v>
@@ -891,7 +891,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>14.000789642334</v>
+        <v>14.0007915496826</v>
       </c>
       <c r="H18" t="n">
         <v>7979</v>
@@ -949,7 +949,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6819095611572</v>
+        <v>14.6819105148315</v>
       </c>
       <c r="H20" t="n">
         <v>19890</v>
@@ -978,7 +978,7 @@
         <v>15.5</v>
       </c>
       <c r="G21" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H21" t="n">
         <v>20677</v>
@@ -1036,7 +1036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H23" t="n">
         <v>4517</v>
@@ -1152,7 +1152,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8115911483765</v>
+        <v>13.8115901947021</v>
       </c>
       <c r="H27" t="n">
         <v>47594</v>
@@ -1210,7 +1210,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G29" t="n">
-        <v>13.2250709533691</v>
+        <v>13.2250699996948</v>
       </c>
       <c r="H29" t="n">
         <v>69505</v>
@@ -1239,7 +1239,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>13.2250709533691</v>
+        <v>13.2250699996948</v>
       </c>
       <c r="H30" t="n">
         <v>34219</v>
@@ -1326,7 +1326,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G33" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H33" t="n">
         <v>13990</v>
@@ -1413,7 +1413,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H36" t="n">
         <v>8817</v>
@@ -1442,7 +1442,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3007497787476</v>
+        <v>13.3007507324219</v>
       </c>
       <c r="H37" t="n">
         <v>21560</v>
@@ -1471,7 +1471,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H38" t="n">
         <v>18250</v>
@@ -1500,7 +1500,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>13.0547895431519</v>
+        <v>13.0547914505005</v>
       </c>
       <c r="H39" t="n">
         <v>43941</v>
@@ -1587,7 +1587,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G42" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H42" t="n">
         <v>27508</v>
@@ -1616,7 +1616,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6007099151611</v>
+        <v>12.6007108688354</v>
       </c>
       <c r="H43" t="n">
         <v>77913</v>
@@ -1645,7 +1645,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H44" t="n">
         <v>70236</v>
@@ -1674,7 +1674,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G45" t="n">
-        <v>12.9412698745728</v>
+        <v>12.9412708282471</v>
       </c>
       <c r="H45" t="n">
         <v>41877</v>
@@ -1732,7 +1732,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G47" t="n">
-        <v>12.903431892395</v>
+        <v>12.9034299850464</v>
       </c>
       <c r="H47" t="n">
         <v>26045</v>
@@ -1790,7 +1790,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H49" t="n">
         <v>62308</v>
@@ -1877,7 +1877,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H52" t="n">
         <v>30733</v>
@@ -1993,7 +1993,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H56" t="n">
         <v>71712</v>
@@ -2051,7 +2051,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H58" t="n">
         <v>38827</v>
@@ -2080,7 +2080,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H59" t="n">
         <v>23840</v>
@@ -2109,7 +2109,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H60" t="n">
         <v>20661</v>
@@ -2138,7 +2138,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G61" t="n">
-        <v>12.3358306884766</v>
+        <v>12.3358316421509</v>
       </c>
       <c r="H61" t="n">
         <v>27576</v>
@@ -2254,7 +2254,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1844720840454</v>
+        <v>12.1844711303711</v>
       </c>
       <c r="H65" t="n">
         <v>17790</v>
@@ -2312,7 +2312,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G67" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H67" t="n">
         <v>16328</v>
@@ -2370,7 +2370,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H69" t="n">
         <v>21775</v>
@@ -2428,7 +2428,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H71" t="n">
         <v>27888</v>
@@ -2573,7 +2573,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H76" t="n">
         <v>5114</v>
@@ -2602,7 +2602,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G77" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H77" t="n">
         <v>19525</v>
@@ -2631,7 +2631,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H78" t="n">
         <v>9685</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.2006320953369</v>
+        <v>11.2006311416626</v>
       </c>
       <c r="H79" t="n">
         <v>30466</v>
@@ -2689,7 +2689,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>11.2763109207153</v>
+        <v>11.2763118743896</v>
       </c>
       <c r="H80" t="n">
         <v>13721</v>
@@ -2718,7 +2718,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H81" t="n">
         <v>47563</v>
@@ -2747,7 +2747,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5951919555664</v>
+        <v>10.5951910018921</v>
       </c>
       <c r="H82" t="n">
         <v>49010</v>
@@ -2805,7 +2805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5005931854248</v>
+        <v>10.5005922317505</v>
       </c>
       <c r="H84" t="n">
         <v>55863</v>
@@ -2892,7 +2892,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>11.4465923309326</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H87" t="n">
         <v>41843</v>
@@ -2979,7 +2979,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H90" t="n">
         <v>13547</v>
@@ -3066,7 +3066,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H93" t="n">
         <v>15977</v>
@@ -3095,7 +3095,7 @@
         <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>11.3519916534424</v>
+        <v>11.3519926071167</v>
       </c>
       <c r="H94" t="n">
         <v>17943</v>
@@ -3124,7 +3124,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H95" t="n">
         <v>94458</v>
@@ -3153,7 +3153,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G96" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H96" t="n">
         <v>230549</v>
@@ -3182,7 +3182,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G97" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H97" t="n">
         <v>30156</v>
@@ -3211,7 +3211,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H98" t="n">
         <v>58338</v>
@@ -3240,7 +3240,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G99" t="n">
-        <v>11.4276723861694</v>
+        <v>11.4276714324951</v>
       </c>
       <c r="H99" t="n">
         <v>90549</v>
@@ -3269,7 +3269,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H100" t="n">
         <v>105663</v>
@@ -3298,7 +3298,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G101" t="n">
-        <v>11.5506525039673</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H101" t="n">
         <v>16088</v>
@@ -3327,7 +3327,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H102" t="n">
         <v>39681</v>
@@ -3414,7 +3414,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H105" t="n">
         <v>57465</v>
@@ -3530,7 +3530,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G109" t="n">
-        <v>11.5506525039673</v>
+        <v>11.550651550293</v>
       </c>
       <c r="H109" t="n">
         <v>34921</v>
@@ -3559,7 +3559,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G110" t="n">
-        <v>11.8344526290894</v>
+        <v>11.834451675415</v>
       </c>
       <c r="H110" t="n">
         <v>21276</v>
@@ -3588,7 +3588,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H111" t="n">
         <v>18000</v>
@@ -3646,7 +3646,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H113" t="n">
         <v>100165</v>
@@ -3675,7 +3675,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H114" t="n">
         <v>96370</v>
@@ -3704,7 +3704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H115" t="n">
         <v>10754</v>
@@ -3733,7 +3733,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G116" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H116" t="n">
         <v>29281</v>
@@ -3791,7 +3791,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4115114212036</v>
+        <v>12.4115104675293</v>
       </c>
       <c r="H118" t="n">
         <v>9073</v>
@@ -3849,7 +3849,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>12.2033920288086</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H120" t="n">
         <v>18650</v>
@@ -3907,7 +3907,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>11.6641712188721</v>
+        <v>11.6641721725464</v>
       </c>
       <c r="H122" t="n">
         <v>38398</v>
@@ -3936,7 +3936,7 @@
         <v>12.25</v>
       </c>
       <c r="G123" t="n">
-        <v>11.588490486145</v>
+        <v>11.5884923934937</v>
       </c>
       <c r="H123" t="n">
         <v>12353</v>
@@ -3994,7 +3994,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G125" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H125" t="n">
         <v>44715</v>
@@ -4052,7 +4052,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>12.2033920288086</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H127" t="n">
         <v>53178</v>
@@ -4110,7 +4110,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G129" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H129" t="n">
         <v>100100</v>
@@ -4139,7 +4139,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H130" t="n">
         <v>21255</v>
@@ -4168,7 +4168,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H131" t="n">
         <v>41589</v>
@@ -4255,7 +4255,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>11.1627931594849</v>
+        <v>11.1627922058105</v>
       </c>
       <c r="H134" t="n">
         <v>35125</v>
@@ -4284,7 +4284,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G135" t="n">
-        <v>11.5979509353638</v>
+        <v>11.5979518890381</v>
       </c>
       <c r="H135" t="n">
         <v>34842</v>
@@ -4313,7 +4313,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G136" t="n">
-        <v>11.5317316055298</v>
+        <v>11.5317306518555</v>
       </c>
       <c r="H136" t="n">
         <v>34461</v>
@@ -4342,7 +4342,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>11.7303905487061</v>
+        <v>11.7303915023804</v>
       </c>
       <c r="H137" t="n">
         <v>33734</v>
@@ -4429,7 +4429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G140" t="n">
-        <v>12.2033920288086</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H140" t="n">
         <v>24892</v>
@@ -4458,7 +4458,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G141" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H141" t="n">
         <v>37220</v>
@@ -4487,7 +4487,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G142" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H142" t="n">
         <v>15956</v>
@@ -4545,7 +4545,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H144" t="n">
         <v>9829</v>
@@ -4574,7 +4574,7 @@
         <v>13</v>
       </c>
       <c r="G145" t="n">
-        <v>12.2979907989502</v>
+        <v>12.2979898452759</v>
       </c>
       <c r="H145" t="n">
         <v>14891</v>
@@ -4632,7 +4632,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G147" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H147" t="n">
         <v>23423</v>
@@ -4661,7 +4661,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G148" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H148" t="n">
         <v>39443</v>
@@ -4777,7 +4777,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>12.3642110824585</v>
+        <v>12.3642101287842</v>
       </c>
       <c r="H152" t="n">
         <v>76384</v>
@@ -4864,7 +4864,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.4682712554932</v>
+        <v>12.4682703018188</v>
       </c>
       <c r="H155" t="n">
         <v>41701</v>
@@ -4922,7 +4922,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G157" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H157" t="n">
         <v>25916</v>
@@ -4980,7 +4980,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H159" t="n">
         <v>36559</v>
@@ -5038,7 +5038,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G161" t="n">
-        <v>12.1277103424072</v>
+        <v>12.1277112960815</v>
       </c>
       <c r="H161" t="n">
         <v>34152</v>
@@ -5067,7 +5067,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H162" t="n">
         <v>39212</v>
@@ -5096,7 +5096,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>11.862832069397</v>
+        <v>11.8628311157227</v>
       </c>
       <c r="H163" t="n">
         <v>34086</v>
@@ -5183,7 +5183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G166" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H166" t="n">
         <v>9153</v>
@@ -5212,7 +5212,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G167" t="n">
-        <v>11.7966117858887</v>
+        <v>11.796612739563</v>
       </c>
       <c r="H167" t="n">
         <v>6760</v>
@@ -5299,7 +5299,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3169107437134</v>
+        <v>12.3169116973877</v>
       </c>
       <c r="H170" t="n">
         <v>6203</v>
@@ -5357,7 +5357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>12.2317714691162</v>
+        <v>12.2317724227905</v>
       </c>
       <c r="H172" t="n">
         <v>6977</v>
@@ -5444,7 +5444,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G175" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H175" t="n">
         <v>13252</v>
@@ -5502,7 +5502,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H177" t="n">
         <v>11320</v>
@@ -5531,7 +5531,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>12.2223119735718</v>
+        <v>12.2223110198975</v>
       </c>
       <c r="H178" t="n">
         <v>16515</v>
@@ -5560,7 +5560,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G179" t="n">
-        <v>12.3547506332397</v>
+        <v>12.3547515869141</v>
       </c>
       <c r="H179" t="n">
         <v>21056</v>
@@ -5589,7 +5589,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G180" t="n">
-        <v>12.4209699630737</v>
+        <v>12.420970916748</v>
       </c>
       <c r="H180" t="n">
         <v>13780</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>12.3925914764404</v>
+        <v>12.3925905227661</v>
       </c>
       <c r="H181" t="n">
         <v>37878</v>
@@ -5734,7 +5734,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>12.44935131073</v>
+        <v>12.4493503570557</v>
       </c>
       <c r="H185" t="n">
         <v>18304</v>
@@ -5763,7 +5763,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G186" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H186" t="n">
         <v>17730</v>
@@ -5821,7 +5821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G188" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H188" t="n">
         <v>11933</v>
@@ -5850,7 +5850,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>12.2033920288086</v>
+        <v>12.2033910751343</v>
       </c>
       <c r="H189" t="n">
         <v>22438</v>
@@ -5908,7 +5908,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G191" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H191" t="n">
         <v>5115</v>
@@ -5966,7 +5966,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G193" t="n">
-        <v>11.6452512741089</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H193" t="n">
         <v>10010</v>
@@ -6024,7 +6024,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H195" t="n">
         <v>9323</v>
@@ -6111,7 +6111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>11.6830921173096</v>
+        <v>11.6830911636353</v>
       </c>
       <c r="H198" t="n">
         <v>9999</v>
@@ -6140,7 +6140,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G199" t="n">
-        <v>11.6263303756714</v>
+        <v>11.62633228302</v>
       </c>
       <c r="H199" t="n">
         <v>12593</v>
@@ -6169,7 +6169,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>11.5695724487305</v>
+        <v>11.5695714950562</v>
       </c>
       <c r="H200" t="n">
         <v>18599</v>
@@ -6343,7 +6343,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G206" t="n">
-        <v>11.6925506591797</v>
+        <v>11.692551612854</v>
       </c>
       <c r="H206" t="n">
         <v>17437</v>
@@ -6401,7 +6401,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G208" t="n">
-        <v>11.8817529678345</v>
+        <v>11.8817520141602</v>
       </c>
       <c r="H208" t="n">
         <v>15504</v>
@@ -6430,7 +6430,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G209" t="n">
-        <v>11.6452512741089</v>
+        <v>11.6452522277832</v>
       </c>
       <c r="H209" t="n">
         <v>2762</v>
@@ -6459,7 +6459,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>11.4749727249146</v>
+        <v>11.4749708175659</v>
       </c>
       <c r="H210" t="n">
         <v>12812</v>
@@ -6488,7 +6488,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>11.3709125518799</v>
+        <v>11.3709115982056</v>
       </c>
       <c r="H211" t="n">
         <v>30604</v>
@@ -6517,7 +6517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>11.4938917160034</v>
+        <v>11.4938907623291</v>
       </c>
       <c r="H212" t="n">
         <v>9861</v>
@@ -6546,7 +6546,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G213" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H213" t="n">
         <v>27664</v>
@@ -6575,7 +6575,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G214" t="n">
-        <v>11.4371318817139</v>
+        <v>11.4371309280396</v>
       </c>
       <c r="H214" t="n">
         <v>46989</v>
@@ -6691,7 +6691,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>11.0587320327759</v>
+        <v>11.0587310791016</v>
       </c>
       <c r="H218" t="n">
         <v>37998</v>
@@ -6720,7 +6720,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H219" t="n">
         <v>10867</v>
@@ -6749,7 +6749,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>11.0208921432495</v>
+        <v>11.0208911895752</v>
       </c>
       <c r="H220" t="n">
         <v>16358</v>
@@ -6778,7 +6778,7 @@
         <v>11.5</v>
       </c>
       <c r="G221" t="n">
-        <v>10.8789920806885</v>
+        <v>10.8789930343628</v>
       </c>
       <c r="H221" t="n">
         <v>10402</v>
@@ -6807,7 +6807,7 @@
         <v>11</v>
       </c>
       <c r="G222" t="n">
-        <v>10.4059925079346</v>
+        <v>10.4059934616089</v>
       </c>
       <c r="H222" t="n">
         <v>8716</v>
@@ -6836,7 +6836,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1221933364868</v>
+        <v>10.1221923828125</v>
       </c>
       <c r="H223" t="n">
         <v>18441</v>
@@ -6923,7 +6923,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>10.1316518783569</v>
+        <v>10.1316528320312</v>
       </c>
       <c r="H226" t="n">
         <v>18618</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H228" t="n">
         <v>31580</v>
@@ -7068,7 +7068,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>10.1221933364868</v>
+        <v>10.1221923828125</v>
       </c>
       <c r="H231" t="n">
         <v>19711</v>
@@ -7155,7 +7155,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G234" t="n">
-        <v>9.97083187103271</v>
+        <v>9.97083282470703</v>
       </c>
       <c r="H234" t="n">
         <v>21742</v>
@@ -7184,7 +7184,7 @@
         <v>10.5</v>
       </c>
       <c r="G235" t="n">
-        <v>9.93299198150635</v>
+        <v>9.93299293518066</v>
       </c>
       <c r="H235" t="n">
         <v>4261</v>
@@ -7213,7 +7213,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G236" t="n">
-        <v>9.80055332183838</v>
+        <v>9.80055236816406</v>
       </c>
       <c r="H236" t="n">
         <v>5966</v>
@@ -7329,7 +7329,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H240" t="n">
         <v>23403</v>
@@ -7358,7 +7358,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0086727142334</v>
+        <v>10.0086736679077</v>
       </c>
       <c r="H241" t="n">
         <v>11515</v>
@@ -7416,7 +7416,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>10.1032733917236</v>
+        <v>10.1032724380493</v>
       </c>
       <c r="H243" t="n">
         <v>7314</v>
@@ -7503,7 +7503,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G246" t="n">
-        <v>10.1789531707764</v>
+        <v>10.1789522171021</v>
       </c>
       <c r="H246" t="n">
         <v>25506</v>
@@ -7590,7 +7590,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G249" t="n">
-        <v>9.52621269226074</v>
+        <v>9.52621364593506</v>
       </c>
       <c r="H249" t="n">
         <v>14090</v>
@@ -7619,7 +7619,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>9.50729274749756</v>
+        <v>9.50729370117188</v>
       </c>
       <c r="H250" t="n">
         <v>10311</v>
@@ -7648,7 +7648,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>9.34647369384766</v>
+        <v>9.34647274017334</v>
       </c>
       <c r="H251" t="n">
         <v>15863</v>
@@ -7735,7 +7735,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>9.29917240142822</v>
+        <v>9.29917335510254</v>
       </c>
       <c r="H254" t="n">
         <v>10680</v>
@@ -7764,7 +7764,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>9.96137237548828</v>
+        <v>9.9613733291626</v>
       </c>
       <c r="H255" t="n">
         <v>77427</v>
@@ -7851,7 +7851,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>11.4465923309326</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H258" t="n">
         <v>77059</v>
@@ -7880,7 +7880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>11.2100925445557</v>
+        <v>11.2100915908813</v>
       </c>
       <c r="H259" t="n">
         <v>32840</v>
@@ -7909,7 +7909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G260" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H260" t="n">
         <v>20375</v>
@@ -7938,7 +7938,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G261" t="n">
-        <v>11.2668523788452</v>
+        <v>11.2668514251709</v>
       </c>
       <c r="H261" t="n">
         <v>11841</v>
@@ -7967,7 +7967,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>11.2952308654785</v>
+        <v>11.2952318191528</v>
       </c>
       <c r="H262" t="n">
         <v>7561</v>
@@ -7996,7 +7996,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G263" t="n">
-        <v>11.2290124893188</v>
+        <v>11.2290115356445</v>
       </c>
       <c r="H263" t="n">
         <v>3066</v>
@@ -8054,7 +8054,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G265" t="n">
-        <v>11.1533317565918</v>
+        <v>11.1533327102661</v>
       </c>
       <c r="H265" t="n">
         <v>1992</v>
@@ -8083,7 +8083,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G266" t="n">
-        <v>11.314151763916</v>
+        <v>11.3141527175903</v>
       </c>
       <c r="H266" t="n">
         <v>13617</v>
@@ -8112,7 +8112,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H267" t="n">
         <v>6337</v>
@@ -8141,7 +8141,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3330707550049</v>
+        <v>11.3330717086792</v>
       </c>
       <c r="H268" t="n">
         <v>7750</v>
@@ -8170,7 +8170,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H269" t="n">
         <v>15428</v>
@@ -8199,7 +8199,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G270" t="n">
-        <v>11.4844312667847</v>
+        <v>11.484432220459</v>
       </c>
       <c r="H270" t="n">
         <v>5222</v>
@@ -8257,7 +8257,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G272" t="n">
-        <v>11.8439121246338</v>
+        <v>11.8439111709595</v>
       </c>
       <c r="H272" t="n">
         <v>452664</v>
@@ -8286,7 +8286,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G273" t="n">
-        <v>11.8060703277588</v>
+        <v>11.8060712814331</v>
       </c>
       <c r="H273" t="n">
         <v>9792</v>
@@ -8344,7 +8344,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>11.5411920547485</v>
+        <v>11.5411911010742</v>
       </c>
       <c r="H275" t="n">
         <v>6258</v>
@@ -8402,7 +8402,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5790319442749</v>
+        <v>11.5790309906006</v>
       </c>
       <c r="H277" t="n">
         <v>39974</v>
@@ -8460,7 +8460,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>11.3992910385132</v>
+        <v>11.3992919921875</v>
       </c>
       <c r="H279" t="n">
         <v>5669</v>
@@ -8518,7 +8518,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.4465923309326</v>
+        <v>11.446590423584</v>
       </c>
       <c r="H281" t="n">
         <v>3469</v>
@@ -8547,7 +8547,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G282" t="n">
-        <v>11.4087524414062</v>
+        <v>11.4087514877319</v>
       </c>
       <c r="H282" t="n">
         <v>9074</v>
@@ -8605,7 +8605,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>11.7966117858887</v>
+        <v>11.796612739563</v>
       </c>
       <c r="H284" t="n">
         <v>13107</v>
@@ -8663,7 +8663,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G286" t="n">
-        <v>11.9101314544678</v>
+        <v>11.9101305007935</v>
       </c>
       <c r="H286" t="n">
         <v>18279</v>
@@ -8721,7 +8721,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G288" t="n">
-        <v>11.8155317306519</v>
+        <v>11.8155307769775</v>
       </c>
       <c r="H288" t="n">
         <v>5961</v>
@@ -8750,7 +8750,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2128505706787</v>
+        <v>12.212851524353</v>
       </c>
       <c r="H289" t="n">
         <v>18611</v>
@@ -8808,7 +8808,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H291" t="n">
         <v>45569</v>
@@ -8837,7 +8837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H292" t="n">
         <v>41365</v>
@@ -8866,7 +8866,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>12.2885313034058</v>
+        <v>12.2885303497314</v>
       </c>
       <c r="H293" t="n">
         <v>19905</v>
@@ -8895,7 +8895,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>12.4398899078369</v>
+        <v>12.4398908615112</v>
       </c>
       <c r="H294" t="n">
         <v>39678</v>
@@ -8924,7 +8924,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G295" t="n">
-        <v>12.1750116348267</v>
+        <v>12.1750106811523</v>
       </c>
       <c r="H295" t="n">
         <v>35719</v>
@@ -8953,7 +8953,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G296" t="n">
-        <v>12.137170791626</v>
+        <v>12.1371717453003</v>
       </c>
       <c r="H296" t="n">
         <v>113027</v>
@@ -9040,7 +9040,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>12.0331106185913</v>
+        <v>12.0331115722656</v>
       </c>
       <c r="H299" t="n">
         <v>6219</v>
@@ -9098,7 +9098,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>11.900671005249</v>
+        <v>11.9006719589233</v>
       </c>
       <c r="H301" t="n">
         <v>4323</v>
@@ -9156,7 +9156,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1087913513184</v>
+        <v>12.1087923049927</v>
       </c>
       <c r="H303" t="n">
         <v>4967</v>
@@ -9214,7 +9214,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>12.3547506332397</v>
+        <v>12.3547515869141</v>
       </c>
       <c r="H305" t="n">
         <v>7507</v>
@@ -9272,7 +9272,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G307" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H307" t="n">
         <v>23675</v>
@@ -9301,7 +9301,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H308" t="n">
         <v>11462</v>
@@ -9330,7 +9330,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>12.0141897201538</v>
+        <v>12.0141906738281</v>
       </c>
       <c r="H309" t="n">
         <v>19820</v>
@@ -9359,7 +9359,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G310" t="n">
-        <v>12.3831310272217</v>
+        <v>12.3831300735474</v>
       </c>
       <c r="H310" t="n">
         <v>86708</v>
@@ -9388,7 +9388,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H311" t="n">
         <v>118963</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H312" t="n">
         <v>60848</v>
@@ -9504,7 +9504,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>12.8655910491943</v>
+        <v>12.86559009552</v>
       </c>
       <c r="H315" t="n">
         <v>31712</v>
@@ -9562,7 +9562,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G317" t="n">
-        <v>13.0642509460449</v>
+        <v>13.0642518997192</v>
       </c>
       <c r="H317" t="n">
         <v>729414</v>
@@ -9591,7 +9591,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>12.9601898193359</v>
+        <v>12.9601907730103</v>
       </c>
       <c r="H318" t="n">
         <v>114421</v>
@@ -9620,7 +9620,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>12.8182916641235</v>
+        <v>12.8182907104492</v>
       </c>
       <c r="H319" t="n">
         <v>115510</v>
@@ -9649,7 +9649,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>13.1966905593872</v>
+        <v>13.1966896057129</v>
       </c>
       <c r="H320" t="n">
         <v>115939</v>
@@ -9707,7 +9707,7 @@
         <v>14</v>
       </c>
       <c r="G322" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H322" t="n">
         <v>121250</v>
@@ -9765,7 +9765,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G324" t="n">
-        <v>13.2250709533691</v>
+        <v>13.2250699996948</v>
       </c>
       <c r="H324" t="n">
         <v>19992</v>
@@ -9794,7 +9794,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H325" t="n">
         <v>89076</v>
@@ -9823,7 +9823,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G326" t="n">
-        <v>13.7075290679932</v>
+        <v>13.7075300216675</v>
       </c>
       <c r="H326" t="n">
         <v>108302</v>
@@ -9881,7 +9881,7 @@
         <v>14.25</v>
       </c>
       <c r="G328" t="n">
-        <v>13.480489730835</v>
+        <v>13.4804906845093</v>
       </c>
       <c r="H328" t="n">
         <v>127967</v>
@@ -9910,7 +9910,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>13.3385906219482</v>
+        <v>13.3385896682739</v>
       </c>
       <c r="H329" t="n">
         <v>198840</v>
@@ -9968,7 +9968,7 @@
         <v>14</v>
       </c>
       <c r="G331" t="n">
-        <v>13.2439908981323</v>
+        <v>13.243989944458</v>
       </c>
       <c r="H331" t="n">
         <v>50115</v>
@@ -9997,7 +9997,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5467109680176</v>
+        <v>13.5467100143433</v>
       </c>
       <c r="H332" t="n">
         <v>62629</v>
@@ -10026,7 +10026,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G333" t="n">
-        <v>13.2912902832031</v>
+        <v>13.2912912368774</v>
       </c>
       <c r="H333" t="n">
         <v>23303</v>
@@ -10055,7 +10055,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>13.1399307250977</v>
+        <v>13.1399297714233</v>
       </c>
       <c r="H334" t="n">
         <v>35387</v>
@@ -10084,7 +10084,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H335" t="n">
         <v>11048</v>
@@ -10171,7 +10171,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G338" t="n">
-        <v>12.7142305374146</v>
+        <v>12.7142295837402</v>
       </c>
       <c r="H338" t="n">
         <v>27898</v>
@@ -10200,7 +10200,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>12.5439510345459</v>
+        <v>12.5439519882202</v>
       </c>
       <c r="H339" t="n">
         <v>106184</v>
@@ -10229,7 +10229,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>12.799370765686</v>
+        <v>12.7993698120117</v>
       </c>
       <c r="H340" t="n">
         <v>39580</v>
@@ -10403,7 +10403,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>13.764289855957</v>
+        <v>13.7642908096313</v>
       </c>
       <c r="H346" t="n">
         <v>87295</v>
@@ -10432,7 +10432,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G347" t="n">
-        <v>13.177770614624</v>
+        <v>13.1777696609497</v>
       </c>
       <c r="H347" t="n">
         <v>1624911</v>
@@ -10461,7 +10461,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>13.2629098892212</v>
+        <v>13.2629108428955</v>
       </c>
       <c r="H348" t="n">
         <v>46007</v>
@@ -10490,7 +10490,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G349" t="n">
-        <v>13.2629098892212</v>
+        <v>13.2629108428955</v>
       </c>
       <c r="H349" t="n">
         <v>74321</v>
@@ -10519,7 +10519,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G350" t="n">
-        <v>13.0453300476074</v>
+        <v>13.0453310012817</v>
       </c>
       <c r="H350" t="n">
         <v>29429</v>
@@ -10606,7 +10606,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7548303604126</v>
+        <v>13.7548294067383</v>
       </c>
       <c r="H353" t="n">
         <v>38579</v>
@@ -10635,7 +10635,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>13.385890007019</v>
+        <v>13.3858890533447</v>
       </c>
       <c r="H354" t="n">
         <v>47384</v>
@@ -10693,7 +10693,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.5817909240723</v>
+        <v>12.5817918777466</v>
       </c>
       <c r="H356" t="n">
         <v>162095</v>
@@ -10809,7 +10809,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1115503311157</v>
+        <v>13.1115493774414</v>
       </c>
       <c r="H360" t="n">
         <v>130944</v>
@@ -10838,7 +10838,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3764295578003</v>
+        <v>13.3764305114746</v>
       </c>
       <c r="H361" t="n">
         <v>58014</v>
@@ -10867,7 +10867,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G362" t="n">
-        <v>13.7737503051758</v>
+        <v>13.7737512588501</v>
       </c>
       <c r="H362" t="n">
         <v>69104</v>
@@ -10925,7 +10925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>13.792670249939</v>
+        <v>13.7926692962646</v>
       </c>
       <c r="H364" t="n">
         <v>32181</v>
@@ -10954,7 +10954,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>14.2845888137817</v>
+        <v>14.2845897674561</v>
       </c>
       <c r="H365" t="n">
         <v>87561</v>
@@ -11012,7 +11012,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G367" t="n">
-        <v>14.4548692703247</v>
+        <v>14.454870223999</v>
       </c>
       <c r="H367" t="n">
         <v>59900</v>
@@ -11099,7 +11099,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H370" t="n">
         <v>87340</v>
@@ -11128,7 +11128,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G371" t="n">
-        <v>15.3441076278687</v>
+        <v>15.344108581543</v>
       </c>
       <c r="H371" t="n">
         <v>38672</v>
@@ -11186,7 +11186,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G373" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H373" t="n">
         <v>58745</v>
@@ -11215,7 +11215,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G374" t="n">
-        <v>15.7225093841553</v>
+        <v>15.722508430481</v>
       </c>
       <c r="H374" t="n">
         <v>59328</v>
@@ -11244,7 +11244,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G375" t="n">
-        <v>15.5522298812866</v>
+        <v>15.5522289276123</v>
       </c>
       <c r="H375" t="n">
         <v>73481</v>
@@ -11273,7 +11273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0792293548584</v>
+        <v>15.0792284011841</v>
       </c>
       <c r="H376" t="n">
         <v>56480</v>
@@ -11331,7 +11331,7 @@
         <v>15.5</v>
       </c>
       <c r="G378" t="n">
-        <v>14.6629886627197</v>
+        <v>14.662989616394</v>
       </c>
       <c r="H378" t="n">
         <v>85275</v>
@@ -11447,7 +11447,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H382" t="n">
         <v>47987</v>
@@ -11476,7 +11476,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H383" t="n">
         <v>42204</v>
@@ -11505,7 +11505,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H384" t="n">
         <v>29024</v>
@@ -11534,7 +11534,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G385" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H385" t="n">
         <v>96136</v>
@@ -11592,7 +11592,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H387" t="n">
         <v>75211</v>
@@ -11650,7 +11650,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G389" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H389" t="n">
         <v>31834</v>
@@ -11679,7 +11679,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>15.0843820571899</v>
+        <v>15.0843811035156</v>
       </c>
       <c r="H390" t="n">
         <v>50895</v>
@@ -11708,7 +11708,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H391" t="n">
         <v>32365</v>
@@ -11737,7 +11737,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7020149230957</v>
+        <v>14.7020139694214</v>
       </c>
       <c r="H392" t="n">
         <v>23786</v>
@@ -11795,7 +11795,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>15.0079078674316</v>
+        <v>15.007908821106</v>
       </c>
       <c r="H394" t="n">
         <v>33934</v>
@@ -11911,7 +11911,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G398" t="n">
-        <v>14.950553894043</v>
+        <v>14.9505529403687</v>
       </c>
       <c r="H398" t="n">
         <v>35897</v>
@@ -11969,7 +11969,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H400" t="n">
         <v>31415</v>
@@ -12143,7 +12143,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7593698501587</v>
+        <v>14.7593688964844</v>
       </c>
       <c r="H406" t="n">
         <v>43836</v>
@@ -12201,7 +12201,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G408" t="n">
-        <v>14.5108318328857</v>
+        <v>14.5108308792114</v>
       </c>
       <c r="H408" t="n">
         <v>38004</v>
@@ -12259,7 +12259,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G410" t="n">
-        <v>14.6064224243164</v>
+        <v>14.6064233779907</v>
       </c>
       <c r="H410" t="n">
         <v>20011</v>
@@ -12346,7 +12346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H413" t="n">
         <v>34048</v>
@@ -12375,7 +12375,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>14.6446599960327</v>
+        <v>14.6446590423584</v>
       </c>
       <c r="H414" t="n">
         <v>3689</v>
@@ -12404,7 +12404,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6255416870117</v>
+        <v>14.6255407333374</v>
       </c>
       <c r="H415" t="n">
         <v>18337</v>
@@ -12433,7 +12433,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>14.5299501419067</v>
+        <v>14.5299491882324</v>
       </c>
       <c r="H416" t="n">
         <v>105045</v>
@@ -12549,7 +12549,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H420" t="n">
         <v>38844</v>
@@ -12607,7 +12607,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H422" t="n">
         <v>59124</v>
@@ -12723,7 +12723,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>15.1035003662109</v>
+        <v>15.1034994125366</v>
       </c>
       <c r="H426" t="n">
         <v>26636</v>
@@ -12781,7 +12781,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G428" t="n">
-        <v>15.3520383834839</v>
+        <v>15.3520374298096</v>
       </c>
       <c r="H428" t="n">
         <v>49360</v>
@@ -12839,7 +12839,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G430" t="n">
-        <v>15.1799736022949</v>
+        <v>15.1799726486206</v>
       </c>
       <c r="H430" t="n">
         <v>15809</v>
@@ -12897,7 +12897,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H432" t="n">
         <v>28274</v>
@@ -12926,7 +12926,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>15.1226186752319</v>
+        <v>15.1226177215576</v>
       </c>
       <c r="H433" t="n">
         <v>29865</v>
@@ -13071,7 +13071,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G438" t="n">
-        <v>14.835844039917</v>
+        <v>14.8358430862427</v>
       </c>
       <c r="H438" t="n">
         <v>18515</v>
@@ -13100,7 +13100,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1417369842529</v>
+        <v>15.1417360305786</v>
       </c>
       <c r="H439" t="n">
         <v>30668</v>
@@ -13158,7 +13158,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>15.3902759552002</v>
+        <v>15.3902750015259</v>
       </c>
       <c r="H441" t="n">
         <v>39019</v>
@@ -13216,7 +13216,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2755651473999</v>
+        <v>15.2755641937256</v>
       </c>
       <c r="H443" t="n">
         <v>45829</v>
@@ -13332,7 +13332,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>13.9563999176025</v>
+        <v>13.9563989639282</v>
       </c>
       <c r="H447" t="n">
         <v>34226</v>
@@ -13419,7 +13419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G450" t="n">
-        <v>14.0711097717285</v>
+        <v>14.0711088180542</v>
       </c>
       <c r="H450" t="n">
         <v>16818</v>
@@ -13680,7 +13680,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G459" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H459" t="n">
         <v>13373</v>
@@ -13709,7 +13709,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G460" t="n">
-        <v>12.9431247711182</v>
+        <v>12.9431257247925</v>
       </c>
       <c r="H460" t="n">
         <v>31924</v>
@@ -13738,7 +13738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H461" t="n">
         <v>47646</v>
@@ -13767,7 +13767,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H462" t="n">
         <v>24475</v>
@@ -13796,7 +13796,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H463" t="n">
         <v>22702</v>
@@ -13825,7 +13825,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G464" t="n">
-        <v>12.8666515350342</v>
+        <v>12.8666524887085</v>
       </c>
       <c r="H464" t="n">
         <v>16431</v>
@@ -13854,7 +13854,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G465" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H465" t="n">
         <v>66942</v>
@@ -13883,7 +13883,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G466" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H466" t="n">
         <v>75734</v>
@@ -13912,7 +13912,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5034027099609</v>
+        <v>12.5034036636353</v>
       </c>
       <c r="H467" t="n">
         <v>44815</v>
@@ -13999,7 +13999,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H470" t="n">
         <v>36379</v>
@@ -14144,7 +14144,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H475" t="n">
         <v>61238</v>
@@ -14202,7 +14202,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>11.8533792495728</v>
+        <v>11.8533802032471</v>
       </c>
       <c r="H477" t="n">
         <v>44549</v>
@@ -14231,7 +14231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G478" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H478" t="n">
         <v>133410</v>
@@ -14289,7 +14289,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G480" t="n">
-        <v>11.987208366394</v>
+        <v>11.9872074127197</v>
       </c>
       <c r="H480" t="n">
         <v>47163</v>
@@ -14318,7 +14318,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G481" t="n">
-        <v>12.0636806488037</v>
+        <v>12.063681602478</v>
       </c>
       <c r="H481" t="n">
         <v>28977</v>
@@ -14347,7 +14347,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G482" t="n">
-        <v>12.0254440307617</v>
+        <v>12.025444984436</v>
       </c>
       <c r="H482" t="n">
         <v>53386</v>
@@ -14376,7 +14376,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>12.273983001709</v>
+        <v>12.2739839553833</v>
       </c>
       <c r="H483" t="n">
         <v>87339</v>
@@ -14463,7 +14463,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H486" t="n">
         <v>45367</v>
@@ -14492,7 +14492,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G487" t="n">
-        <v>12.29310131073</v>
+        <v>12.2931022644043</v>
       </c>
       <c r="H487" t="n">
         <v>28990</v>
@@ -14521,7 +14521,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>12.6181125640869</v>
+        <v>12.6181135177612</v>
       </c>
       <c r="H488" t="n">
         <v>41086</v>
@@ -14695,7 +14695,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8151416778564</v>
+        <v>11.8151435852051</v>
       </c>
       <c r="H494" t="n">
         <v>12222</v>
@@ -14753,7 +14753,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G496" t="n">
-        <v>11.7960243225098</v>
+        <v>11.7960252761841</v>
       </c>
       <c r="H496" t="n">
         <v>19191</v>
@@ -14811,7 +14811,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>11.6239585876465</v>
+        <v>11.6239595413208</v>
       </c>
       <c r="H498" t="n">
         <v>38500</v>
@@ -14840,7 +14840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G499" t="n">
-        <v>12.216628074646</v>
+        <v>12.2166290283203</v>
       </c>
       <c r="H499" t="n">
         <v>77135</v>
@@ -14898,7 +14898,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>12.331337928772</v>
+        <v>12.3313388824463</v>
       </c>
       <c r="H501" t="n">
         <v>67973</v>
@@ -14956,7 +14956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G503" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H503" t="n">
         <v>36066</v>
@@ -15043,7 +15043,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H506" t="n">
         <v>176133</v>
@@ -15101,7 +15101,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G508" t="n">
-        <v>13.344612121582</v>
+        <v>13.3446111679077</v>
       </c>
       <c r="H508" t="n">
         <v>57867</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="G512" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H512" t="n">
         <v>20590</v>
@@ -15333,7 +15333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G516" t="n">
-        <v>13.2299022674561</v>
+        <v>13.2299013137817</v>
       </c>
       <c r="H516" t="n">
         <v>46611</v>
@@ -15420,7 +15420,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G519" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H519" t="n">
         <v>40078</v>
@@ -15449,7 +15449,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G520" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H520" t="n">
         <v>21758</v>
@@ -15478,7 +15478,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G521" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H521" t="n">
         <v>64754</v>
@@ -15507,7 +15507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G522" t="n">
-        <v>13.459321975708</v>
+        <v>13.4593210220337</v>
       </c>
       <c r="H522" t="n">
         <v>13016</v>
@@ -15565,7 +15565,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>13.440203666687</v>
+        <v>13.4402027130127</v>
       </c>
       <c r="H524" t="n">
         <v>10410</v>
@@ -15710,7 +15710,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1725454330444</v>
+        <v>13.1725463867188</v>
       </c>
       <c r="H529" t="n">
         <v>14580</v>
@@ -15884,7 +15884,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G535" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H535" t="n">
         <v>118515</v>
@@ -15971,7 +15971,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G538" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H538" t="n">
         <v>187474</v>
@@ -16000,7 +16000,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G539" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H539" t="n">
         <v>78221</v>
@@ -16029,7 +16029,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G540" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H540" t="n">
         <v>298944</v>
@@ -16116,7 +16116,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G543" t="n">
-        <v>13.5931510925293</v>
+        <v>13.593150138855</v>
       </c>
       <c r="H543" t="n">
         <v>40682</v>
@@ -16377,7 +16377,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>13.8416891098022</v>
+        <v>13.8416872024536</v>
       </c>
       <c r="H552" t="n">
         <v>18934</v>
@@ -16406,7 +16406,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G553" t="n">
-        <v>13.8225708007812</v>
+        <v>13.8225698471069</v>
       </c>
       <c r="H553" t="n">
         <v>12102</v>
@@ -16493,7 +16493,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G556" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H556" t="n">
         <v>13812</v>
@@ -16522,7 +16522,7 @@
         <v>14</v>
       </c>
       <c r="G557" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H557" t="n">
         <v>24397</v>
@@ -16551,7 +16551,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G558" t="n">
-        <v>13.401967048645</v>
+        <v>13.4019660949707</v>
       </c>
       <c r="H558" t="n">
         <v>27948</v>
@@ -16580,7 +16580,7 @@
         <v>14</v>
       </c>
       <c r="G559" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H559" t="n">
         <v>22244</v>
@@ -16609,7 +16609,7 @@
         <v>14</v>
       </c>
       <c r="G560" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H560" t="n">
         <v>16756</v>
@@ -16638,7 +16638,7 @@
         <v>14</v>
       </c>
       <c r="G561" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H561" t="n">
         <v>10223</v>
@@ -16754,7 +16754,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G565" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H565" t="n">
         <v>66135</v>
@@ -16783,7 +16783,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>13.7269792556763</v>
+        <v>13.726978302002</v>
       </c>
       <c r="H566" t="n">
         <v>38521</v>
@@ -16812,7 +16812,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G567" t="n">
-        <v>13.8799257278442</v>
+        <v>13.8799247741699</v>
       </c>
       <c r="H567" t="n">
         <v>34268</v>
@@ -16899,7 +16899,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H570" t="n">
         <v>219173</v>
@@ -16928,7 +16928,7 @@
         <v>14</v>
       </c>
       <c r="G571" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H571" t="n">
         <v>178522</v>
@@ -17044,7 +17044,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>13.7843341827393</v>
+        <v>13.7843332290649</v>
       </c>
       <c r="H575" t="n">
         <v>33781</v>
@@ -17102,7 +17102,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>14.5681858062744</v>
+        <v>14.5681867599487</v>
       </c>
       <c r="H577" t="n">
         <v>300850</v>
@@ -17131,7 +17131,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2622928619385</v>
+        <v>14.2622919082642</v>
       </c>
       <c r="H578" t="n">
         <v>113200</v>
@@ -17160,7 +17160,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3005294799805</v>
+        <v>14.3005285263062</v>
       </c>
       <c r="H579" t="n">
         <v>77910</v>
@@ -17479,7 +17479,7 @@
         <v>14</v>
       </c>
       <c r="G590" t="n">
-        <v>13.382848739624</v>
+        <v>13.3828477859497</v>
       </c>
       <c r="H590" t="n">
         <v>109158</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>12.7137050628662</v>
+        <v>12.7137060165405</v>
       </c>
       <c r="H598" t="n">
         <v>61248</v>
@@ -17740,7 +17740,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G599" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H599" t="n">
         <v>76279</v>
@@ -17798,7 +17798,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>12.7328233718872</v>
+        <v>12.7328243255615</v>
       </c>
       <c r="H601" t="n">
         <v>36560</v>
@@ -17827,7 +17827,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>12.8092966079712</v>
+        <v>12.8092975616455</v>
       </c>
       <c r="H602" t="n">
         <v>51879</v>
@@ -17914,7 +17914,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G605" t="n">
-        <v>12.312219619751</v>
+        <v>12.3122205734253</v>
       </c>
       <c r="H605" t="n">
         <v>89825</v>
@@ -17943,7 +17943,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G606" t="n">
-        <v>12.2548637390137</v>
+        <v>12.2548656463623</v>
       </c>
       <c r="H606" t="n">
         <v>57474</v>
@@ -18030,7 +18030,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H609" t="n">
         <v>88111</v>
@@ -18088,7 +18088,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="n">
-        <v>13.268138885498</v>
+        <v>13.2681379318237</v>
       </c>
       <c r="H611" t="n">
         <v>86158</v>
@@ -18175,7 +18175,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G614" t="n">
-        <v>13.3637294769287</v>
+        <v>13.3637285232544</v>
       </c>
       <c r="H614" t="n">
         <v>147836</v>
@@ -18262,7 +18262,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G617" t="n">
-        <v>13.0387182235718</v>
+        <v>13.0387172698975</v>
       </c>
       <c r="H617" t="n">
         <v>46574</v>
@@ -18407,7 +18407,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H622" t="n">
         <v>40402</v>
@@ -18436,7 +18436,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H623" t="n">
         <v>82380</v>
@@ -18465,7 +18465,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G624" t="n">
-        <v>12.7710599899292</v>
+        <v>12.7710609436035</v>
       </c>
       <c r="H624" t="n">
         <v>62905</v>
@@ -18494,7 +18494,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>12.6754684448242</v>
+        <v>12.6754693984985</v>
       </c>
       <c r="H625" t="n">
         <v>51174</v>
@@ -18581,7 +18581,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>12.6563501358032</v>
+        <v>12.6563510894775</v>
       </c>
       <c r="H628" t="n">
         <v>43747</v>
@@ -18668,7 +18668,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>12.8284149169922</v>
+        <v>12.8284158706665</v>
       </c>
       <c r="H631" t="n">
         <v>69447</v>
@@ -18784,7 +18784,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G635" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H635" t="n">
         <v>124717</v>
@@ -18871,7 +18871,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H638" t="n">
         <v>21080</v>
@@ -18900,7 +18900,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G639" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H639" t="n">
         <v>40704</v>
@@ -18929,7 +18929,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G640" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H640" t="n">
         <v>101641</v>
@@ -18958,7 +18958,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G641" t="n">
-        <v>14.4047546386719</v>
+        <v>14.4047555923462</v>
       </c>
       <c r="H641" t="n">
         <v>104803</v>
@@ -19045,7 +19045,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G644" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H644" t="n">
         <v>37693</v>
@@ -19132,7 +19132,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G647" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H647" t="n">
         <v>62394</v>
@@ -19306,7 +19306,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G653" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H653" t="n">
         <v>67181</v>
@@ -19480,7 +19480,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H659" t="n">
         <v>65476</v>
@@ -19538,7 +19538,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H661" t="n">
         <v>35343</v>
@@ -19625,7 +19625,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G664" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H664" t="n">
         <v>45922</v>
@@ -19654,7 +19654,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G665" t="n">
-        <v>15.9751262664795</v>
+        <v>15.9751253128052</v>
       </c>
       <c r="H665" t="n">
         <v>60499</v>
@@ -19683,7 +19683,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G666" t="n">
-        <v>16.1108360290527</v>
+        <v>16.1108379364014</v>
       </c>
       <c r="H666" t="n">
         <v>28199</v>
@@ -19770,7 +19770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>15.1220846176147</v>
+        <v>15.1220855712891</v>
       </c>
       <c r="H669" t="n">
         <v>107477</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>14.6761770248413</v>
+        <v>14.6761779785156</v>
       </c>
       <c r="H672" t="n">
         <v>131068</v>
@@ -19944,7 +19944,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G675" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H675" t="n">
         <v>84935</v>
@@ -20002,7 +20002,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G677" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H677" t="n">
         <v>28484</v>
@@ -20031,7 +20031,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G678" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H678" t="n">
         <v>45965</v>
@@ -20089,7 +20089,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H680" t="n">
         <v>49932</v>
@@ -20205,7 +20205,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H684" t="n">
         <v>33213</v>
@@ -20263,7 +20263,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H686" t="n">
         <v>149634</v>
@@ -20292,7 +20292,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G687" t="n">
-        <v>15.8394155502319</v>
+        <v>15.8394145965576</v>
       </c>
       <c r="H687" t="n">
         <v>39470</v>
@@ -20350,7 +20350,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G689" t="n">
-        <v>16.1496105194092</v>
+        <v>16.1496124267578</v>
       </c>
       <c r="H689" t="n">
         <v>60094</v>
@@ -20553,7 +20553,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G696" t="n">
-        <v>15.6843156814575</v>
+        <v>15.6843166351318</v>
       </c>
       <c r="H696" t="n">
         <v>33104</v>
@@ -20582,7 +20582,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>15.8975763320923</v>
+        <v>15.8975772857666</v>
       </c>
       <c r="H697" t="n">
         <v>154495</v>
@@ -20611,7 +20611,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H698" t="n">
         <v>76799</v>
@@ -20640,7 +20640,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G699" t="n">
-        <v>15.3741188049316</v>
+        <v>15.374119758606</v>
       </c>
       <c r="H699" t="n">
         <v>43123</v>
@@ -20727,7 +20727,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G702" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H702" t="n">
         <v>27978</v>
@@ -20843,7 +20843,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H706" t="n">
         <v>80940</v>
@@ -20872,7 +20872,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G707" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H707" t="n">
         <v>82998</v>
@@ -20988,7 +20988,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.4128942489624</v>
+        <v>15.4128932952881</v>
       </c>
       <c r="H711" t="n">
         <v>31373</v>
@@ -21046,7 +21046,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H713" t="n">
         <v>58117</v>
@@ -21191,7 +21191,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G718" t="n">
-        <v>15.141471862793</v>
+        <v>15.1414728164673</v>
       </c>
       <c r="H718" t="n">
         <v>55322</v>
@@ -21249,7 +21249,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>15.0833110809326</v>
+        <v>15.0833101272583</v>
       </c>
       <c r="H720" t="n">
         <v>39360</v>
@@ -21278,7 +21278,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G721" t="n">
-        <v>14.966986656189</v>
+        <v>14.9669857025146</v>
       </c>
       <c r="H721" t="n">
         <v>65632</v>
@@ -21307,7 +21307,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>14.8506631851196</v>
+        <v>14.8506622314453</v>
       </c>
       <c r="H722" t="n">
         <v>53763</v>
@@ -21394,7 +21394,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>14.3078184127808</v>
+        <v>14.3078193664551</v>
       </c>
       <c r="H725" t="n">
         <v>86664</v>
@@ -21423,7 +21423,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G726" t="n">
-        <v>14.4823045730591</v>
+        <v>14.4823036193848</v>
       </c>
       <c r="H726" t="n">
         <v>87213</v>
@@ -21452,7 +21452,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H727" t="n">
         <v>73456</v>
@@ -21597,7 +21597,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G732" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H732" t="n">
         <v>67534</v>
@@ -21655,7 +21655,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2302703857422</v>
+        <v>14.2302694320679</v>
       </c>
       <c r="H734" t="n">
         <v>45192</v>
@@ -21713,7 +21713,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G736" t="n">
-        <v>15.2771835327148</v>
+        <v>15.2771825790405</v>
       </c>
       <c r="H736" t="n">
         <v>101028</v>
@@ -21771,7 +21771,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G738" t="n">
-        <v>15.2965707778931</v>
+        <v>15.2965698242188</v>
       </c>
       <c r="H738" t="n">
         <v>284400</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8700494766235</v>
+        <v>14.8700504302979</v>
       </c>
       <c r="H739" t="n">
         <v>99147</v>
@@ -21916,7 +21916,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5486068725586</v>
+        <v>15.5486059188843</v>
       </c>
       <c r="H743" t="n">
         <v>51182</v>
@@ -22032,7 +22032,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G747" t="n">
-        <v>15.8781871795654</v>
+        <v>15.8781890869141</v>
       </c>
       <c r="H747" t="n">
         <v>39016</v>
@@ -22148,7 +22148,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>15.2577953338623</v>
+        <v>15.2577962875366</v>
       </c>
       <c r="H751" t="n">
         <v>131748</v>
@@ -22235,7 +22235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H754" t="n">
         <v>50268</v>
@@ -22264,7 +22264,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>14.9282112121582</v>
+        <v>14.9282121658325</v>
       </c>
       <c r="H755" t="n">
         <v>44022</v>
@@ -22438,7 +22438,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G761" t="n">
-        <v>14.1914949417114</v>
+        <v>14.1914958953857</v>
       </c>
       <c r="H761" t="n">
         <v>62425</v>
@@ -22496,7 +22496,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H763" t="n">
         <v>51431</v>
@@ -22525,7 +22525,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H764" t="n">
         <v>67676</v>
@@ -22583,7 +22583,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>14.2108821868896</v>
+        <v>14.210883140564</v>
       </c>
       <c r="H766" t="n">
         <v>97709</v>
@@ -22612,7 +22612,7 @@
         <v>14.5</v>
       </c>
       <c r="G767" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H767" t="n">
         <v>48972</v>
@@ -22641,7 +22641,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G768" t="n">
-        <v>13.9976215362549</v>
+        <v>13.9976224899292</v>
       </c>
       <c r="H768" t="n">
         <v>48388</v>
@@ -22670,7 +22670,7 @@
         <v>14.5</v>
       </c>
       <c r="G769" t="n">
-        <v>14.0557832717896</v>
+        <v>14.0557842254639</v>
       </c>
       <c r="H769" t="n">
         <v>43039</v>
@@ -22728,7 +22728,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G771" t="n">
-        <v>13.6874256134033</v>
+        <v>13.687424659729</v>
       </c>
       <c r="H771" t="n">
         <v>91611</v>
@@ -22757,7 +22757,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G772" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H772" t="n">
         <v>59694</v>
@@ -22815,7 +22815,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G774" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H774" t="n">
         <v>46705</v>
@@ -22931,7 +22931,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G778" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H778" t="n">
         <v>54214</v>
@@ -22960,7 +22960,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G779" t="n">
-        <v>13.163969039917</v>
+        <v>13.1639680862427</v>
       </c>
       <c r="H779" t="n">
         <v>31292</v>
@@ -23047,7 +23047,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>13.222131729126</v>
+        <v>13.2221307754517</v>
       </c>
       <c r="H782" t="n">
         <v>29208</v>
@@ -23076,7 +23076,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G783" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H783" t="n">
         <v>48982</v>
@@ -23105,7 +23105,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G784" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H784" t="n">
         <v>44891</v>
@@ -23192,7 +23192,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G787" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H787" t="n">
         <v>75458</v>
@@ -23221,7 +23221,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G788" t="n">
-        <v>13.9200735092163</v>
+        <v>13.920072555542</v>
       </c>
       <c r="H788" t="n">
         <v>161892</v>
@@ -23453,7 +23453,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H796" t="n">
         <v>130807</v>
@@ -23511,7 +23511,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H798" t="n">
         <v>24558</v>
@@ -23598,7 +23598,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H801" t="n">
         <v>52319</v>
@@ -23627,7 +23627,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3578405380249</v>
+        <v>13.3578414916992</v>
       </c>
       <c r="H802" t="n">
         <v>34321</v>
@@ -23772,7 +23772,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>13.2802925109863</v>
+        <v>13.280291557312</v>
       </c>
       <c r="H807" t="n">
         <v>77476</v>
@@ -23859,7 +23859,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>13.8619108200073</v>
+        <v>13.8619117736816</v>
       </c>
       <c r="H810" t="n">
         <v>292244</v>
@@ -23888,7 +23888,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G811" t="n">
-        <v>14.5210781097412</v>
+        <v>14.5210790634155</v>
       </c>
       <c r="H811" t="n">
         <v>260837</v>
@@ -23917,7 +23917,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G812" t="n">
-        <v>14.0751714706421</v>
+        <v>14.0751724243164</v>
       </c>
       <c r="H812" t="n">
         <v>95170</v>
@@ -24062,7 +24062,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G817" t="n">
-        <v>13.6098756790161</v>
+        <v>13.6098766326904</v>
       </c>
       <c r="H817" t="n">
         <v>77436</v>
@@ -24236,7 +24236,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0088701248169</v>
+        <v>13.0088710784912</v>
       </c>
       <c r="H823" t="n">
         <v>139568</v>
@@ -24294,7 +24294,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G825" t="n">
-        <v>13.1251935958862</v>
+        <v>13.1251945495605</v>
       </c>
       <c r="H825" t="n">
         <v>40244</v>
@@ -24323,7 +24323,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>12.9507083892822</v>
+        <v>12.9507074356079</v>
       </c>
       <c r="H826" t="n">
         <v>46870</v>
@@ -24352,7 +24352,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G827" t="n">
-        <v>12.9700965881348</v>
+        <v>12.9700956344604</v>
       </c>
       <c r="H827" t="n">
         <v>35005</v>
@@ -24381,7 +24381,7 @@
         <v>13.5</v>
       </c>
       <c r="G828" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H828" t="n">
         <v>44484</v>
@@ -24584,7 +24584,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>13.4160041809082</v>
+        <v>13.4160032272339</v>
       </c>
       <c r="H835" t="n">
         <v>51758</v>
@@ -24961,7 +24961,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H848" t="n">
         <v>65992</v>
@@ -24990,7 +24990,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G849" t="n">
-        <v>12.349702835083</v>
+        <v>12.3497018814087</v>
       </c>
       <c r="H849" t="n">
         <v>101683</v>
@@ -25193,7 +25193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G856" t="n">
-        <v>12.5241889953613</v>
+        <v>12.524188041687</v>
       </c>
       <c r="H856" t="n">
         <v>89742</v>
@@ -25425,7 +25425,7 @@
         <v>13</v>
       </c>
       <c r="G864" t="n">
-        <v>12.6017370223999</v>
+        <v>12.6017379760742</v>
       </c>
       <c r="H864" t="n">
         <v>23829</v>
@@ -25454,7 +25454,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G865" t="n">
-        <v>12.5435743331909</v>
+        <v>12.5435752868652</v>
       </c>
       <c r="H865" t="n">
         <v>77981</v>
@@ -25512,7 +25512,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G867" t="n">
-        <v>11.9037952423096</v>
+        <v>11.9037942886353</v>
       </c>
       <c r="H867" t="n">
         <v>165052</v>
@@ -25570,7 +25570,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>11.5354356765747</v>
+        <v>11.535436630249</v>
       </c>
       <c r="H869" t="n">
         <v>221362</v>
@@ -25657,7 +25657,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G872" t="n">
-        <v>11.8262462615967</v>
+        <v>11.8262453079224</v>
       </c>
       <c r="H872" t="n">
         <v>56333</v>
@@ -25715,7 +25715,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G874" t="n">
-        <v>11.6129846572876</v>
+        <v>11.6129856109619</v>
       </c>
       <c r="H874" t="n">
         <v>58043</v>
@@ -25773,7 +25773,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G876" t="n">
-        <v>11.6905355453491</v>
+        <v>11.6905345916748</v>
       </c>
       <c r="H876" t="n">
         <v>76554</v>
@@ -25802,7 +25802,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0201187133789</v>
+        <v>12.0201177597046</v>
       </c>
       <c r="H877" t="n">
         <v>82169</v>
@@ -25831,7 +25831,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G878" t="n">
-        <v>12.1558303833008</v>
+        <v>12.1558294296265</v>
       </c>
       <c r="H878" t="n">
         <v>210169</v>
@@ -25976,7 +25976,7 @@
         <v>13.5</v>
       </c>
       <c r="G883" t="n">
-        <v>13.0864200592041</v>
+        <v>13.0864191055298</v>
       </c>
       <c r="H883" t="n">
         <v>63353</v>
@@ -37002,6 +37002,35 @@
         <v>76785</v>
       </c>
       <c r="I1263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1264" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>62000</v>
+      </c>
+      <c r="I1264" t="s">
         <v>9</v>
       </c>
     </row>
